--- a/data/Matriz_Normativa_IA_Educacion_LATAM.xlsx
+++ b/data/Matriz_Normativa_IA_Educacion_LATAM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tecmx-my.sharepoint.com/personal/a00834778_tec_mx/Documents/Desktop/Carlos Auquilla/Proyectos/GENIAL/GENIAL_dev/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="825" documentId="13_ncr:1_{65400818-7CE5-0644-BE68-1BD2DD50F50F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9789FD9-D95A-4DBB-94ED-392668BBD5D2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DEF93B8B-1B75-490B-94A3-E0F7B496BF87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1099" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1099" uniqueCount="388">
   <si>
     <t>Investigador</t>
   </si>
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Senado de la República </t>
   </si>
   <si>
-    <t>Ético-regulatorio</t>
+    <t>Ética</t>
   </si>
   <si>
     <t>Indirecto</t>
@@ -156,9 +156,6 @@
     <t>Oficina de la UNESCO en México + Gobierno del Estado de Guanajuato</t>
   </si>
   <si>
-    <t>Ética</t>
-  </si>
-  <si>
     <t>Sección/Capítulo</t>
   </si>
   <si>
@@ -276,7 +273,7 @@
     <t>Guía de uso de IA con perspectiva de género e interseccionalidad (Diplomado Relaciones de Género)</t>
   </si>
   <si>
-    <t>UNAM - Centro de Investigaciones y Estudios de Género (CIEG)</t>
+    <t>UNAM</t>
   </si>
   <si>
     <t>https://cieg.unam.mx/docs/difusion/uso-etico-IA-23DRG.pdf</t>
@@ -286,9 +283,6 @@
   </si>
   <si>
     <t>Recomendaciones para el uso educativo de la Inteligencia Artificial</t>
-  </si>
-  <si>
-    <t>UNAM (Coordinación GAIA-Gen)</t>
   </si>
   <si>
     <t>https://iagen.unam.mx/recursos/Recomendaciones_IAGEN_UNAM_2025.pdf</t>
@@ -412,9 +406,6 @@
     <t>Uso y  desarrollo ético de la Inteligencia Artificial en la Universidad: docencia e investigación</t>
   </si>
   <si>
-    <t>UNAM</t>
-  </si>
-  <si>
     <t>https://www.tic.unam.mx/wp-content/uploads/2025/11/Uso-y-desarrollo-etico-del-IA-en-la-UNAM_v-digital.pdf</t>
   </si>
   <si>
@@ -604,340 +595,337 @@
     <t>Código de Ética de la UNAM</t>
   </si>
   <si>
+    <t>26/08/2024</t>
+  </si>
+  <si>
+    <t>https://www.gaceta.unam.mx/promueve-la-unam-integridad-academica/</t>
+  </si>
+  <si>
+    <t>Regula las prácticas del uso de la 'inteligencia artificial' y establece lineamientos para evitar el 'plagio' y respetar los 'derechos de autor'. Promueve la 'integridad académica' como un principio fundamental en la comunidad universitaria.</t>
+  </si>
+  <si>
+    <t>GUÍA EN INTELIGENCIA ARTIFICIAL</t>
+  </si>
+  <si>
+    <t>CETYS Universidad</t>
+  </si>
+  <si>
+    <t>https://repositorio.cetys.mx/bitstream/60000/1856/1/GUIA%20EN%20INTELIGENCIA%20ARTIFICIAL.pdf</t>
+  </si>
+  <si>
+    <t>Establece lineamientos para el uso de herramientas de inteligencia artificial en CETYS Universidad. Proporciona un marco de referencia para la alfabetización en IA en el contexto educativo.</t>
+  </si>
+  <si>
+    <t>01/05/2025</t>
+  </si>
+  <si>
+    <t>https://innovacioneducativa.ibero.mx/wp-content/uploads/2025/05/Estrategia-Pedagogica-DIGITAL.pdf?pid=753</t>
+  </si>
+  <si>
+    <t>Establece un marco estratégico para la 'adopción integral y transformadora de la IA' en la universidad. Propone un enfoque sistémico y participativo, destacando la importancia de la 'pedagogía dinámica' en la integración de la IA en los procesos educativos.</t>
+  </si>
+  <si>
+    <t>CÓDIGO DE ÉTICA DE LA UNIVERSIDAD DE GUADALAJARA</t>
+  </si>
+  <si>
+    <t>01/02/2018</t>
+  </si>
+  <si>
+    <t>https://secgral.udg.mx/sites/default/files/Normatividad_general/2018-03-02-codigo-de-etica-feb2018.pdf</t>
+  </si>
+  <si>
+    <t>Establece los 'principios y valores' que rigen la conducta de la comunidad universitaria, promoviendo la 'diversidad', 'equidad' y 'honestidad'. Aunque no menciona IA directamente, su enfoque ético es relevante para la implementación de tecnologías en educación.</t>
+  </si>
+  <si>
+    <t>Criterios para el uso de Inteligencia Artificial Generativa en la Universidad Autónoma del Estado de México</t>
+  </si>
+  <si>
+    <t>Universidad Autónoma del Estado de México</t>
+  </si>
+  <si>
+    <t>01/02/2025</t>
+  </si>
+  <si>
+    <t>https://campusvirtual.uaemex.mx/pdf/Innovacion/CriteriosIAGen.pdf</t>
+  </si>
+  <si>
+    <t>Establece un marco institucional para el uso de 'Inteligencia Artificial Generativa' en la educación, promoviendo el desarrollo de competencias tecnológicas y un enfoque ético. Fomenta la 'integridad académica' y la 'protección de datos personales e institucionales' en el proceso de enseñanza-aprendizaje.</t>
+  </si>
+  <si>
+    <t>Acuerdo de creación del Consejo Coordinador de Inteligencia Artificial</t>
+  </si>
+  <si>
+    <t>https://www.gaceta.unam.mx/wp-content/uploads/2026/03/260317-Acuerdo-creacion-CCOIA-UNAM.pdf</t>
+  </si>
+  <si>
+    <t>Establece la creación del 'Consejo Coordinador de Inteligencia Artificial' para articular capacidades institucionales y promover la 'integridad académica' y la 'propiedad intelectual' en el contexto de la IA. Este acuerdo busca fortalecer la educación y la innovación en la UNAM, alineándose con las demandas sociales contemporáneas.</t>
+  </si>
+  <si>
+    <t>Lineamientos para el uso adecuado de Inteligencia Artificial ...</t>
+  </si>
+  <si>
+    <t>IPN</t>
+  </si>
+  <si>
+    <t>https://portalinsitucionalsa.blob.core.windows.net/cms/e509379fc52143b238842100b969b5ac/documentos/Lineamientos+para+el+uso+de+la+IA.pdf</t>
+  </si>
+  <si>
+    <t>Establece directrices para el 'uso adecuado' de herramientas de IA en la educación. Promueve la integración de la IA en los procesos de enseñanza-aprendizaje y el entorno laboral de los egresados.</t>
+  </si>
+  <si>
+    <t>Lineamientos para el uso de inteligencia artificial</t>
+  </si>
+  <si>
+    <t>https://revistas.juridicas.unam.mx/index.php/derecho-electoral/lineamientos-ia</t>
+  </si>
+  <si>
+    <t>Establece lineamientos para el uso de herramientas de IA en la elaboración de manuscritos. Proporciona directrices para autores, promoviendo un uso responsable de la inteligencia artificial en el ámbito académico.</t>
+  </si>
+  <si>
+    <t>Cuestiones Constitucionales. Revista Mexicana de Derecho Constitucional</t>
+  </si>
+  <si>
+    <t>Promueve el 'uso responsable, ético y crítico' de tecnologías de Inteligencia Artificial. Establece directrices que pueden influir en la práctica educativa y la gobernanza de IA en el ámbito nacional.</t>
+  </si>
+  <si>
+    <t>Grupo Académico de Inteligencia Artificial Generativa en Educación (GAIA-GEN) de la Universidad</t>
+  </si>
+  <si>
+    <t>01/01/2024</t>
+  </si>
+  <si>
+    <t>https://posgrado.unam.mx/mesoamericanos/uploads/docs/2024/2025/Recomend+p+uso+educat+de+Inteligencia+Artificial+Generativa.pdf</t>
+  </si>
+  <si>
+    <t>Promueve la creación de redes de colaboración y propone 'lineamientos y recomendaciones de uso' de la IA en educación. Establece un marco para la formación continua en el ámbito de la inteligencia artificial generativa.</t>
+  </si>
+  <si>
+    <t>Lineamientos Éticos para el uso de la Inteligencia Artificial en la UAM Azcapotzalco</t>
+  </si>
+  <si>
+    <t>División de Ciencias Básicas e Ingeniería, UAM Azcapotzalco</t>
+  </si>
+  <si>
+    <t>https://consejoacademico.azc.uam.mx/pluginfile.php/7245/mod_folder/content/0/0.+Orden+del+día/Orden+del+día+Sesión+541+Ordinaria.pdf</t>
+  </si>
+  <si>
+    <t>Designa a un integrante del alumnado para completar la Comisión que propone 'Lineamientos Éticos para el uso de la Inteligencia Artificial'. Este documento es relevante para establecer principios éticos en el uso de IA en la institución.</t>
+  </si>
+  <si>
+    <t>Lineamientos interamericanos de gobernanza de datos e inteligencia artificial</t>
+  </si>
+  <si>
+    <t>OEA</t>
+  </si>
+  <si>
+    <t>https://www.oas.org/ext/es/principal/documentos/publicaciones/moduleid/7650/id/1080/lang/2/controller/item/action/download</t>
+  </si>
+  <si>
+    <t>Establece 'lineamientos transversales de gobernanza de datos a inteligencia artificial' y promueve la 'ética, transparencia y protección de derechos humanos'. Es un documento de trabajo que busca guiar la gobernanza de IA en la región.</t>
+  </si>
+  <si>
+    <t>Orientaciones y definiciones sobre el uso de la inteligencia artificial generativa en los procesos académicos</t>
+  </si>
+  <si>
+    <t>16/10/2023</t>
+  </si>
+  <si>
+    <t>Establece orientaciones para el uso de la 'inteligencia artificial generativa' en procesos académicos, promoviendo su integración en la educación superior. Proporciona recomendaciones y criterios para un uso ético y efectivo de la tecnología en el aprendizaje.</t>
+  </si>
+  <si>
+    <t>Recomendación emitida por el Consejo Consultivo del Instituto Federal de Telecomunicaciones (Instituto) en relación con inteligencia artificial y telecomunicaciones</t>
+  </si>
+  <si>
+    <t>Instituto Federal de Telecomunicaciones</t>
+  </si>
+  <si>
+    <t>https://www.ift.org.mx/sites/default/files/ag_ii-5_recomendacion_inteligenica_artificial_cci_acc.pdf</t>
+  </si>
+  <si>
+    <t>Establece recomendaciones sobre 'Regulación', 'Ética y gobernanza de la IA', y 'Capacidades o recursos humanos del sector'. Proporciona un marco para la implementación de la Estrategia Nacional de Inteligencia Artificial en México.</t>
+  </si>
+  <si>
+    <t>Marco general para el uso ético de sistemas de inteligencia artificial en la Universidad Panamericana</t>
+  </si>
+  <si>
+    <t>https://ciie.up.edu.mx/ai4ed</t>
+  </si>
+  <si>
+    <t>Establece 'principios éticos' para el uso de IA en la educación, promoviendo un examen continuo de prácticas académicas. Es un marco normativo que guía las decisiones relacionadas con sistemas de IA en la institución.</t>
+  </si>
+  <si>
+    <t>REGLAMENTO DE USO DE INTELIGENCIA ARTIFICIAL EN INSTITUCIONES DE EDUCACIÓN SUPERIOR ALPES</t>
+  </si>
+  <si>
+    <t>Alianza para la Educación Superior</t>
+  </si>
+  <si>
+    <t>01/07/2025</t>
+  </si>
+  <si>
+    <t>http://201.99.44.50/Boletas/PHP/reglamentoia.pdf</t>
+  </si>
+  <si>
+    <t>Regula el 'uso responsable, ético, transparente y pedagógicamente pertinente' de herramientas de IA en instituciones educativas. Define conceptos clave como 'Inteligencia Artificial' y 'Uso Responsable', aplicando a toda la comunidad ALPES en diversas actividades académicas y administrativas.</t>
+  </si>
+  <si>
+    <t>Políticas para el uso de inteligencia artificial. Versión 1.0</t>
+  </si>
+  <si>
+    <t>Universidad de Investigación e Innovación de México</t>
+  </si>
+  <si>
+    <t>01/06/2025</t>
+  </si>
+  <si>
+    <t>https://repositorio.uiix.edu.mx/server/api/core/bitstreams/e490e475-e5e2-464d-b3ef-90cc514b88d0/content</t>
+  </si>
+  <si>
+    <t>Establece un marco normativo que regula el uso ético y responsable de la inteligencia artificial en el postgrado, promoviendo su aprovechamiento para el aprendizaje y la investigación. Incluye principios como 'uso ético y responsable' y 'transparencia y atribución'.</t>
+  </si>
+  <si>
+    <t>Política de Uso Responsable de Inteligencia Artificial</t>
+  </si>
+  <si>
+    <t>Instituto Tecnológico de Celaya</t>
+  </si>
+  <si>
+    <t>01/03/2022</t>
+  </si>
+  <si>
+    <t>https://celaya.tecnm.mx/wp-content/uploads/2022/03/Politica_de_Uso_Responsable_de_Inteligencia_Artificial.pdf</t>
+  </si>
+  <si>
+    <t>Establece un marco ético y responsable para el uso de IA en la comunidad educativa, fundamentado en principios como 'Ética y Responsabilidad Social' y 'Inclusión y Democratización del Acceso'. Promueve la transparencia, supervisión y el acceso equitativo a herramientas de IA.</t>
+  </si>
+  <si>
+    <t>Guía para el uso ético de la IA - ult ver con observaciones SA</t>
+  </si>
+  <si>
+    <t>Universidad de Guanajuato</t>
+  </si>
+  <si>
+    <t>https://colmenia.ugto.mx/wp-content/uploads/2025/05/Guia-para-el-uso-etico-de-la-IA-version-preliminar.pdf</t>
+  </si>
+  <si>
+    <t>Establece principios éticos para el uso de IA en el contexto universitario, incluyendo 'prevención de sesgos algorítmicos' y 'protección de datos sensibles'. Proporciona un marco para la integración de la IA en la enseñanza, aprendizaje e investigación.</t>
+  </si>
+  <si>
+    <t>GUÍA BÁSICA PARA DOCENTES DE LA UAA 2024</t>
+  </si>
+  <si>
+    <t>Universidad Autónoma de Aguascalientes</t>
+  </si>
+  <si>
+    <t>01/05/2024</t>
+  </si>
+  <si>
+    <t>https://www.uaa.mx/portal/wp-content/uploads/2024/05/GBDUAA_2024-Final.pdf</t>
+  </si>
+  <si>
+    <t>Establece directrices sobre el uso de la 'Inteligencia Artificial' en la práctica docente, promoviendo su integración como herramienta educativa. Fomenta una reflexión ética y humanista sobre su aplicación en el aula, buscando mejorar las experiencias de aprendizaje.</t>
+  </si>
+  <si>
+    <t>Reglamentos de Estudios Profesionales 2025</t>
+  </si>
+  <si>
+    <t>ITAM</t>
+  </si>
+  <si>
+    <t>https://escolar.itam.mx/documentos/reg_licenciatura.pdf</t>
+  </si>
+  <si>
+    <t>Se estipula que los miembros de la comunidad se comprometen a utilizar las herramientas de inteligencia artificial de acuerdo con las recomendaciones y lineamientos que el Instituto expida al respecto.</t>
+  </si>
+  <si>
+    <t>Recomendaciones éticas sobre el uso de la inteligencia artificial (IA) en educación superior: una revisión sistemática</t>
+  </si>
+  <si>
+    <t>15/08/2025</t>
+  </si>
+  <si>
+    <t>https://www.google.com.mx/url?sa=t&amp;source=web&amp;rct=j&amp;opi=89978449&amp;url=https://dialogossobreeducacion.cucsh.udg.mx/index.php/DSE/article/view/1743/1499&amp;ved=2ahUKEwjz9uac26qUAxXtQTABHWEoDL4QFnoECBgQAQ&amp;usg=AOvVaw14DVx1Hkx2ZA_uXZVfbZug</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se establecen los siguientes segmentos: recomendaciones para instituciones, recomendaciones para profesorado y para alumnado. </t>
+  </si>
+  <si>
+    <t>Manual del Estudiante</t>
+  </si>
+  <si>
+    <t>CEDIM</t>
+  </si>
+  <si>
+    <t>https://www.primeringreso.cedim.edu.mx/wp-content/uploads/2023/12/Manual_del_Estudiante_CEDIM.pdf</t>
+  </si>
+  <si>
+    <t>Documento institucional reglamentario. Estipula que se debe citar el uso de la inteligencia artificial en todo tipo de trabajo.</t>
+  </si>
+  <si>
+    <t>Iniciativa con Proyecto de Decreto por el que se expide la Ley Federal para el desarrollo ético, soberano e inclusivo de la Inteligencia Artificial</t>
+  </si>
+  <si>
+    <t>Honorable Congreso de la Unión</t>
+  </si>
+  <si>
+    <t>30/04/2025</t>
+  </si>
+  <si>
+    <t>http://sil.gobernacion.gob.mx/Archivos/Documentos/2025/04/asun_4896460_20250430_1747757009.pdf</t>
+  </si>
+  <si>
+    <t>Establece un marco normativo para el desarrollo ético de la IA, abordando su impacto en 'educación', 'derechos' y 'oportunidades'. Promueve un enfoque 'soberano' e 'inclusivo' en la implementación de tecnologías de IA.</t>
+  </si>
+  <si>
+    <t>Lineamientos para presentar propuestas de experiencias en evaluación del y para el aprendizaje con inteligencia artificial</t>
+  </si>
+  <si>
+    <t>01/04/2026</t>
+  </si>
+  <si>
+    <t>https://www.cee.unam.mx/wp-content/uploads/2026/04/EvaluaFEST_2026_Lineamientos_para_presentar_propuestas.pdf</t>
+  </si>
+  <si>
+    <t>Establece los 'Lineamientos para presentar propuestas de experiencias en evaluación del y para el aprendizaje con inteligencia artificial'. Define criterios como 'innovación en el uso de la IA' y ejes temáticos relacionados con la evaluación educativa.</t>
+  </si>
+  <si>
+    <t>Lineamientos Éticos para el Uso Responsable de la Inteligencia Artificial</t>
+  </si>
+  <si>
+    <t>Benemérita Universidad Autónoma de Chiapas</t>
+  </si>
+  <si>
+    <t>05/05/2026</t>
+  </si>
+  <si>
+    <t>https://www.unach.mx/images/documentos/legislacion/Lineamientos-ticos-para-el-uso-responsable-de-la-IA.pdf</t>
+  </si>
+  <si>
+    <t>Establece los 'Lineamientos Éticos para el Uso Responsable de la Inteligencia Artificial' en la UNACH, fundamentándose en la 'Ley General de Educación Superior' y la 'Ley de Ciencia, Tecnología e Innovación'. Promueve un enfoque institucional basado en riesgos para la gobernanza de la IA en sus funciones académicas y administrativas.</t>
+  </si>
+  <si>
+    <t>APA 7 - Universidad IEU</t>
+  </si>
+  <si>
+    <t>Universidad IEU</t>
+  </si>
+  <si>
+    <t>No Indica</t>
+  </si>
+  <si>
+    <t>https://media.ieu.edu.mx/supportFiles/apa/manualCriteriosEditoriales_APA6.pdf</t>
+  </si>
+  <si>
+    <t>Establece lineamientos para la citación de 'contenido desarrollado con inteligencia artificial generativa' y 'figuras elaboradas con herramientas de inteligencia artificial'. Proporciona directrices para la escritura académica en el contexto educativo, promoviendo la claridad y rigor en la presentación de trabajos.</t>
+  </si>
+  <si>
+    <t>http://repositorio.cetys.mx:8080/bitstream/60000/1856/1/GUIA+EN+INTELIGENCIA+ARTIFICIAL.pdf</t>
+  </si>
+  <si>
+    <t>Establece lineamientos para el uso de herramientas de 'inteligencia artificial' en CETYS Universidad. Proporciona un marco de referencia para la alfabetización en IA en el contexto educativo.</t>
+  </si>
+  <si>
     <t>Universidad Nacional Autónoma de México</t>
-  </si>
-  <si>
-    <t>26/08/2024</t>
-  </si>
-  <si>
-    <t>https://www.gaceta.unam.mx/promueve-la-unam-integridad-academica/</t>
-  </si>
-  <si>
-    <t>Regula las prácticas del uso de la 'inteligencia artificial' y establece lineamientos para evitar el 'plagio' y respetar los 'derechos de autor'. Promueve la 'integridad académica' como un principio fundamental en la comunidad universitaria.</t>
-  </si>
-  <si>
-    <t>GUÍA EN INTELIGENCIA ARTIFICIAL</t>
-  </si>
-  <si>
-    <t>CETYS Universidad</t>
-  </si>
-  <si>
-    <t>https://repositorio.cetys.mx/bitstream/60000/1856/1/GUIA%20EN%20INTELIGENCIA%20ARTIFICIAL.pdf</t>
-  </si>
-  <si>
-    <t>Establece lineamientos para el uso de herramientas de inteligencia artificial en CETYS Universidad. Proporciona un marco de referencia para la alfabetización en IA en el contexto educativo.</t>
-  </si>
-  <si>
-    <t>01/05/2025</t>
-  </si>
-  <si>
-    <t>https://innovacioneducativa.ibero.mx/wp-content/uploads/2025/05/Estrategia-Pedagogica-DIGITAL.pdf?pid=753</t>
-  </si>
-  <si>
-    <t>Establece un marco estratégico para la 'adopción integral y transformadora de la IA' en la universidad. Propone un enfoque sistémico y participativo, destacando la importancia de la 'pedagogía dinámica' en la integración de la IA en los procesos educativos.</t>
-  </si>
-  <si>
-    <t>CÓDIGO DE ÉTICA DE LA UNIVERSIDAD DE GUADALAJARA</t>
-  </si>
-  <si>
-    <t>01/02/2018</t>
-  </si>
-  <si>
-    <t>https://secgral.udg.mx/sites/default/files/Normatividad_general/2018-03-02-codigo-de-etica-feb2018.pdf</t>
-  </si>
-  <si>
-    <t>Establece los 'principios y valores' que rigen la conducta de la comunidad universitaria, promoviendo la 'diversidad', 'equidad' y 'honestidad'. Aunque no menciona IA directamente, su enfoque ético es relevante para la implementación de tecnologías en educación.</t>
-  </si>
-  <si>
-    <t>Criterios para el uso de Inteligencia Artificial Generativa en la Universidad Autónoma del Estado de México</t>
-  </si>
-  <si>
-    <t>Universidad Autónoma del Estado de México</t>
-  </si>
-  <si>
-    <t>01/02/2025</t>
-  </si>
-  <si>
-    <t>https://campusvirtual.uaemex.mx/pdf/Innovacion/CriteriosIAGen.pdf</t>
-  </si>
-  <si>
-    <t>Establece un marco institucional para el uso de 'Inteligencia Artificial Generativa' en la educación, promoviendo el desarrollo de competencias tecnológicas y un enfoque ético. Fomenta la 'integridad académica' y la 'protección de datos personales e institucionales' en el proceso de enseñanza-aprendizaje.</t>
-  </si>
-  <si>
-    <t>Acuerdo de creación del Consejo Coordinador de Inteligencia Artificial</t>
-  </si>
-  <si>
-    <t>https://www.gaceta.unam.mx/wp-content/uploads/2026/03/260317-Acuerdo-creacion-CCOIA-UNAM.pdf</t>
-  </si>
-  <si>
-    <t>Establece la creación del 'Consejo Coordinador de Inteligencia Artificial' para articular capacidades institucionales y promover la 'integridad académica' y la 'propiedad intelectual' en el contexto de la IA. Este acuerdo busca fortalecer la educación y la innovación en la UNAM, alineándose con las demandas sociales contemporáneas.</t>
-  </si>
-  <si>
-    <t>Lineamientos para el uso adecuado de Inteligencia Artificial ...</t>
-  </si>
-  <si>
-    <t>IPN</t>
-  </si>
-  <si>
-    <t>https://portalinsitucionalsa.blob.core.windows.net/cms/e509379fc52143b238842100b969b5ac/documentos/Lineamientos+para+el+uso+de+la+IA.pdf</t>
-  </si>
-  <si>
-    <t>Establece directrices para el 'uso adecuado' de herramientas de IA en la educación. Promueve la integración de la IA en los procesos de enseñanza-aprendizaje y el entorno laboral de los egresados.</t>
-  </si>
-  <si>
-    <t>Lineamientos para el uso de inteligencia artificial</t>
-  </si>
-  <si>
-    <t>https://revistas.juridicas.unam.mx/index.php/derecho-electoral/lineamientos-ia</t>
-  </si>
-  <si>
-    <t>Establece lineamientos para el uso de herramientas de IA en la elaboración de manuscritos. Proporciona directrices para autores, promoviendo un uso responsable de la inteligencia artificial en el ámbito académico.</t>
-  </si>
-  <si>
-    <t>Cuestiones Constitucionales. Revista Mexicana de Derecho Constitucional</t>
-  </si>
-  <si>
-    <t>Promueve el 'uso responsable, ético y crítico' de tecnologías de Inteligencia Artificial. Establece directrices que pueden influir en la práctica educativa y la gobernanza de IA en el ámbito nacional.</t>
-  </si>
-  <si>
-    <t>Grupo Académico de Inteligencia Artificial Generativa en Educación (GAIA-GEN) de la Universidad</t>
-  </si>
-  <si>
-    <t>01/01/2024</t>
-  </si>
-  <si>
-    <t>https://posgrado.unam.mx/mesoamericanos/uploads/docs/2024/2025/Recomend+p+uso+educat+de+Inteligencia+Artificial+Generativa.pdf</t>
-  </si>
-  <si>
-    <t>Promueve la creación de redes de colaboración y propone 'lineamientos y recomendaciones de uso' de la IA en educación. Establece un marco para la formación continua en el ámbito de la inteligencia artificial generativa.</t>
-  </si>
-  <si>
-    <t>Lineamientos Éticos para el uso de la Inteligencia Artificial en la UAM Azcapotzalco</t>
-  </si>
-  <si>
-    <t>División de Ciencias Básicas e Ingeniería, UAM Azcapotzalco</t>
-  </si>
-  <si>
-    <t>https://consejoacademico.azc.uam.mx/pluginfile.php/7245/mod_folder/content/0/0.+Orden+del+día/Orden+del+día+Sesión+541+Ordinaria.pdf</t>
-  </si>
-  <si>
-    <t>Designa a un integrante del alumnado para completar la Comisión que propone 'Lineamientos Éticos para el uso de la Inteligencia Artificial'. Este documento es relevante para establecer principios éticos en el uso de IA en la institución.</t>
-  </si>
-  <si>
-    <t>Lineamientos interamericanos de gobernanza de datos e inteligencia artificial</t>
-  </si>
-  <si>
-    <t>OEA</t>
-  </si>
-  <si>
-    <t>https://www.oas.org/ext/es/principal/documentos/publicaciones/moduleid/7650/id/1080/lang/2/controller/item/action/download</t>
-  </si>
-  <si>
-    <t>Establece 'lineamientos transversales de gobernanza de datos a inteligencia artificial' y promueve la 'ética, transparencia y protección de derechos humanos'. Es un documento de trabajo que busca guiar la gobernanza de IA en la región.</t>
-  </si>
-  <si>
-    <t>Orientaciones y definiciones sobre el uso de la inteligencia artificial generativa en los procesos académicos</t>
-  </si>
-  <si>
-    <t>16/10/2023</t>
-  </si>
-  <si>
-    <t>Establece orientaciones para el uso de la 'inteligencia artificial generativa' en procesos académicos, promoviendo su integración en la educación superior. Proporciona recomendaciones y criterios para un uso ético y efectivo de la tecnología en el aprendizaje.</t>
-  </si>
-  <si>
-    <t>Recomendación emitida por el Consejo Consultivo del Instituto Federal de Telecomunicaciones (Instituto) en relación con inteligencia artificial y telecomunicaciones</t>
-  </si>
-  <si>
-    <t>Instituto Federal de Telecomunicaciones</t>
-  </si>
-  <si>
-    <t>https://www.ift.org.mx/sites/default/files/ag_ii-5_recomendacion_inteligenica_artificial_cci_acc.pdf</t>
-  </si>
-  <si>
-    <t>Establece recomendaciones sobre 'Regulación', 'Ética y gobernanza de la IA', y 'Capacidades o recursos humanos del sector'. Proporciona un marco para la implementación de la Estrategia Nacional de Inteligencia Artificial en México.</t>
-  </si>
-  <si>
-    <t>Marco general para el uso ético de sistemas de inteligencia artificial en la Universidad Panamericana</t>
-  </si>
-  <si>
-    <t>https://ciie.up.edu.mx/ai4ed</t>
-  </si>
-  <si>
-    <t>Establece 'principios éticos' para el uso de IA en la educación, promoviendo un examen continuo de prácticas académicas. Es un marco normativo que guía las decisiones relacionadas con sistemas de IA en la institución.</t>
-  </si>
-  <si>
-    <t>REGLAMENTO DE USO DE INTELIGENCIA ARTIFICIAL EN INSTITUCIONES DE EDUCACIÓN SUPERIOR ALPES</t>
-  </si>
-  <si>
-    <t>Alianza para la Educación Superior</t>
-  </si>
-  <si>
-    <t>01/07/2025</t>
-  </si>
-  <si>
-    <t>http://201.99.44.50/Boletas/PHP/reglamentoia.pdf</t>
-  </si>
-  <si>
-    <t>Regula el 'uso responsable, ético, transparente y pedagógicamente pertinente' de herramientas de IA en instituciones educativas. Define conceptos clave como 'Inteligencia Artificial' y 'Uso Responsable', aplicando a toda la comunidad ALPES en diversas actividades académicas y administrativas.</t>
-  </si>
-  <si>
-    <t>Políticas para el uso de inteligencia artificial. Versión 1.0</t>
-  </si>
-  <si>
-    <t>Universidad de Investigación e Innovación de México</t>
-  </si>
-  <si>
-    <t>01/06/2025</t>
-  </si>
-  <si>
-    <t>https://repositorio.uiix.edu.mx/server/api/core/bitstreams/e490e475-e5e2-464d-b3ef-90cc514b88d0/content</t>
-  </si>
-  <si>
-    <t>Establece un marco normativo que regula el uso ético y responsable de la inteligencia artificial en el postgrado, promoviendo su aprovechamiento para el aprendizaje y la investigación. Incluye principios como 'uso ético y responsable' y 'transparencia y atribución'.</t>
-  </si>
-  <si>
-    <t>Política de Uso Responsable de Inteligencia Artificial</t>
-  </si>
-  <si>
-    <t>Instituto Tecnológico de Celaya</t>
-  </si>
-  <si>
-    <t>01/03/2022</t>
-  </si>
-  <si>
-    <t>https://celaya.tecnm.mx/wp-content/uploads/2022/03/Politica_de_Uso_Responsable_de_Inteligencia_Artificial.pdf</t>
-  </si>
-  <si>
-    <t>Establece un marco ético y responsable para el uso de IA en la comunidad educativa, fundamentado en principios como 'Ética y Responsabilidad Social' y 'Inclusión y Democratización del Acceso'. Promueve la transparencia, supervisión y el acceso equitativo a herramientas de IA.</t>
-  </si>
-  <si>
-    <t>Guía para el uso ético de la IA - ult ver con observaciones SA</t>
-  </si>
-  <si>
-    <t>Universidad de Guanajuato</t>
-  </si>
-  <si>
-    <t>https://colmenia.ugto.mx/wp-content/uploads/2025/05/Guia-para-el-uso-etico-de-la-IA-version-preliminar.pdf</t>
-  </si>
-  <si>
-    <t>Establece principios éticos para el uso de IA en el contexto universitario, incluyendo 'prevención de sesgos algorítmicos' y 'protección de datos sensibles'. Proporciona un marco para la integración de la IA en la enseñanza, aprendizaje e investigación.</t>
-  </si>
-  <si>
-    <t>GUÍA BÁSICA PARA DOCENTES DE LA UAA 2024</t>
-  </si>
-  <si>
-    <t>Universidad Autónoma de Aguascalientes</t>
-  </si>
-  <si>
-    <t>01/05/2024</t>
-  </si>
-  <si>
-    <t>https://www.uaa.mx/portal/wp-content/uploads/2024/05/GBDUAA_2024-Final.pdf</t>
-  </si>
-  <si>
-    <t>Establece directrices sobre el uso de la 'Inteligencia Artificial' en la práctica docente, promoviendo su integración como herramienta educativa. Fomenta una reflexión ética y humanista sobre su aplicación en el aula, buscando mejorar las experiencias de aprendizaje.</t>
-  </si>
-  <si>
-    <t>Reglamentos de Estudios Profesionales 2025</t>
-  </si>
-  <si>
-    <t>ITAM</t>
-  </si>
-  <si>
-    <t>https://escolar.itam.mx/documentos/reg_licenciatura.pdf</t>
-  </si>
-  <si>
-    <t>Se estipula que los miembros de la comunidad se comprometen a utilizar las herramientas de inteligencia artificial de acuerdo con las recomendaciones y lineamientos que el Instituto expida al respecto.</t>
-  </si>
-  <si>
-    <t>Recomendaciones éticas sobre el uso de la inteligencia artificial (IA) en educación superior: una revisión sistemática</t>
-  </si>
-  <si>
-    <t>15/08/2025</t>
-  </si>
-  <si>
-    <t>https://www.google.com.mx/url?sa=t&amp;source=web&amp;rct=j&amp;opi=89978449&amp;url=https://dialogossobreeducacion.cucsh.udg.mx/index.php/DSE/article/view/1743/1499&amp;ved=2ahUKEwjz9uac26qUAxXtQTABHWEoDL4QFnoECBgQAQ&amp;usg=AOvVaw14DVx1Hkx2ZA_uXZVfbZug</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Se establecen los siguientes segmentos: recomendaciones para instituciones, recomendaciones para profesorado y para alumnado. </t>
-  </si>
-  <si>
-    <t>Manual del Estudiante</t>
-  </si>
-  <si>
-    <t>CEDIM</t>
-  </si>
-  <si>
-    <t>https://www.primeringreso.cedim.edu.mx/wp-content/uploads/2023/12/Manual_del_Estudiante_CEDIM.pdf</t>
-  </si>
-  <si>
-    <t>Documento institucional reglamentario. Estipula que se debe citar el uso de la inteligencia artificial en todo tipo de trabajo.</t>
-  </si>
-  <si>
-    <t>Iniciativa con Proyecto de Decreto por el que se expide la Ley Federal para el desarrollo ético, soberano e inclusivo de la Inteligencia Artificial</t>
-  </si>
-  <si>
-    <t>Honorable Congreso de la Unión</t>
-  </si>
-  <si>
-    <t>30/04/2025</t>
-  </si>
-  <si>
-    <t>http://sil.gobernacion.gob.mx/Archivos/Documentos/2025/04/asun_4896460_20250430_1747757009.pdf</t>
-  </si>
-  <si>
-    <t>Establece un marco normativo para el desarrollo ético de la IA, abordando su impacto en 'educación', 'derechos' y 'oportunidades'. Promueve un enfoque 'soberano' e 'inclusivo' en la implementación de tecnologías de IA.</t>
-  </si>
-  <si>
-    <t>Lineamientos para presentar propuestas de experiencias en evaluación del y para el aprendizaje con inteligencia artificial</t>
-  </si>
-  <si>
-    <t>01/04/2026</t>
-  </si>
-  <si>
-    <t>https://www.cee.unam.mx/wp-content/uploads/2026/04/EvaluaFEST_2026_Lineamientos_para_presentar_propuestas.pdf</t>
-  </si>
-  <si>
-    <t>Establece los 'Lineamientos para presentar propuestas de experiencias en evaluación del y para el aprendizaje con inteligencia artificial'. Define criterios como 'innovación en el uso de la IA' y ejes temáticos relacionados con la evaluación educativa.</t>
-  </si>
-  <si>
-    <t>Lineamientos Éticos para el Uso Responsable de la Inteligencia Artificial</t>
-  </si>
-  <si>
-    <t>Benemérita Universidad Autónoma de Chiapas</t>
-  </si>
-  <si>
-    <t>05/05/2026</t>
-  </si>
-  <si>
-    <t>https://www.unach.mx/images/documentos/legislacion/Lineamientos-ticos-para-el-uso-responsable-de-la-IA.pdf</t>
-  </si>
-  <si>
-    <t>Establece los 'Lineamientos Éticos para el Uso Responsable de la Inteligencia Artificial' en la UNACH, fundamentándose en la 'Ley General de Educación Superior' y la 'Ley de Ciencia, Tecnología e Innovación'. Promueve un enfoque institucional basado en riesgos para la gobernanza de la IA en sus funciones académicas y administrativas.</t>
-  </si>
-  <si>
-    <t>APA 7 - Universidad IEU</t>
-  </si>
-  <si>
-    <t>Guía pedagógica</t>
-  </si>
-  <si>
-    <t>Universidad IEU</t>
-  </si>
-  <si>
-    <t>No Indica</t>
-  </si>
-  <si>
-    <t>https://media.ieu.edu.mx/supportFiles/apa/manualCriteriosEditoriales_APA6.pdf</t>
-  </si>
-  <si>
-    <t>Establece lineamientos para la citación de 'contenido desarrollado con inteligencia artificial generativa' y 'figuras elaboradas con herramientas de inteligencia artificial'. Proporciona directrices para la escritura académica en el contexto educativo, promoviendo la claridad y rigor en la presentación de trabajos.</t>
-  </si>
-  <si>
-    <t>http://repositorio.cetys.mx:8080/bitstream/60000/1856/1/GUIA+EN+INTELIGENCIA+ARTIFICIAL.pdf</t>
-  </si>
-  <si>
-    <t>Establece lineamientos para el uso de herramientas de 'inteligencia artificial' en CETYS Universidad. Proporciona un marco de referencia para la alfabetización en IA en el contexto educativo.</t>
   </si>
   <si>
     <t>https://cuaieed.unam.mx/descargas/recomendaciones-uso-iagen-docencia-unam-2023.pdf</t>
@@ -1058,7 +1046,7 @@
     <t>Suprema Corte de Justicia de la Nación</t>
   </si>
   <si>
-    <t>Protección de datos</t>
+    <t>Protección de Datos</t>
   </si>
   <si>
     <t>https://transparencia-ciudadana.scjn.gob.mx/resoluciones-relevantes-de-la-SCJN/derechos-digitales/ad-6-2025</t>
@@ -1221,9 +1209,6 @@
   </si>
   <si>
     <t>Derrogada</t>
-  </si>
-  <si>
-    <t>Protección de Datos</t>
   </si>
   <si>
     <t>Mención breve</t>
@@ -1339,7 +1324,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1371,7 +1356,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1733,7 +1717,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" ht="15">
       <c r="A2" s="3" t="s">
         <v>13</v>
       </c>
@@ -1775,7 +1759,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" ht="15">
       <c r="A3" s="3" t="s">
         <v>13</v>
       </c>
@@ -1836,28 +1820,28 @@
         <v>35</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J4" s="6">
         <v>45292</v>
       </c>
       <c r="K4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L4" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>39</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" ht="15">
       <c r="A5" s="3" t="s">
         <v>13</v>
       </c>
@@ -1865,10 +1849,10 @@
         <v>14</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>27</v>
@@ -1889,24 +1873,24 @@
         <v>45961</v>
       </c>
       <c r="K5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="L5" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L5" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="M5" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="15">
+      <c r="A6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>34</v>
@@ -1915,31 +1899,31 @@
         <v>27</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J6" s="6">
         <v>46051</v>
       </c>
       <c r="K6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="L6" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" ht="15">
       <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
@@ -1947,19 +1931,19 @@
         <v>14</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>20</v>
@@ -1971,16 +1955,16 @@
         <v>46038</v>
       </c>
       <c r="K7" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="L7" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" ht="15">
       <c r="A8" s="3" t="s">
         <v>13</v>
       </c>
@@ -1988,10 +1972,10 @@
         <v>14</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>56</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>27</v>
@@ -2000,7 +1984,7 @@
         <v>28</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>30</v>
@@ -2012,16 +1996,16 @@
         <v>46127</v>
       </c>
       <c r="K8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="L8" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" ht="15">
       <c r="A9" s="3" t="s">
         <v>13</v>
       </c>
@@ -2029,10 +2013,10 @@
         <v>14</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>17</v>
@@ -2041,28 +2025,28 @@
         <v>28</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J9" s="6">
         <v>46127</v>
       </c>
       <c r="K9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="L9" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>62</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" ht="15">
       <c r="A10" s="3" t="s">
         <v>13</v>
       </c>
@@ -2070,16 +2054,16 @@
         <v>14</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>29</v>
@@ -2094,24 +2078,24 @@
         <v>45352</v>
       </c>
       <c r="K10" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="L10" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="L10" s="3" t="s">
+      <c r="M10" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="15">
+      <c r="A11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>34</v>
@@ -2120,10 +2104,10 @@
         <v>27</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>30</v>
@@ -2135,33 +2119,33 @@
         <v>45778</v>
       </c>
       <c r="K11" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="L11" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="L11" s="3" t="s">
+      <c r="M11" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="15">
+      <c r="A12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="M11" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>29</v>
@@ -2176,24 +2160,24 @@
         <v>45809</v>
       </c>
       <c r="K12" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L12" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="L12" s="3" t="s">
+      <c r="M12" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="15">
+      <c r="A13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>34</v>
@@ -2202,10 +2186,10 @@
         <v>27</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>30</v>
@@ -2217,24 +2201,24 @@
         <v>45992</v>
       </c>
       <c r="K13" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="L13" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="L13" s="3" t="s">
+      <c r="M13" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="15">
+      <c r="A14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>79</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>26</v>
@@ -2243,7 +2227,7 @@
         <v>27</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>29</v>
@@ -2258,36 +2242,36 @@
         <v>45778</v>
       </c>
       <c r="K14" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="15">
+      <c r="A15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="3" t="s">
+      <c r="E15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="G15" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>30</v>
@@ -2299,16 +2283,16 @@
         <v>45778</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" ht="15">
       <c r="A16" s="3" t="s">
         <v>13</v>
       </c>
@@ -2316,7 +2300,7 @@
         <v>14</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>26</v>
@@ -2325,7 +2309,7 @@
         <v>27</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>29</v>
@@ -2340,24 +2324,24 @@
         <v>45778</v>
       </c>
       <c r="K16" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="60.75">
+      <c r="A17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="L16" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="57.95">
-      <c r="A17" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>34</v>
@@ -2366,10 +2350,10 @@
         <v>17</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>30</v>
@@ -2378,27 +2362,27 @@
         <v>21</v>
       </c>
       <c r="J17" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="L17" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="K17" s="3" t="s">
+      <c r="M17" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="60.75">
+      <c r="A18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="57.95">
-      <c r="A18" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>95</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>34</v>
@@ -2407,10 +2391,10 @@
         <v>17</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>30</v>
@@ -2419,27 +2403,27 @@
         <v>21</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K18" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="60.75">
+      <c r="A19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="57.95">
-      <c r="A19" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>98</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>34</v>
@@ -2448,10 +2432,10 @@
         <v>17</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>30</v>
@@ -2460,19 +2444,19 @@
         <v>21</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="15">
       <c r="A20" s="3" t="s">
         <v>13</v>
       </c>
@@ -2480,7 +2464,7 @@
         <v>14</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>16</v>
@@ -2489,10 +2473,10 @@
         <v>17</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>20</v>
@@ -2504,16 +2488,16 @@
         <v>45015</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="L20" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:13" ht="15">
       <c r="A21" s="3" t="s">
         <v>13</v>
       </c>
@@ -2521,7 +2505,7 @@
         <v>14</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>26</v>
@@ -2530,7 +2514,7 @@
         <v>27</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>29</v>
@@ -2545,16 +2529,16 @@
         <v>45292</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:13" ht="15">
       <c r="A22" s="3" t="s">
         <v>13</v>
       </c>
@@ -2562,7 +2546,7 @@
         <v>14</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>26</v>
@@ -2571,7 +2555,7 @@
         <v>27</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>29</v>
@@ -2586,13 +2570,13 @@
         <v>45215</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="13.5" customHeight="1">
@@ -2603,19 +2587,19 @@
         <v>14</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>20</v>
@@ -2627,33 +2611,33 @@
         <v>45778</v>
       </c>
       <c r="K23" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="L23" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="15">
+      <c r="A24" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="L23" s="12" t="s">
+      <c r="D24" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
-      <c r="A24" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>117</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>29</v>
@@ -2668,24 +2652,24 @@
         <v>45678</v>
       </c>
       <c r="K24" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="15">
+      <c r="A25" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>118</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
-      <c r="A25" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>34</v>
@@ -2694,7 +2678,7 @@
         <v>27</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>121</v>
+        <v>75</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>29</v>
@@ -2709,16 +2693,16 @@
         <v>45931</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="15">
       <c r="A26" s="3" t="s">
         <v>13</v>
       </c>
@@ -2726,19 +2710,19 @@
         <v>14</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>121</v>
+        <v>75</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>30</v>
@@ -2750,16 +2734,16 @@
         <v>45689</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="15">
       <c r="A27" s="10" t="s">
         <v>13</v>
       </c>
@@ -2767,7 +2751,7 @@
         <v>14</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>16</v>
@@ -2776,10 +2760,10 @@
         <v>17</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>30</v>
@@ -2788,19 +2772,19 @@
         <v>21</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:13" ht="15">
       <c r="A28" s="3" t="s">
         <v>13</v>
       </c>
@@ -2808,7 +2792,7 @@
         <v>14</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>16</v>
@@ -2817,10 +2801,10 @@
         <v>17</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>30</v>
@@ -2829,13 +2813,13 @@
         <v>21</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="M28" s="3" t="s">
         <v>24</v>
@@ -2849,19 +2833,19 @@
         <v>14</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>30</v>
@@ -2870,68 +2854,68 @@
         <v>21</v>
       </c>
       <c r="J29" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="15">
+      <c r="A30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="K29" s="3" t="s">
+      <c r="D30" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="L29" s="3" t="s">
+      <c r="G30" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J30" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13">
-      <c r="A30" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C30" s="3" t="s">
+      <c r="K30" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F30" s="3" t="s">
+      <c r="L30" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J30" s="6" t="s">
+      <c r="M30" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="15">
+      <c r="A31" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>143</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="L30" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="M30" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13">
-      <c r="A31" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>26</v>
@@ -2940,7 +2924,7 @@
         <v>27</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>29</v>
@@ -2949,30 +2933,30 @@
         <v>30</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J31" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="15">
+      <c r="A32" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>148</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="M31" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13">
-      <c r="A32" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>151</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>34</v>
@@ -2981,7 +2965,7 @@
         <v>27</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>29</v>
@@ -2993,27 +2977,27 @@
         <v>21</v>
       </c>
       <c r="J32" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="15">
+      <c r="A33" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>153</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13">
-      <c r="A33" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>156</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>26</v>
@@ -3022,7 +3006,7 @@
         <v>27</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>29</v>
@@ -3031,42 +3015,42 @@
         <v>30</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J33" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="15">
+      <c r="A34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="K33" s="3" t="s">
+      <c r="D34" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="M33" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13">
-      <c r="A34" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>162</v>
-      </c>
       <c r="G34" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>30</v>
@@ -3075,39 +3059,39 @@
         <v>21</v>
       </c>
       <c r="J34" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="15">
+      <c r="A35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="K34" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L34" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="M34" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13">
-      <c r="A35" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="G35" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>30</v>
@@ -3116,39 +3100,39 @@
         <v>21</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="K35" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="15">
+      <c r="A36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13">
-      <c r="A36" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>170</v>
-      </c>
       <c r="G36" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>20</v>
@@ -3157,19 +3141,19 @@
         <v>21</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="M36" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="37" spans="1:13">
+    <row r="37" spans="1:13" ht="15">
       <c r="A37" s="3" t="s">
         <v>13</v>
       </c>
@@ -3177,19 +3161,19 @@
         <v>14</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>20</v>
@@ -3198,27 +3182,27 @@
         <v>21</v>
       </c>
       <c r="J37" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="M37" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="15">
+      <c r="A38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="K37" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="L37" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="M37" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13">
-      <c r="A38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>179</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>34</v>
@@ -3227,10 +3211,10 @@
         <v>27</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>20</v>
@@ -3239,27 +3223,27 @@
         <v>21</v>
       </c>
       <c r="J38" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="M38" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="15">
+      <c r="A39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="L38" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="M38" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13">
-      <c r="A39" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>184</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>34</v>
@@ -3268,10 +3252,10 @@
         <v>27</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>185</v>
+        <v>75</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>30</v>
@@ -3280,19 +3264,19 @@
         <v>21</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="15">
       <c r="A40" s="3" t="s">
         <v>13</v>
       </c>
@@ -3300,7 +3284,7 @@
         <v>14</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>26</v>
@@ -3309,7 +3293,7 @@
         <v>27</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>29</v>
@@ -3318,22 +3302,22 @@
         <v>30</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="15">
       <c r="A41" s="3" t="s">
         <v>13</v>
       </c>
@@ -3341,16 +3325,16 @@
         <v>14</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>29</v>
@@ -3362,19 +3346,19 @@
         <v>21</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="15">
       <c r="A42" s="3" t="s">
         <v>13</v>
       </c>
@@ -3382,7 +3366,7 @@
         <v>14</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>34</v>
@@ -3391,10 +3375,10 @@
         <v>27</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>20</v>
@@ -3403,19 +3387,19 @@
         <v>21</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="15">
       <c r="A43" s="3" t="s">
         <v>13</v>
       </c>
@@ -3423,7 +3407,7 @@
         <v>14</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>34</v>
@@ -3432,7 +3416,7 @@
         <v>27</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>29</v>
@@ -3444,19 +3428,19 @@
         <v>21</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="15">
       <c r="A44" s="3" t="s">
         <v>13</v>
       </c>
@@ -3464,19 +3448,19 @@
         <v>14</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>185</v>
+        <v>75</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>30</v>
@@ -3485,19 +3469,19 @@
         <v>21</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="15">
       <c r="A45" s="3" t="s">
         <v>13</v>
       </c>
@@ -3505,16 +3489,16 @@
         <v>14</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>29</v>
@@ -3523,22 +3507,22 @@
         <v>30</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="15">
       <c r="A46" s="3" t="s">
         <v>13</v>
       </c>
@@ -3546,16 +3530,16 @@
         <v>14</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>121</v>
+        <v>75</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>29</v>
@@ -3564,22 +3548,22 @@
         <v>30</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="M46" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="47" spans="1:13">
+    <row r="47" spans="1:13" ht="15">
       <c r="A47" s="3" t="s">
         <v>13</v>
       </c>
@@ -3587,40 +3571,40 @@
         <v>14</v>
       </c>
       <c r="C47" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J47" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="L47" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J47" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>216</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="48" spans="1:13">
+    <row r="48" spans="1:13" ht="15">
       <c r="A48" s="3" t="s">
         <v>13</v>
       </c>
@@ -3628,7 +3612,7 @@
         <v>14</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>26</v>
@@ -3637,7 +3621,7 @@
         <v>27</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>29</v>
@@ -3646,22 +3630,22 @@
         <v>30</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="15">
       <c r="A49" s="3" t="s">
         <v>13</v>
       </c>
@@ -3669,40 +3653,40 @@
         <v>14</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="G49" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I49" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="J49" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="15">
       <c r="A50" s="3" t="s">
         <v>13</v>
       </c>
@@ -3710,40 +3694,40 @@
         <v>14</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="G50" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I50" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H50" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="J50" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="M50" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="51" spans="1:13">
+    <row r="51" spans="1:13" ht="15">
       <c r="A51" s="3" t="s">
         <v>13</v>
       </c>
@@ -3751,7 +3735,7 @@
         <v>14</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>26</v>
@@ -3760,7 +3744,7 @@
         <v>27</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>29</v>
@@ -3769,22 +3753,22 @@
         <v>30</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="15">
       <c r="A52" s="3" t="s">
         <v>13</v>
       </c>
@@ -3792,7 +3776,7 @@
         <v>14</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>34</v>
@@ -3801,31 +3785,31 @@
         <v>27</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="53" spans="1:13">
+    <row r="53" spans="1:13" ht="15">
       <c r="A53" s="3" t="s">
         <v>13</v>
       </c>
@@ -3833,7 +3817,7 @@
         <v>14</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>34</v>
@@ -3842,31 +3826,31 @@
         <v>27</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G53" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I53" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H53" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="J53" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="15">
       <c r="A54" s="3" t="s">
         <v>13</v>
       </c>
@@ -3874,19 +3858,19 @@
         <v>14</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>30</v>
@@ -3895,39 +3879,39 @@
         <v>21</v>
       </c>
       <c r="J54" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="15">
+      <c r="A55" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F55" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="M54" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13">
-      <c r="A55" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>245</v>
-      </c>
       <c r="G55" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>30</v>
@@ -3936,39 +3920,39 @@
         <v>21</v>
       </c>
       <c r="J55" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="M55" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="15">
+      <c r="A56" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F56" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="K55" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="L55" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="M55" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13">
-      <c r="A56" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>250</v>
-      </c>
       <c r="G56" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>30</v>
@@ -3977,19 +3961,19 @@
         <v>21</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="15">
       <c r="A57" s="3" t="s">
         <v>13</v>
       </c>
@@ -3997,7 +3981,7 @@
         <v>14</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>34</v>
@@ -4006,31 +3990,31 @@
         <v>17</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="G57" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I57" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="J57" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="15">
       <c r="A58" s="3" t="s">
         <v>13</v>
       </c>
@@ -4038,7 +4022,7 @@
         <v>14</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>26</v>
@@ -4047,7 +4031,7 @@
         <v>27</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>29</v>
@@ -4056,39 +4040,39 @@
         <v>30</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J58" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="60.75">
+      <c r="A59" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F59" s="3" t="s">
         <v>260</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" ht="57.95">
-      <c r="A59" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>264</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>29</v>
@@ -4097,22 +4081,22 @@
         <v>20</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="L59" s="3" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="15">
       <c r="A60" s="3" t="s">
         <v>13</v>
       </c>
@@ -4120,7 +4104,7 @@
         <v>14</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>26</v>
@@ -4129,10 +4113,10 @@
         <v>17</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>30</v>
@@ -4141,60 +4125,60 @@
         <v>21</v>
       </c>
       <c r="J60" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L60" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="M60" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="15">
+      <c r="A61" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F61" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="M60" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13">
-      <c r="A61" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>272</v>
-      </c>
       <c r="G61" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J61" s="6">
         <v>45078</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" ht="15">
       <c r="A62" s="3" t="s">
         <v>13</v>
       </c>
@@ -4202,7 +4186,7 @@
         <v>14</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>16</v>
@@ -4211,10 +4195,10 @@
         <v>17</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>30</v>
@@ -4223,19 +4207,19 @@
         <v>21</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="L62" s="3" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="M62" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="63" spans="1:13">
+    <row r="63" spans="1:13" ht="15">
       <c r="A63" s="3" t="s">
         <v>13</v>
       </c>
@@ -4243,16 +4227,16 @@
         <v>14</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>121</v>
+        <v>75</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>29</v>
@@ -4264,16 +4248,16 @@
         <v>21</v>
       </c>
       <c r="J63" s="9" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="L63" s="3" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="30.75">
@@ -4284,19 +4268,19 @@
         <v>14</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>30</v>
@@ -4305,36 +4289,36 @@
         <v>21</v>
       </c>
       <c r="J64" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="L64" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="M64" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="15">
+      <c r="A65" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F65" s="3" t="s">
         <v>286</v>
-      </c>
-      <c r="K64" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="L64" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="M64" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13">
-      <c r="A65" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>291</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>29</v>
@@ -4343,22 +4327,22 @@
         <v>30</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J65" s="6" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="L65" s="3" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" ht="15">
       <c r="A66" s="3" t="s">
         <v>13</v>
       </c>
@@ -4366,7 +4350,7 @@
         <v>14</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>26</v>
@@ -4375,7 +4359,7 @@
         <v>27</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>29</v>
@@ -4384,22 +4368,22 @@
         <v>30</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="15">
       <c r="A67" s="3" t="s">
         <v>13</v>
       </c>
@@ -4407,7 +4391,7 @@
         <v>14</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>26</v>
@@ -4416,7 +4400,7 @@
         <v>27</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>185</v>
+        <v>292</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>29</v>
@@ -4425,19 +4409,19 @@
         <v>30</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="L67" s="3" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="68" spans="1:13" ht="15">
@@ -4448,7 +4432,7 @@
         <v>14</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>34</v>
@@ -4457,10 +4441,10 @@
         <v>27</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>30</v>
@@ -4469,16 +4453,16 @@
         <v>21</v>
       </c>
       <c r="J68" s="6" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="L68" s="3" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="M68" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="69" spans="1:13" ht="15">
@@ -4489,7 +4473,7 @@
         <v>14</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>34</v>
@@ -4498,28 +4482,28 @@
         <v>27</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="L69" s="3" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="M69" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="30.75">
@@ -4530,19 +4514,19 @@
         <v>14</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>30</v>
@@ -4551,16 +4535,16 @@
         <v>21</v>
       </c>
       <c r="J70" s="6" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="L70" s="3" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="M70" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="71" spans="1:13" ht="24.75" customHeight="1">
@@ -4571,16 +4555,16 @@
         <v>14</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G71" s="3" t="s">
         <v>29</v>
@@ -4592,16 +4576,16 @@
         <v>21</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="K71" s="11" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="L71" s="11" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="M71" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="72" spans="1:13" ht="30.75">
@@ -4612,37 +4596,37 @@
         <v>14</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G72" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I72" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="J72" s="6" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="L72" s="3" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="M72" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="73" spans="1:13" ht="15">
@@ -4653,7 +4637,7 @@
         <v>14</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>26</v>
@@ -4662,7 +4646,7 @@
         <v>27</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>185</v>
+        <v>75</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>29</v>
@@ -4674,16 +4658,16 @@
         <v>21</v>
       </c>
       <c r="J73" s="6" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="L73" s="3" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="M73" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="74" spans="1:13" ht="15">
@@ -4694,34 +4678,34 @@
         <v>14</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H74" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J74" s="6">
         <v>2025</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="L74" s="3" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="M74" s="3" t="s">
         <v>24</v>
@@ -4735,16 +4719,16 @@
         <v>14</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>29</v>
@@ -4753,19 +4737,19 @@
         <v>30</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J75" s="6" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="L75" s="3" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="M75" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="76" spans="1:13" ht="30.75">
@@ -4776,16 +4760,16 @@
         <v>14</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="D76" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>29</v>
@@ -4797,39 +4781,39 @@
         <v>21</v>
       </c>
       <c r="J76" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="K76" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="L76" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="M76" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" ht="30.75">
+      <c r="A77" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F77" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="K76" s="3" t="s">
+      <c r="G77" s="12" t="s">
         <v>332</v>
-      </c>
-      <c r="L76" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="M76" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13" ht="15">
-      <c r="A77" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="E77" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F77" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="G77" s="3" t="s">
-        <v>336</v>
       </c>
       <c r="H77" s="3" t="s">
         <v>30</v>
@@ -4841,10 +4825,10 @@
         <v>45663</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="L77" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="M77" s="3" t="s">
         <v>24</v>
@@ -4858,16 +4842,16 @@
         <v>14</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="D78" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>29</v>
@@ -4876,16 +4860,16 @@
         <v>30</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J78" s="6" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="L78" s="3" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="M78" s="3" t="s">
         <v>24</v>
@@ -4899,37 +4883,37 @@
         <v>14</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H79" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J79" s="6" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="L79" s="3" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="M79" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="80" spans="1:13" ht="30.75">
@@ -4940,37 +4924,37 @@
         <v>14</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="D80" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G80" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I80" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H80" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I80" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="J80" s="6" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="L80" s="3" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="M80" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="81" spans="1:13" ht="30.75">
@@ -4981,37 +4965,37 @@
         <v>14</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="D81" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F81" s="13" t="s">
-        <v>190</v>
+      <c r="F81" s="3" t="s">
+        <v>186</v>
       </c>
       <c r="G81" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I81" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="J81" s="6">
         <v>2025</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="L81" s="3" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="M81" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="82" spans="1:13" ht="15">
@@ -5022,37 +5006,37 @@
         <v>14</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>185</v>
+        <v>75</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H82" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J82" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="L82" s="3" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="M82" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="83" spans="1:13" ht="15">
@@ -5417,7 +5401,7 @@
           <x14:formula1>
             <xm:f>Dominio!$A$1:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>G3:G1048576</xm:sqref>
+          <xm:sqref>G2:G1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E31F6FF8-8A6C-5643-A155-4F7B3EA2A96D}">
           <x14:formula1>
@@ -5453,7 +5437,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="15.6">
       <c r="A1" s="1" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="15.6">
@@ -5463,157 +5447,157 @@
     </row>
     <row r="3" spans="1:1" ht="15.6">
       <c r="A3" s="1" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="15.6">
       <c r="A4" s="1" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="15.6">
       <c r="A5" s="1" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="15.6">
       <c r="A6" s="1" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="15.6">
       <c r="A7" s="1" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="15.6">
       <c r="A8" s="1" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="15.6">
       <c r="A9" s="1" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="15.6">
       <c r="A10" s="1" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="15.6">
       <c r="A11" s="1" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="15.6">
       <c r="A12" s="1" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="15.6">
       <c r="A13" s="1" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="15.6">
       <c r="A14" s="1" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="15.6">
       <c r="A15" s="1" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="15.6">
       <c r="A16" s="1" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="15.6">
       <c r="A17" s="1" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15.6">
       <c r="A18" s="1" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="15.6">
       <c r="A19" s="1" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15.6">
       <c r="A20" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="15.6">
       <c r="A21" s="1" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="15.6">
       <c r="A22" s="1" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="15.6">
       <c r="A23" s="1" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="15.6">
       <c r="A24" s="1" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="15.6">
       <c r="A25" s="1" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="15.6">
       <c r="A26" s="1" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="15.6">
       <c r="A27" s="1" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="15.6">
       <c r="A28" s="1" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="15.6">
       <c r="A29" s="1" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="15.6">
       <c r="A30" s="1" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="15.6">
       <c r="A31" s="1" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="15.6">
       <c r="A32" s="1" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="15.6">
       <c r="A33" s="1" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
     </row>
   </sheetData>
@@ -5634,12 +5618,12 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -5649,22 +5633,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -5674,7 +5658,7 @@
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -5703,7 +5687,7 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
     </row>
   </sheetData>
@@ -5724,22 +5708,22 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>391</v>
+        <v>332</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -5784,17 +5768,17 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -5815,7 +5799,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/data/Matriz_Normativa_IA_Educacion_LATAM.xlsx
+++ b/data/Matriz_Normativa_IA_Educacion_LATAM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30125"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tecmx-my.sharepoint.com/personal/a00834778_tec_mx/Documents/Desktop/Carlos Auquilla/Proyectos/GENIAL/GENIAL_dev/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DEF93B8B-1B75-490B-94A3-E0F7B496BF87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="428" documentId="8_{DEF93B8B-1B75-490B-94A3-E0F7B496BF87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{350EF929-F841-4D67-802D-87771D8B7F4B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1099" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1595" uniqueCount="529">
   <si>
     <t>Investigador</t>
   </si>
@@ -1109,6 +1109,434 @@
     <t>Establece la creación del 'Consejo Coordinador de Inteligencia Artificial' en la UNAM, con el objetivo de potenciar las capacidades institucionales en IA y fortalecer la autonomía tecnológica de la Universidad.</t>
   </si>
   <si>
+    <t>Inteligencia Artificial y la Imaginación Humana: Una Investigación Ética</t>
+  </si>
+  <si>
+    <t>https://www.ipn.mx/assets/files/innovacion/docs/Docencia-politecnica/Docencia-politecnica-24/inteligencia-artificial-y-la-inaginacion-humana.pdf</t>
+  </si>
+  <si>
+    <t>Documento académico no vinculante. Analiza implicaciones éticas de IA generativa en creatividad, formación docente y educación superior. Discute sesgos, propiedad intelectual, dependencia tecnológica y complementariedad humano-IA.</t>
+  </si>
+  <si>
+    <t>Guía de uso de inteligencia artificial generativa en la evaluación educativa en el posgrado</t>
+  </si>
+  <si>
+    <t>https://www.pdcb.unam.mx/documentos/alumnos/guia-de-uso-de-inteligencia-artificial-generativa-en-evaluacion-educativa-en-el-posgrado.pdf?ui=1409252254</t>
+  </si>
+  <si>
+    <t>Documento institucional de referencia para uso ético y pedagógico de IA generativa en evaluación de posgrado. Incluye principios de integridad académica, alfabetización en IA, evaluación híbrida, uso responsable de LLMs, sesgos algorítmicos y lineamientos para docentes y estudiantes. Promueve enfoque humanista y evaluación crítica del uso de IA.</t>
+  </si>
+  <si>
+    <t>Pautas para hacer uso de la Inteligencia Artificial en la Formación Docente Universitaria</t>
+  </si>
+  <si>
+    <t>https://cfop.ceide.unam.mx/wp-content/uploads/2025/06/Conferencia-Pautas-para-hacer-uso-de-la-IA-en-la-formacion-docente-universitaria.pdf</t>
+  </si>
+  <si>
+    <t>Documento presentado en el IV Seminario Internacional Educación y TAC. Incluye pautas institucionales para uso ético de IA, programas de formación docente, microtalleres y adopción transversal de IA generativa en educación superior. Evidencia institucionalización progresiva de IA en la UNAM.</t>
+  </si>
+  <si>
+    <t>Relevancia de la Inteligencia Artificial en la educación</t>
+  </si>
+  <si>
+    <t>https://www.zaragoza.unam.mx/wp-content/2023/Publicaciones/libros/csociales/Relevancia_IA_educacion.pdf</t>
+  </si>
+  <si>
+    <t>Compilación institucional revisada por pares sobre IA en educación. Incluye revisión sistemática sobre LLMs en educación latinoamericana, ética, evaluación, gestión académica y formación profesional. Refleja madurez institucional y adopción formal de IA educativa en UNAM.</t>
+  </si>
+  <si>
+    <t>Políticas de uso de Inteligencia Artificial para trabajos académicos</t>
+  </si>
+  <si>
+    <t>https://www.economia.unam.mx/profesores/eloria/index_htm_files/Uso%20de%20IA.pdf</t>
+  </si>
+  <si>
+    <t>Define usos permitidos y prohibidos de IA generativa en trabajos académicos, incorpora declaración obligatoria de uso IA y mecanismos de sanción. Representa regulación institucional madura de IA académica.</t>
+  </si>
+  <si>
+    <t>La Inteligencia Artificial Generativa (IAGEN) en el profesorado y estudiantado de la UNAM. Retos y prospectivas</t>
+  </si>
+  <si>
+    <t>https://www.ceide.unam.mx/wp-content/uploads/2025/08/IAGen_UNAM_2025.pdf</t>
+  </si>
+  <si>
+    <t>Documento institucional oficial que diagnostica el uso de IA generativa en educación superior UNAM. No establece regulación obligatoria, pero sí orientaciones estratégicas, éticas y pedagógicas. Referencia explícita al proyecto institucional “Desarrollo de la IAGen en la docencia universitaria” del PDI 2023–2027.</t>
+  </si>
+  <si>
+    <t>Derechos digitales y la sexta generación: acceso, privacidad y libertad en el ciberespacio</t>
+  </si>
+  <si>
+    <t>https://www.google.com/url?sa=t&amp;source=web&amp;rct=j&amp;opi=89978449&amp;url=https://revistas.juridicas.unam.mx/index.php/hechos-y-derechos/article/view/19934/19951&amp;ved=2ahUKEwjKp6in-tSUAxV9fTABHSpdFtI4FBAWegQIMBAB&amp;usg=AOvVaw3ajc17fzIwcN8MDw3wACsR</t>
+  </si>
+  <si>
+    <t>Artículo académico-jurídico sobre derechos digitales, privacidad, IA ética y gobernanza del ciberespacio. No constituye normativa vinculante ni política institucional, pero refleja tendencias doctrinales y preocupaciones regulatorias emergentes en México.</t>
+  </si>
+  <si>
+    <t>Recomendaciones sobre el uso de materiales explícitos y/o sensibles en actividades docentes en la ENaCiF</t>
+  </si>
+  <si>
+    <t>https://www.enacif.unam.mx/wp-content/uploads/2025/05/Sintesis-Recomendaciones-sobre-el-uso-de-Materiales-Explicitos-y_o-Sensibles-en-actividades-docentes-en-la-ENaCiF.pdf</t>
+  </si>
+  <si>
+    <t>Documento institucional que regula el manejo ético de materiales sensibles en actividades docentes. Incluye referencia explícita al posible uso de imágenes generadas mediante inteligencia artificial y establece principios de inclusión, consentimiento, privacidad y enfoque informado sobre trauma.</t>
+  </si>
+  <si>
+    <t>Plan de Desarrollo IIMAS-UNAM 2024-2028</t>
+  </si>
+  <si>
+    <t>https://www.iimas.unam.mx/wp-content/uploads/2025/04/Plan-de-Desarrollo-IIMAS-2024_2028-v1.pdf</t>
+  </si>
+  <si>
+    <t>El documento plantea la creación formal de “Principios IIMAS para una IA Ética, Responsable y Sostenible”, incluyendo aprobación institucional, regulación del actuar académico, capacitación docente y uso de IA generativa en educación. Constituye evidencia de gobernanza institucional emergente sobre IA en educación superior.</t>
+  </si>
+  <si>
+    <t>Políticas Educativas: Lecciones del IFE Conference 2024</t>
+  </si>
+  <si>
+    <t>Fecha no disponible: inferida
+por contexto del año 2024</t>
+  </si>
+  <si>
+    <t>https://tec.mx/sites/default/files/repositorio/ife/pdf/politicas-educativas-ife-tec-de-monterrey.pdf?srsltid=AfmBOop0NBuvTlnWsQNr0jjulBXKVddrSclv1GBNCc1pGB9TZUS7Cckj</t>
+  </si>
+  <si>
+    <t>Documento estratégico sobre IA en educación, alfabetización IA, riesgos éticos, desinformación, privacidad y regulación. Referencia marcos UNESCO y tendencias globales de gobernanza educativa.</t>
+  </si>
+  <si>
+    <t>Congreso Internacional de Inteligencia Artificial: potencial, retos y oportunidades para México</t>
+  </si>
+  <si>
+    <t>https://www.ipn.mx/assets/files/imageninstitucional/docs/identidad/2025/05/uso-ia.pdf</t>
+  </si>
+  <si>
+    <t>Documento institucional sobre gobernanza, ética, protección de datos y uso educativo de IA. No constituye regulación vinculante.</t>
+  </si>
+  <si>
+    <t>Uso personal y académico de inteligencia artificial en estudiantes universitarios: estudio exploratorio</t>
+  </si>
+  <si>
+    <t>30/03/2025</t>
+  </si>
+  <si>
+    <t>https://apertura.cugdl.udg.mx/index.php/apertura/article/view/2604</t>
+  </si>
+  <si>
+    <t>Estudio empírico sobre adopción real de IA en educación superior mexicana. Identifica uso masivo de ChatGPT y otras IA, ausencia de acceso institucional formal, necesidad de regulación ética y vacíos de gobernanza universitaria. Útil como evidencia contextual de madurez y barreras de adopción.</t>
+  </si>
+  <si>
+    <t>Inteligencia Artificial Generativa: Enfoques Prácticos para Docentes (Edu Book)</t>
+  </si>
+  <si>
+    <t>https://observatorio.tec.mx/wp-content/uploads/2025/07/EDU-BOOK_IA-GENERATIVA_V6.pdf</t>
+  </si>
+  <si>
+    <t>Edu book realizado para reportar el observatorio realizado por el instituto por el futuro de la educación del Tecnológico de Monterrey. Una herramienta enfocada en la implementación práctica de la IA y sus implicaciones éticas</t>
+  </si>
+  <si>
+    <t>Guía para el Uso Ético y Responsable de la Inteligencia Artificial Generativa en Entornos Digitales para el Aprendizaje</t>
+  </si>
+  <si>
+    <t>Integra el uso de la Inteligencia Artificial con el cóidgio de ética de la institución y sus regulaciones disciplinarias</t>
+  </si>
+  <si>
+    <t>Principios de acción para un uso ético y crítico de la IAG en la educación superior mexicana</t>
+  </si>
+  <si>
+    <t>https://www.gob.mx/cms/uploads/attachment/file/1071410/ENIAG2025_PRINCIPIOS.pdf</t>
+  </si>
+  <si>
+    <t>Define 10 principios como un marco de trabajo para la agenda de Educación Superior y solicita establecer lineamientos institucionales claros para el usoético, crítico y con propóstio dentro de las instituciones.</t>
+  </si>
+  <si>
+    <t>Observatorio Interinstitucional de Inteligencia Artificial en la Educación Superior en México: Documento Fundacional</t>
+  </si>
+  <si>
+    <t>ANUIES, FIMPES, UNAM, UAM, UPN, Santander</t>
+  </si>
+  <si>
+    <t>https://observatorio-ia.org/OIIAES.pdf</t>
+  </si>
+  <si>
+    <t>Marco de trabajo colaborativo interinstitucional para monitorear el impacto de la Inteligencia Artificial y generar una política pública. Su objetivo es monitorear las prácticas de integración de la IA en la educación superior sistematizando y
+evaluando su integración en este nivel educativo</t>
+  </si>
+  <si>
+    <t>México: evaluación del estadío de preparación de la inteligencia artificial</t>
+  </si>
+  <si>
+    <t>https://unesdoc.unesco.org/ark:/48223/pf0000390568</t>
+  </si>
+  <si>
+    <t>Perfil país de UNESCO que funciona como índice del ecosistema de IA en México, no como norma vinculante. Sirve para contextualizar políticas universitarias y ubicar documentos nacionales. Su límite es que resume información y no fija obligaciones legales. Conviene incluirlo solo como fuente contextual.</t>
+  </si>
+  <si>
+    <t>Lineamientos para el uso de herramientas de inteligencia artificial en CETYS Universidad</t>
+  </si>
+  <si>
+    <t>https://www.cetys.mx/wp-content/uploads/2024/04/Comunicado-Vicerrectoria-Academica-IA.pdf</t>
+  </si>
+  <si>
+    <t>Establece pautas para el uso de herramientas de IA en actividades académicas, incluyendo condiciones sobre "propiedad intelectual" y "plagio". Promueve la "alfabetización en IA" como parte de las competencias educativas en CETYS Universidad.</t>
+  </si>
+  <si>
+    <t>Guía en inteligencia artificial: grupo de trabajo de alfabetización en IA</t>
+  </si>
+  <si>
+    <t>Establece un marco para la 'alfabetización en inteligencia artificial' en CETYS Universidad, sugiriendo elementos básicos de conocimiento y terminología. Se deriva de los 'Lineamientos para el uso de herramientas de inteligencia artificial' emitidos en octubre de 2023.</t>
+  </si>
+  <si>
+    <t>Maestría en Audio y la Industria del Entretenimiento Digital con Certificación en Negocios del Entretenimiento</t>
+  </si>
+  <si>
+    <t>Fermatta</t>
+  </si>
+  <si>
+    <t>https://www.fermatta.edu.mx/planes-educativos-mae/maestr%C3%ADa-en-audio-y-la-industria-del-entretenimiento-digital-con-certificaci%C3%B3n-en-negocios-del-entretenimiento</t>
+  </si>
+  <si>
+    <t>Establece un programa académico que incluye 'Herramientas de Inteligencia Artificial para la Creación de Música' en varios semestres. Promueve el uso de tecnología avanzada en la producción musical, integrando IA como parte fundamental de la formación profesional en la industria del entretenimiento.</t>
+  </si>
+  <si>
+    <t>Diseño de materiales digitales</t>
+  </si>
+  <si>
+    <t>Secretaría de Educación Pública</t>
+  </si>
+  <si>
+    <t>01/01/2023</t>
+  </si>
+  <si>
+    <t>http://www.sev.gob.mx/educacion-normal/curricular/wp-content/uploads/sites/14/2026/03/ENJE_LEP_6o_Diseno-de-materiales-Digitales.pdf</t>
+  </si>
+  <si>
+    <t>Establece el desarrollo de habilidades para diseñar materiales digitales educativos e incorpora la formación en el uso pedagógico, crítico y ético de herramientas basadas en 'inteligencia artificial'. Este curso busca preparar a los futuros educadores para crear recursos inclusivos y accesibles en entornos preescolares.</t>
+  </si>
+  <si>
+    <t>Maestría en Audio y la Industria del Entretenimiento Digital con Certificación en Mezcla</t>
+  </si>
+  <si>
+    <t>Centro Universitario de Música Fermatta</t>
+  </si>
+  <si>
+    <t>https://www.fermatta.edu.mx/planes-educativos-mae/maestr%C3%ADa-en-audio-y-la-industria-del-entretenimiento-digital-con-certificaci%C3%B3n-en-mezcla</t>
+  </si>
+  <si>
+    <t>Establece un programa académico que incluye 'Herramientas de Inteligencia Artificial para la Creación de Música' en varios semestres. Proporciona formación en técnicas de mezcla y producción musical, integrando aplicaciones avanzadas de IA en la educación musical.</t>
+  </si>
+  <si>
+    <t>Ley General de Humanidades, Ciencia, Tecnología e Innovación</t>
+  </si>
+  <si>
+    <t>Gobierno de México</t>
+  </si>
+  <si>
+    <t>https://sipot.ciateq.mx/planeacion/29%20XXIX%20INFORMES/Informe_In_Extenso_2023_ene_jun.pdf.pdf</t>
+  </si>
+  <si>
+    <t>Establece la evaluación de la gestión en el marco del Programa Institucional y menciona la 'evaluación de su gestión' como parte de las nuevas disposiciones. Aunque no se centra en IA, su aplicación puede influir en la regulación de tecnologías emergentes en el ámbito educativo.</t>
+  </si>
+  <si>
+    <t>Código de Ética e Integridad para un Buen Gobierno en la Administración Pública Federal</t>
+  </si>
+  <si>
+    <t>Secretaría Anticorrupción y Buen Gobierno</t>
+  </si>
+  <si>
+    <t>18/11/2025</t>
+  </si>
+  <si>
+    <t>https://www.cibnor.gob.mx/files/admon/DOF_CODIGO_ETICA_APF_2025.pdf</t>
+  </si>
+  <si>
+    <t>Establece principios de 'ética e integridad' para la administración pública. Aunque no menciona IA directamente, su enfoque en la ética es relevante para la gobernanza de tecnologías emergentes en el sector educativo.</t>
+  </si>
+  <si>
+    <t>Ley General en Materia de Humanidades, Ciencias, Tecnologías e Innovación</t>
+  </si>
+  <si>
+    <t>CIATEC, A.C., CENTRO DE INNOVACIÓN APLICADA EN TECNOLOGÍAS COMPETITIVAS</t>
+  </si>
+  <si>
+    <t>Mención breve</t>
+  </si>
+  <si>
+    <t>08/05/2023</t>
+  </si>
+  <si>
+    <t>https://www.ciatec.mx/archivos/98bafc961336f547dcd60e17270c6c5b.pdf</t>
+  </si>
+  <si>
+    <t>Establece un marco normativo para la promoción de 'Ciencias, Tecnologías e Innovación', incluyendo aspectos relacionados con la inteligencia artificial. Aunque no se centra exclusivamente en IA, su relevancia para la gobernanza de tecnologías emergentes es significativa.</t>
+  </si>
+  <si>
+    <t>Lineamientos Complementarios para la Maestría en Ciencias con Orientación en Robótica</t>
+  </si>
+  <si>
+    <t>Centro de Investigación en Matemáticas, A. C. (Cimat)</t>
+  </si>
+  <si>
+    <t>https://mcr.cimat.mx/es/Lineamientos_MCR</t>
+  </si>
+  <si>
+    <t>Regula el funcionamiento de la Maestría en Ciencias con Orientación en Robótica, incluyendo la formación en 'inteligencia artificial' y su interacción con la robótica. Establece lineamientos para la calidad académica y la estructura del programa de posgrado.</t>
+  </si>
+  <si>
+    <t>SIP-30</t>
+  </si>
+  <si>
+    <t>01/01/2021</t>
+  </si>
+  <si>
+    <t>https://www.cic.ipn.mx/doc/MCyTIAyCD/5-Opt-IA-explicativa-interpretable.pdf</t>
+  </si>
+  <si>
+    <t>Establece los lineamientos para la unidad de aprendizaje 'Inteligencia Artificial Explicativa e Interpretable', incluyendo objetivos de aprendizaje y competencias específicas en el ámbito de la IA. Define la estructura curricular y los requisitos para la maestría en Ciencia y Tecnología de Inteligencia Artificial y Ciencia de Datos.</t>
+  </si>
+  <si>
+    <t>Inteligencia Artificial Explicable</t>
+  </si>
+  <si>
+    <t>26/07/2023</t>
+  </si>
+  <si>
+    <t>https://www.cic.ipn.mx/doc/DCC/15.%20Inteligencia-Artificial-Explicable-Registrada.pdf</t>
+  </si>
+  <si>
+    <t>Establece lineamientos para la unidad de aprendizaje 'Inteligencia Artificial Explicable', incluyendo conceptos de 'transparencia' y 'explicabilidad' en IA. Define aprendizajes y habilidades que los estudiantes deben demostrar, promoviendo la responsabilidad y la ética en el uso de IA.</t>
+  </si>
+  <si>
+    <t>Política de uso de IA</t>
+  </si>
+  <si>
+    <t>CIATEJ</t>
+  </si>
+  <si>
+    <t>https://revistaenfoques.ciatej.mx/index.php/revistaenfoques/politica_uso_de_IA</t>
+  </si>
+  <si>
+    <t>Establece directrices para el 'uso de inteligencia artificial' en el contexto institucional. Define el empleo de herramientas digitales basadas en modelos generativos, orientando su aplicación en la educación superior.</t>
+  </si>
+  <si>
+    <t>Programa de Trabajo - CIATEC</t>
+  </si>
+  <si>
+    <t>CIATEC</t>
+  </si>
+  <si>
+    <t>https://www.ciatec.mx/archivos/fbbd14366497df3a41a3023121745292.pdf</t>
+  </si>
+  <si>
+    <t>Establece un programa de trabajo que incluye la 'inteligencia artificial' como parte de las especialidades en el posgrado, promoviendo la formación de recursos humanos con capacidad de respuesta a necesidades sociales e industriales. Se enfoca en la vinculación con sectores educativos y tecnológicos para democratizar el conocimiento.</t>
+  </si>
+  <si>
+    <t>PLAN DE TRABAJO - CIATEC</t>
+  </si>
+  <si>
+    <t>https://www.ciatec.mx/archivos/04ae246e577be2fd8cd2b915aba3c9c3.pdf</t>
+  </si>
+  <si>
+    <t>Impulsa la 'investigación y desarrollo tecnológico' en áreas como 'inteligencia artificial' y 'robótica'. Establece colaboración con empresas e instituciones para fomentar políticas que protejan el medio ambiente y promuevan la sostenibilidad.</t>
+  </si>
+  <si>
+    <t>7.1.7 Coordinación de Datos y Analítica</t>
+  </si>
+  <si>
+    <t>Dirección de Innovación y Desarrollo Tecnológico</t>
+  </si>
+  <si>
+    <t>https://reposipot.imss.gob.mx/organizacion/UP/CNMEMPRH/CTOMP/2025/F_III_Atribuciones-Funciones/NC/9_DIDT/7.1.7%20Coord.%20de%20Datos%20y%20Analitica_DIDT.pdf</t>
+  </si>
+  <si>
+    <t>Coordina la implementación de 'políticas, lineamientos y criterios' en materia de 'inteligencia artificial' y 'analítica de datos'. Establece procedimientos para la transferencia de conocimientos y supervisa el diseño de herramientas tecnológicas relacionadas con la IA.</t>
+  </si>
+  <si>
+    <t>Declaración sobre Inteligencia Artificial</t>
+  </si>
+  <si>
+    <t>Revista Médica del IMSS</t>
+  </si>
+  <si>
+    <t>https://revistamedica.imss.gob.mx/index.php/revista_medica/IA</t>
+  </si>
+  <si>
+    <t>Establece criterios editoriales para el uso responsable de IA en el ámbito biomédico, incluyendo 'transparencia', 'responsabilidad humana' y 'protección de datos'. Regula el uso de herramientas de IA en la elaboración y revisión de manuscritos, enfatizando la supervisión humana y la confidencialidad.</t>
+  </si>
+  <si>
+    <t>Uso de la Inteligencia Artificial para disminuir los costos</t>
+  </si>
+  <si>
+    <t>Colegio de Contadores Públicos de Guadalajara Jalisco</t>
+  </si>
+  <si>
+    <t>01/06/2024</t>
+  </si>
+  <si>
+    <t>https://ccpg.org.mx/wp-content/uploads/2024/06/Vision_contable_mayo_2024.pdf</t>
+  </si>
+  <si>
+    <t>Establece directrices sobre el 'Uso de la Inteligencia Artificial para disminuir los costos' en el ámbito contable. Proporciona un enfoque técnico que puede influir en la implementación de IA en procesos educativos y administrativos.</t>
+  </si>
+  <si>
+    <t>Política de supervisión ética</t>
+  </si>
+  <si>
+    <t>El Colegio de la Frontera Norte</t>
+  </si>
+  <si>
+    <t>https://ojs.colef.mx/index.php/fronteranorte/politica_de_supervision_etica</t>
+  </si>
+  <si>
+    <t>Regula el uso de herramientas de inteligencia artificial bajo los 'lineamientos establecidos por la Secretaría de Ciencia, Humanidades, Tecnología'. Establece principios éticos para su implementación en el ámbito educativo.</t>
+  </si>
+  <si>
+    <t>4º CONCURSO DE CREATIVIDAD DIGITAL 2026</t>
+  </si>
+  <si>
+    <t>Colegio Alemán</t>
+  </si>
+  <si>
+    <t>01/01/2026</t>
+  </si>
+  <si>
+    <t>https://humboldt.edu.mx/creatividad-digital/wp-content/uploads/2026/01/Convocatoria-4-Concurso-de-Creatividad-Digital-Primaria.pdf</t>
+  </si>
+  <si>
+    <t>Establece lineamientos para la participación en un concurso de creatividad digital, prohibiendo el 'uso de inteligencia artificial' y plantillas prediseñadas en los proyectos. Promueve la originalidad y la asesoría docente en la creación de productos multimedia.</t>
+  </si>
+  <si>
+    <t>Plan de Acción_G3.14_Anexo_Entregar</t>
+  </si>
+  <si>
+    <t>https://soporte.enesmorelia.unam.mx/respuesta-pliegos-petitorios/doc/3/3.14_Anexo.pdf</t>
+  </si>
+  <si>
+    <t>Establece la oferta de cursos relacionados con 'ética e inteligencia artificial' y 'herramientas de Inteligencia Artificial para Docentes'. Refleja un interés institucional por integrar la IA en la formación docente y la práctica educativa.</t>
+  </si>
+  <si>
+    <t>Política de uso IA</t>
+  </si>
+  <si>
+    <t>Frontera Norte</t>
+  </si>
+  <si>
+    <t>https://fronteranorte.colef.mx/index.php/fronteranorte/politica_de_IA</t>
+  </si>
+  <si>
+    <t>Exige 'transparencia total' en el uso de herramientas de inteligencia artificial durante la elaboración de manuscritos. Establece principios éticos para el uso de IA en el contexto académico.</t>
+  </si>
+  <si>
+    <t>Maestría: Asuntos Políticos y Políticas Públicas</t>
+  </si>
+  <si>
+    <t>Colegio de San Luis</t>
+  </si>
+  <si>
+    <t>https://www.colsan.edu.mx/arch/mappp/MAPPP-10a_2026-28.pdf</t>
+  </si>
+  <si>
+    <t>Prohíbe el uso de 'Inteligencia Artificial generativa' en la elaboración de anteproyectos. Establece lineamientos para la admisión a la maestría en asuntos políticos y políticas públicas, incluyendo la detección de plagio.</t>
+  </si>
+  <si>
     <t>Brasil</t>
   </si>
   <si>
@@ -1209,9 +1637,6 @@
   </si>
   <si>
     <t>Derrogada</t>
-  </si>
-  <si>
-    <t>Mención breve</t>
   </si>
 </sst>
 </file>
@@ -1222,7 +1647,7 @@
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
     <numFmt numFmtId="165" formatCode="dd\.mm\.yyyy;@"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1255,6 +1680,14 @@
     <font>
       <sz val="10"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1321,10 +1754,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1356,8 +1790,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1658,7 +2098,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M106"/>
+  <dimension ref="A1:M135"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="16.140625" customWidth="1"/>
@@ -4629,14 +5069,14 @@
         <v>43</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="15">
+    <row r="73" spans="1:13" ht="30.75">
       <c r="A73" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="C73" s="12" t="s">
         <v>315</v>
       </c>
       <c r="D73" s="3" t="s">
@@ -5039,343 +5479,1846 @@
         <v>43</v>
       </c>
     </row>
-    <row r="83" spans="1:13" ht="15">
-      <c r="A83" s="3"/>
-      <c r="B83" s="3"/>
-      <c r="C83" s="3"/>
-      <c r="D83" s="3"/>
-      <c r="E83" s="3"/>
-      <c r="F83" s="3"/>
-      <c r="G83" s="3"/>
-      <c r="I83" s="3"/>
-      <c r="J83" s="6"/>
-      <c r="K83" s="3"/>
-      <c r="L83" s="3"/>
-      <c r="M83" s="3"/>
-    </row>
-    <row r="84" spans="1:13" ht="15">
-      <c r="A84" s="3"/>
-      <c r="B84" s="3"/>
-      <c r="C84" s="3"/>
-      <c r="D84" s="3"/>
-      <c r="E84" s="3"/>
-      <c r="F84" s="3"/>
-      <c r="G84" s="3"/>
-      <c r="H84" s="3"/>
-      <c r="I84" s="3"/>
-      <c r="J84" s="6"/>
-      <c r="K84" s="3"/>
-      <c r="L84" s="3"/>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="1:13" ht="15">
-      <c r="A85" s="3"/>
-      <c r="B85" s="3"/>
-      <c r="C85" s="3"/>
-      <c r="D85" s="3"/>
-      <c r="E85" s="3"/>
-      <c r="F85" s="3"/>
-      <c r="G85" s="3"/>
-      <c r="H85" s="3"/>
-      <c r="I85" s="3"/>
-      <c r="J85" s="6"/>
-      <c r="K85" s="3"/>
-      <c r="L85" s="3"/>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="1:13" ht="15">
-      <c r="A86" s="3"/>
-      <c r="B86" s="3"/>
-      <c r="C86" s="3"/>
-      <c r="D86" s="3"/>
-      <c r="E86" s="3"/>
-      <c r="F86" s="3"/>
-      <c r="G86" s="3"/>
-      <c r="H86" s="3"/>
-      <c r="I86" s="3"/>
-      <c r="J86" s="6"/>
-      <c r="K86" s="3"/>
-      <c r="L86" s="3"/>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="1:13" ht="15">
-      <c r="A87" s="3"/>
-      <c r="B87" s="3"/>
-      <c r="C87" s="3"/>
-      <c r="D87" s="3"/>
-      <c r="E87" s="3"/>
-      <c r="F87" s="3"/>
-      <c r="G87" s="3"/>
-      <c r="H87" s="3"/>
-      <c r="I87" s="3"/>
-      <c r="J87" s="6"/>
-      <c r="K87" s="3"/>
-      <c r="L87" s="3"/>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="1:13" ht="15">
-      <c r="A88" s="3"/>
-      <c r="B88" s="3"/>
-      <c r="C88" s="3"/>
-      <c r="D88" s="3"/>
-      <c r="E88" s="3"/>
-      <c r="F88" s="3"/>
-      <c r="G88" s="3"/>
-      <c r="H88" s="3"/>
-      <c r="I88" s="3"/>
-      <c r="J88" s="6"/>
-      <c r="K88" s="3"/>
-      <c r="L88" s="3"/>
-      <c r="M88" s="3"/>
-    </row>
-    <row r="89" spans="1:13" ht="15">
-      <c r="A89" s="3"/>
-      <c r="B89" s="3"/>
-      <c r="C89" s="3"/>
-      <c r="D89" s="3"/>
-      <c r="E89" s="3"/>
-      <c r="F89" s="3"/>
-      <c r="G89" s="3"/>
-      <c r="H89" s="3"/>
-      <c r="I89" s="3"/>
-      <c r="J89" s="6"/>
-      <c r="K89" s="3"/>
-      <c r="L89" s="3"/>
-      <c r="M89" s="3"/>
-    </row>
-    <row r="90" spans="1:13" ht="15">
-      <c r="A90" s="3"/>
-      <c r="B90" s="3"/>
-      <c r="C90" s="3"/>
-      <c r="D90" s="3"/>
-      <c r="E90" s="3"/>
-      <c r="F90" s="3"/>
-      <c r="G90" s="3"/>
-      <c r="H90" s="3"/>
-      <c r="I90" s="3"/>
-      <c r="J90" s="6"/>
-      <c r="K90" s="3"/>
-      <c r="L90" s="3"/>
-      <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="1:13" ht="15">
-      <c r="A91" s="3"/>
-      <c r="B91" s="3"/>
-      <c r="C91" s="3"/>
-      <c r="D91" s="3"/>
-      <c r="E91" s="3"/>
-      <c r="F91" s="3"/>
-      <c r="G91" s="3"/>
-      <c r="H91" s="3"/>
-      <c r="I91" s="3"/>
-      <c r="J91" s="6"/>
-      <c r="K91" s="3"/>
-      <c r="L91" s="3"/>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="1:13" ht="15">
-      <c r="A92" s="3"/>
-      <c r="B92" s="3"/>
-      <c r="C92" s="3"/>
-      <c r="D92" s="3"/>
-      <c r="E92" s="3"/>
-      <c r="F92" s="3"/>
-      <c r="G92" s="3"/>
-      <c r="H92" s="3"/>
-      <c r="I92" s="3"/>
-      <c r="J92" s="6"/>
-      <c r="K92" s="3"/>
-      <c r="L92" s="3"/>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="1:13" ht="15">
-      <c r="A93" s="3"/>
-      <c r="B93" s="3"/>
-      <c r="C93" s="3"/>
-      <c r="D93" s="3"/>
-      <c r="E93" s="3"/>
-      <c r="F93" s="3"/>
-      <c r="G93" s="3"/>
-      <c r="H93" s="3"/>
-      <c r="I93" s="3"/>
-      <c r="J93" s="6"/>
-      <c r="K93" s="3"/>
-      <c r="L93" s="3"/>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="1:13" ht="15">
-      <c r="A94" s="3"/>
-      <c r="B94" s="3"/>
-      <c r="C94" s="3"/>
-      <c r="D94" s="3"/>
-      <c r="E94" s="3"/>
-      <c r="F94" s="3"/>
-      <c r="G94" s="3"/>
-      <c r="H94" s="3"/>
-      <c r="I94" s="3"/>
-      <c r="J94" s="6"/>
-      <c r="K94" s="3"/>
-      <c r="L94" s="3"/>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="1:13" ht="15">
-      <c r="A95" s="3"/>
-      <c r="B95" s="3"/>
-      <c r="C95" s="3"/>
-      <c r="D95" s="3"/>
-      <c r="E95" s="3"/>
-      <c r="F95" s="3"/>
-      <c r="G95" s="3"/>
-      <c r="H95" s="3"/>
-      <c r="I95" s="3"/>
-      <c r="J95" s="6"/>
-      <c r="K95" s="3"/>
-      <c r="L95" s="3"/>
-      <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="1:13" ht="15">
-      <c r="A96" s="3"/>
-      <c r="B96" s="3"/>
-      <c r="C96" s="3"/>
-      <c r="D96" s="3"/>
-      <c r="E96" s="3"/>
-      <c r="F96" s="3"/>
-      <c r="G96" s="3"/>
-      <c r="H96" s="3"/>
-      <c r="I96" s="3"/>
-      <c r="J96" s="6"/>
-      <c r="K96" s="3"/>
-      <c r="L96" s="3"/>
-      <c r="M96" s="3"/>
-    </row>
-    <row r="97" spans="1:13" ht="15">
-      <c r="A97" s="3"/>
-      <c r="B97" s="3"/>
-      <c r="C97" s="3"/>
-      <c r="D97" s="3"/>
-      <c r="E97" s="3"/>
-      <c r="F97" s="3"/>
-      <c r="G97" s="3"/>
-      <c r="H97" s="3"/>
-      <c r="I97" s="3"/>
-      <c r="J97" s="6"/>
-      <c r="K97" s="3"/>
-      <c r="L97" s="3"/>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" spans="1:13" ht="15">
-      <c r="A98" s="3"/>
-      <c r="B98" s="3"/>
-      <c r="C98" s="3"/>
-      <c r="D98" s="3"/>
-      <c r="E98" s="3"/>
-      <c r="F98" s="3"/>
-      <c r="G98" s="3"/>
-      <c r="H98" s="3"/>
-      <c r="I98" s="3"/>
-      <c r="J98" s="6"/>
-      <c r="K98" s="3"/>
-      <c r="L98" s="3"/>
-      <c r="M98" s="3"/>
-    </row>
-    <row r="99" spans="1:13" ht="15">
-      <c r="A99" s="3"/>
-      <c r="B99" s="3"/>
-      <c r="C99" s="3"/>
-      <c r="D99" s="3"/>
-      <c r="E99" s="3"/>
-      <c r="F99" s="3"/>
-      <c r="G99" s="3"/>
-      <c r="H99" s="3"/>
-      <c r="I99" s="3"/>
-      <c r="J99" s="6"/>
-      <c r="K99" s="3"/>
-      <c r="L99" s="3"/>
-      <c r="M99" s="3"/>
-    </row>
-    <row r="100" spans="1:13" ht="15">
-      <c r="A100" s="3"/>
-      <c r="B100" s="3"/>
-      <c r="C100" s="3"/>
-      <c r="D100" s="3"/>
-      <c r="E100" s="3"/>
-      <c r="F100" s="3"/>
-      <c r="G100" s="3"/>
-      <c r="H100" s="3"/>
-      <c r="I100" s="3"/>
-      <c r="J100" s="6"/>
-      <c r="K100" s="3"/>
-      <c r="L100" s="3"/>
-      <c r="M100" s="3"/>
-    </row>
-    <row r="101" spans="1:13" ht="15">
-      <c r="A101" s="3"/>
-      <c r="B101" s="3"/>
-      <c r="C101" s="3"/>
-      <c r="D101" s="3"/>
-      <c r="E101" s="3"/>
-      <c r="F101" s="3"/>
-      <c r="G101" s="3"/>
-      <c r="H101" s="3"/>
-      <c r="I101" s="3"/>
-      <c r="J101" s="6"/>
-      <c r="K101" s="3"/>
-      <c r="L101" s="3"/>
-      <c r="M101" s="3"/>
-    </row>
-    <row r="102" spans="1:13" ht="15">
-      <c r="A102" s="3"/>
-      <c r="B102" s="3"/>
-      <c r="C102" s="3"/>
-      <c r="D102" s="3"/>
-      <c r="E102" s="3"/>
-      <c r="F102" s="3"/>
-      <c r="G102" s="3"/>
-      <c r="H102" s="3"/>
-      <c r="I102" s="3"/>
-      <c r="J102" s="6"/>
-      <c r="K102" s="3"/>
-      <c r="L102" s="3"/>
-      <c r="M102" s="3"/>
+    <row r="83" spans="1:13" ht="167.25">
+      <c r="A83" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C83" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H83" t="s">
+        <v>30</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J83" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="K83" s="13" t="s">
+        <v>354</v>
+      </c>
+      <c r="L83" s="11" t="s">
+        <v>355</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" ht="213">
+      <c r="A84" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C84" s="12" t="s">
+        <v>356</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J84" s="6">
+        <v>46113</v>
+      </c>
+      <c r="K84" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="L84" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="M84" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" ht="167.25">
+      <c r="A85" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="D85" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J85" s="6">
+        <v>45576</v>
+      </c>
+      <c r="K85" s="13" t="s">
+        <v>360</v>
+      </c>
+      <c r="L85" s="11" t="s">
+        <v>361</v>
+      </c>
+      <c r="M85" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" ht="183">
+      <c r="A86" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C86" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J86" s="6">
+        <v>46113</v>
+      </c>
+      <c r="K86" s="13" t="s">
+        <v>363</v>
+      </c>
+      <c r="L86" s="11" t="s">
+        <v>364</v>
+      </c>
+      <c r="M86" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" ht="137.25">
+      <c r="A87" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C87" s="11" t="s">
+        <v>365</v>
+      </c>
+      <c r="D87" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J87" s="6">
+        <v>46043</v>
+      </c>
+      <c r="K87" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="L87" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="M87" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" ht="198">
+      <c r="A88" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C88" s="11" t="s">
+        <v>368</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J88" s="6">
+        <v>45870</v>
+      </c>
+      <c r="K88" s="13" t="s">
+        <v>369</v>
+      </c>
+      <c r="L88" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="M88" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" ht="152.25">
+      <c r="A89" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C89" s="11" t="s">
+        <v>371</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J89" s="6">
+        <v>45689</v>
+      </c>
+      <c r="K89" s="13" t="s">
+        <v>372</v>
+      </c>
+      <c r="L89" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" ht="183">
+      <c r="A90" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C90" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="D90" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J90" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="K90" s="13" t="s">
+        <v>375</v>
+      </c>
+      <c r="L90" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="M90" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" ht="213">
+      <c r="A91" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="D91" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J91" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="K91" s="13" t="s">
+        <v>378</v>
+      </c>
+      <c r="L91" s="11" t="s">
+        <v>379</v>
+      </c>
+      <c r="M91" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" ht="121.5">
+      <c r="A92" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C92" s="11" t="s">
+        <v>380</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J92" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="K92" s="13" t="s">
+        <v>382</v>
+      </c>
+      <c r="L92" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="M92" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" ht="91.5">
+      <c r="A93" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C93" s="11" t="s">
+        <v>384</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I93" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J93" s="6">
+        <v>45748</v>
+      </c>
+      <c r="K93" s="13" t="s">
+        <v>385</v>
+      </c>
+      <c r="L93" s="11" t="s">
+        <v>386</v>
+      </c>
+      <c r="M93" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" ht="198">
+      <c r="A94" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C94" s="11" t="s">
+        <v>387</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J94" t="s">
+        <v>388</v>
+      </c>
+      <c r="K94" s="13" t="s">
+        <v>389</v>
+      </c>
+      <c r="L94" s="11" t="s">
+        <v>390</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" ht="137.25">
+      <c r="A95" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C95" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I95" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J95" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="K95" s="13" t="s">
+        <v>392</v>
+      </c>
+      <c r="L95" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="M95" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" ht="76.5">
+      <c r="A96" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C96" s="11" t="s">
+        <v>394</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J96" s="14">
+        <v>45663</v>
+      </c>
+      <c r="K96" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="L96" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" ht="121.5">
+      <c r="A97" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C97" s="11" t="s">
+        <v>396</v>
+      </c>
+      <c r="D97" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J97" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="K97" s="13" t="s">
+        <v>397</v>
+      </c>
+      <c r="L97" s="12" t="s">
+        <v>398</v>
+      </c>
+      <c r="M97" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" ht="183">
+      <c r="A98" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C98" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="D98" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F98" t="s">
+        <v>400</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J98" s="14">
+        <v>45660</v>
+      </c>
+      <c r="K98" s="13" t="s">
+        <v>401</v>
+      </c>
+      <c r="L98" s="12" t="s">
+        <v>402</v>
+      </c>
+      <c r="M98" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" ht="183">
+      <c r="A99" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C99" s="11" t="s">
+        <v>403</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J99" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="K99" s="13" t="s">
+        <v>404</v>
+      </c>
+      <c r="L99" s="11" t="s">
+        <v>405</v>
+      </c>
+      <c r="M99" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" ht="152.25">
+      <c r="A100" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C100" s="12" t="s">
+        <v>406</v>
+      </c>
+      <c r="D100" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H100" t="s">
+        <v>30</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J100" s="6">
+        <v>45200</v>
+      </c>
+      <c r="K100" s="13" t="s">
+        <v>407</v>
+      </c>
+      <c r="L100" s="12" t="s">
+        <v>408</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" ht="121.5">
+      <c r="A101" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C101" s="15" t="s">
+        <v>409</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J101" s="6">
+        <v>45292</v>
+      </c>
+      <c r="K101" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="L101" s="15" t="s">
+        <v>410</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" ht="30.75">
+      <c r="A102" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="D102" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J102" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="K102" s="13" t="s">
+        <v>413</v>
+      </c>
+      <c r="L102" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="103" spans="1:13" ht="15">
-      <c r="A103" s="3"/>
-      <c r="B103" s="3"/>
-      <c r="C103" s="3"/>
-      <c r="D103" s="3"/>
-      <c r="E103" s="3"/>
-      <c r="F103" s="3"/>
-      <c r="G103" s="3"/>
-      <c r="H103" s="3"/>
-      <c r="I103" s="3"/>
-      <c r="J103" s="6"/>
-      <c r="K103" s="3"/>
-      <c r="L103" s="3"/>
-      <c r="M103" s="3"/>
-    </row>
-    <row r="104" spans="1:13" ht="15">
-      <c r="A104" s="3"/>
-      <c r="B104" s="3"/>
-      <c r="C104" s="3"/>
-      <c r="D104" s="3"/>
-      <c r="E104" s="3"/>
-      <c r="F104" s="3"/>
-      <c r="G104" s="3"/>
-      <c r="H104" s="3"/>
-      <c r="I104" s="3"/>
-      <c r="J104" s="6"/>
-      <c r="K104" s="3"/>
-      <c r="L104" s="3"/>
-      <c r="M104" s="3"/>
-    </row>
-    <row r="105" spans="1:13" ht="15"/>
-    <row r="106" spans="1:13" ht="15"/>
+      <c r="A103" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H103" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I103" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J103" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="K103" s="13" t="s">
+        <v>418</v>
+      </c>
+      <c r="L103" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="M103" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" ht="30.75">
+      <c r="A104" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="D104" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H104" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I104" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J104" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="K104" s="13" t="s">
+        <v>422</v>
+      </c>
+      <c r="L104" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="M104" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" ht="15">
+      <c r="A105" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="G105" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H105" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I105" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J105" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="K105" s="13" t="s">
+        <v>426</v>
+      </c>
+      <c r="L105" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="M105" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" ht="15">
+      <c r="A106" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H106" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I106" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J106" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="K106" s="13" t="s">
+        <v>431</v>
+      </c>
+      <c r="L106" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="M106" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" ht="15">
+      <c r="A107" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F107" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="G107" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H107" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I107" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="J107" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="K107" s="13" t="s">
+        <v>437</v>
+      </c>
+      <c r="L107" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="M107" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" ht="30.75">
+      <c r="A108" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="D108" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H108" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I108" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J108" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="K108" s="13" t="s">
+        <v>441</v>
+      </c>
+      <c r="L108" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="M108" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" ht="30.75">
+      <c r="A109" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="D109" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="G109" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H109" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I109" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J109" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="K109" s="13" t="s">
+        <v>445</v>
+      </c>
+      <c r="L109" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="M109" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" ht="30.75">
+      <c r="A110" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="D110" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H110" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I110" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J110" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="K110" s="13" t="s">
+        <v>449</v>
+      </c>
+      <c r="L110" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="M110" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" ht="15">
+      <c r="A111" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H111" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I111" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J111" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="K111" s="13" t="s">
+        <v>453</v>
+      </c>
+      <c r="L111" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="M111" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" ht="30.75">
+      <c r="A112" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="D112" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H112" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I112" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J112" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="K112" s="13" t="s">
+        <v>457</v>
+      </c>
+      <c r="L112" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="M112" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" ht="30.75">
+      <c r="A113" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D113" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H113" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I113" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J113" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="K113" s="13" t="s">
+        <v>460</v>
+      </c>
+      <c r="L113" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="M113" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" ht="30.75">
+      <c r="A114" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="D114" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H114" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I114" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J114" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="K114" s="13" t="s">
+        <v>464</v>
+      </c>
+      <c r="L114" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="M114" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" ht="15">
+      <c r="A115" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H115" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I115" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J115" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="K115" s="13" t="s">
+        <v>468</v>
+      </c>
+      <c r="L115" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="M115" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" ht="15">
+      <c r="A116" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H116" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I116" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J116" s="6" t="s">
+        <v>472</v>
+      </c>
+      <c r="K116" s="13" t="s">
+        <v>473</v>
+      </c>
+      <c r="L116" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="M116" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" ht="30.75">
+      <c r="A117" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="D117" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H117" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I117" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="J117" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="K117" s="13" t="s">
+        <v>477</v>
+      </c>
+      <c r="L117" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="M117" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" ht="30.75">
+      <c r="A118" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="D118" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="G118" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H118" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I118" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J118" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="K118" s="13" t="s">
+        <v>482</v>
+      </c>
+      <c r="L118" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="M118" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" ht="30.75">
+      <c r="A119" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="D119" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F119" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H119" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I119" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J119" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="K119" s="13" t="s">
+        <v>485</v>
+      </c>
+      <c r="L119" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="M119" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" ht="30.75">
+      <c r="A120" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="D120" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="G120" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H120" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I120" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="J120" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="K120" s="13" t="s">
+        <v>489</v>
+      </c>
+      <c r="L120" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="M120" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" ht="15">
+      <c r="A121" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F121" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="G121" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H121" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I121" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="J121" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="K121" s="13" t="s">
+        <v>493</v>
+      </c>
+      <c r="L121" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="M121" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13">
+      <c r="A122" s="3"/>
+      <c r="B122" s="3"/>
+      <c r="C122" s="3"/>
+      <c r="D122" s="3"/>
+      <c r="E122" s="3"/>
+      <c r="F122" s="3"/>
+      <c r="G122" s="3"/>
+      <c r="H122" s="3"/>
+      <c r="I122" s="3"/>
+      <c r="J122" s="6"/>
+      <c r="K122" s="3"/>
+      <c r="L122" s="3"/>
+      <c r="M122" s="3"/>
+    </row>
+    <row r="123" spans="1:13">
+      <c r="A123" s="3"/>
+      <c r="B123" s="3"/>
+      <c r="C123" s="3"/>
+      <c r="D123" s="3"/>
+      <c r="E123" s="3"/>
+      <c r="F123" s="3"/>
+      <c r="G123" s="3"/>
+      <c r="H123" s="3"/>
+      <c r="I123" s="3"/>
+      <c r="J123" s="6"/>
+      <c r="K123" s="3"/>
+      <c r="L123" s="3"/>
+      <c r="M123" s="3"/>
+    </row>
+    <row r="124" spans="1:13">
+      <c r="A124" s="3"/>
+      <c r="B124" s="3"/>
+      <c r="C124" s="3"/>
+      <c r="D124" s="3"/>
+      <c r="E124" s="3"/>
+      <c r="F124" s="3"/>
+      <c r="G124" s="3"/>
+      <c r="H124" s="3"/>
+      <c r="I124" s="3"/>
+      <c r="J124" s="6"/>
+      <c r="K124" s="3"/>
+      <c r="L124" s="3"/>
+      <c r="M124" s="3"/>
+    </row>
+    <row r="125" spans="1:13">
+      <c r="A125" s="3"/>
+      <c r="B125" s="3"/>
+      <c r="C125" s="3"/>
+      <c r="D125" s="3"/>
+      <c r="E125" s="3"/>
+      <c r="F125" s="3"/>
+      <c r="G125" s="3"/>
+      <c r="H125" s="3"/>
+      <c r="I125" s="3"/>
+      <c r="J125" s="6"/>
+      <c r="K125" s="3"/>
+      <c r="L125" s="3"/>
+      <c r="M125" s="3"/>
+    </row>
+    <row r="126" spans="1:13">
+      <c r="A126" s="3"/>
+      <c r="B126" s="3"/>
+      <c r="C126" s="3"/>
+      <c r="D126" s="3"/>
+      <c r="E126" s="3"/>
+      <c r="F126" s="3"/>
+      <c r="G126" s="3"/>
+      <c r="H126" s="3"/>
+      <c r="I126" s="3"/>
+      <c r="J126" s="6"/>
+      <c r="K126" s="3"/>
+      <c r="L126" s="3"/>
+      <c r="M126" s="3"/>
+    </row>
+    <row r="127" spans="1:13">
+      <c r="A127" s="3"/>
+      <c r="B127" s="3"/>
+      <c r="C127" s="3"/>
+      <c r="D127" s="3"/>
+      <c r="E127" s="3"/>
+      <c r="F127" s="3"/>
+      <c r="G127" s="3"/>
+      <c r="H127" s="3"/>
+      <c r="I127" s="3"/>
+      <c r="J127" s="6"/>
+      <c r="K127" s="3"/>
+      <c r="L127" s="3"/>
+      <c r="M127" s="3"/>
+    </row>
+    <row r="128" spans="1:13">
+      <c r="A128" s="3"/>
+      <c r="B128" s="3"/>
+      <c r="C128" s="3"/>
+      <c r="D128" s="3"/>
+      <c r="E128" s="3"/>
+      <c r="F128" s="3"/>
+      <c r="G128" s="3"/>
+      <c r="H128" s="3"/>
+      <c r="I128" s="3"/>
+      <c r="J128" s="6"/>
+      <c r="K128" s="3"/>
+      <c r="L128" s="3"/>
+      <c r="M128" s="3"/>
+    </row>
+    <row r="129" spans="1:13">
+      <c r="A129" s="3"/>
+      <c r="B129" s="3"/>
+      <c r="C129" s="3"/>
+      <c r="D129" s="3"/>
+      <c r="E129" s="3"/>
+      <c r="F129" s="3"/>
+      <c r="G129" s="3"/>
+      <c r="H129" s="3"/>
+      <c r="I129" s="3"/>
+      <c r="J129" s="6"/>
+      <c r="K129" s="3"/>
+      <c r="L129" s="3"/>
+      <c r="M129" s="3"/>
+    </row>
+    <row r="130" spans="1:13">
+      <c r="A130" s="3"/>
+      <c r="B130" s="3"/>
+      <c r="C130" s="3"/>
+      <c r="D130" s="3"/>
+      <c r="E130" s="3"/>
+      <c r="F130" s="3"/>
+      <c r="G130" s="3"/>
+      <c r="H130" s="3"/>
+      <c r="I130" s="3"/>
+      <c r="J130" s="6"/>
+      <c r="K130" s="3"/>
+      <c r="L130" s="3"/>
+      <c r="M130" s="3"/>
+    </row>
+    <row r="131" spans="1:13">
+      <c r="A131" s="3"/>
+      <c r="B131" s="3"/>
+      <c r="C131" s="3"/>
+      <c r="D131" s="3"/>
+      <c r="E131" s="3"/>
+      <c r="F131" s="3"/>
+      <c r="G131" s="3"/>
+      <c r="H131" s="3"/>
+      <c r="I131" s="3"/>
+      <c r="J131" s="6"/>
+      <c r="K131" s="3"/>
+      <c r="L131" s="3"/>
+      <c r="M131" s="3"/>
+    </row>
+    <row r="132" spans="1:13">
+      <c r="A132" s="3"/>
+      <c r="B132" s="3"/>
+      <c r="C132" s="3"/>
+      <c r="D132" s="3"/>
+      <c r="E132" s="3"/>
+      <c r="F132" s="3"/>
+      <c r="G132" s="3"/>
+      <c r="H132" s="3"/>
+      <c r="I132" s="3"/>
+      <c r="J132" s="6"/>
+      <c r="K132" s="3"/>
+      <c r="L132" s="3"/>
+      <c r="M132" s="3"/>
+    </row>
+    <row r="133" spans="1:13">
+      <c r="A133" s="3"/>
+      <c r="B133" s="3"/>
+      <c r="C133" s="3"/>
+      <c r="D133" s="3"/>
+      <c r="E133" s="3"/>
+      <c r="F133" s="3"/>
+      <c r="G133" s="3"/>
+      <c r="H133" s="3"/>
+      <c r="I133" s="3"/>
+      <c r="J133" s="6"/>
+      <c r="K133" s="3"/>
+      <c r="L133" s="3"/>
+      <c r="M133" s="3"/>
+    </row>
+    <row r="134" spans="1:13">
+      <c r="A134" s="3"/>
+      <c r="B134" s="3"/>
+      <c r="C134" s="3"/>
+      <c r="D134" s="3"/>
+      <c r="E134" s="3"/>
+      <c r="F134" s="3"/>
+      <c r="G134" s="3"/>
+      <c r="H134" s="3"/>
+      <c r="I134" s="3"/>
+      <c r="J134" s="6"/>
+      <c r="K134" s="3"/>
+      <c r="L134" s="3"/>
+      <c r="M134" s="3"/>
+    </row>
+    <row r="135" spans="1:13">
+      <c r="A135" s="3"/>
+      <c r="B135" s="3"/>
+      <c r="C135" s="3"/>
+      <c r="D135" s="3"/>
+      <c r="E135" s="3"/>
+      <c r="F135" s="3"/>
+      <c r="G135" s="3"/>
+      <c r="H135" s="3"/>
+      <c r="I135" s="3"/>
+      <c r="J135" s="6"/>
+      <c r="K135" s="3"/>
+      <c r="L135" s="3"/>
+      <c r="M135" s="3"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation allowBlank="1" sqref="G1:H1" xr:uid="{368EE41E-2705-1B43-9A52-5A9881088DDE}"/>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="K83" r:id="rId1" xr:uid="{B26B418E-DD48-4E83-BB37-848152B687EC}"/>
+    <hyperlink ref="K84" r:id="rId2" xr:uid="{6C54A787-4172-4FAF-8153-0DAC9DCDB938}"/>
+    <hyperlink ref="K85" r:id="rId3" xr:uid="{4FBB6745-680C-4EF0-B8E7-1B954BB30B4E}"/>
+    <hyperlink ref="K86" r:id="rId4" xr:uid="{D46786CB-5B8E-4706-9F2B-4C0AD8E73B27}"/>
+    <hyperlink ref="K87" r:id="rId5" xr:uid="{657351BD-88E6-4A80-AB85-9068838CB91A}"/>
+    <hyperlink ref="K88" r:id="rId6" xr:uid="{CE41647C-65AC-4023-85FE-FB3A4CBE66D1}"/>
+    <hyperlink ref="K89" r:id="rId7" xr:uid="{41B93F60-8676-42F8-AB3B-0EF536AA7128}"/>
+    <hyperlink ref="K90" r:id="rId8" xr:uid="{7CC0DEF0-305F-42A6-ABCE-F1487F0EC1DB}"/>
+    <hyperlink ref="K91" r:id="rId9" xr:uid="{75413EF0-9D07-47AC-B005-88AA88E02B09}"/>
+    <hyperlink ref="K92" r:id="rId10" xr:uid="{46EE40CD-1B55-45EE-B796-ADB3AB578548}"/>
+    <hyperlink ref="K93" r:id="rId11" xr:uid="{0FA44BBB-5B41-469E-AC62-F410BFB96E6F}"/>
+    <hyperlink ref="K94" r:id="rId12" xr:uid="{7948EF90-CF8A-4D88-9A7E-76F9DF4CAC33}"/>
+    <hyperlink ref="K95" r:id="rId13" xr:uid="{7D91FB46-A739-499A-B86B-C5C786D36D80}"/>
+    <hyperlink ref="K96" r:id="rId14" xr:uid="{78008A78-AB32-4432-8076-BF165A896490}"/>
+    <hyperlink ref="K97" r:id="rId15" xr:uid="{2109B0C5-5EF4-4DA8-8534-E6A839219026}"/>
+    <hyperlink ref="K98" r:id="rId16" xr:uid="{DE1111F3-01B3-4EE7-971F-3DA2E7AC2683}"/>
+    <hyperlink ref="K99" r:id="rId17" xr:uid="{52E86ECD-12AB-4255-8975-CF40CABAB84F}"/>
+    <hyperlink ref="K100" r:id="rId18" xr:uid="{6C0845F7-D950-4600-A5A4-D3EC5EC18203}"/>
+    <hyperlink ref="K101" r:id="rId19" xr:uid="{30A5C176-4E69-4953-90F1-7D8FD8B8AB96}"/>
+    <hyperlink ref="K102" r:id="rId20" xr:uid="{528CA009-5514-4DB0-BBA7-E8F8FD6113CB}"/>
+    <hyperlink ref="K103" r:id="rId21" xr:uid="{1591B514-C960-482D-B88C-727F4B4D28CC}"/>
+    <hyperlink ref="K104" r:id="rId22" xr:uid="{41CF9F50-2D43-4ADE-BC9E-B7DEE42E292B}"/>
+    <hyperlink ref="K105" r:id="rId23" xr:uid="{73133CAA-A759-429E-B124-8D3B9B1B35BF}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId24"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="7">
@@ -5383,13 +7326,13 @@
           <x14:formula1>
             <xm:f>'Vinculo con educacion'!$A$1:$A$2</xm:f>
           </x14:formula1>
-          <xm:sqref>H84:H1048576 H2:H82</xm:sqref>
+          <xm:sqref>H2:H82 H84:H1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{CB47FA5A-6567-2547-B57E-466B59F1912C}">
           <x14:formula1>
             <xm:f>'Tipo de norma'!$A$1:$A$10</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D1048576</xm:sqref>
+          <xm:sqref>D2:D109 D111:D1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{EF828923-8993-5646-A9D3-B4E6E4049B2E}">
           <x14:formula1>
@@ -5437,7 +7380,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="15.6">
       <c r="A1" s="1" t="s">
-        <v>353</v>
+        <v>495</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="15.6">
@@ -5447,157 +7390,157 @@
     </row>
     <row r="3" spans="1:1" ht="15.6">
       <c r="A3" s="1" t="s">
-        <v>354</v>
+        <v>496</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="15.6">
       <c r="A4" s="1" t="s">
-        <v>355</v>
+        <v>497</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="15.6">
       <c r="A5" s="1" t="s">
-        <v>356</v>
+        <v>498</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="15.6">
       <c r="A6" s="1" t="s">
-        <v>357</v>
+        <v>499</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="15.6">
       <c r="A7" s="1" t="s">
-        <v>358</v>
+        <v>500</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="15.6">
       <c r="A8" s="1" t="s">
-        <v>359</v>
+        <v>501</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="15.6">
       <c r="A9" s="1" t="s">
-        <v>360</v>
+        <v>502</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="15.6">
       <c r="A10" s="1" t="s">
-        <v>361</v>
+        <v>503</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="15.6">
       <c r="A11" s="1" t="s">
-        <v>362</v>
+        <v>504</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="15.6">
       <c r="A12" s="1" t="s">
-        <v>363</v>
+        <v>505</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="15.6">
       <c r="A13" s="1" t="s">
-        <v>364</v>
+        <v>506</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="15.6">
       <c r="A14" s="1" t="s">
-        <v>365</v>
+        <v>507</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="15.6">
       <c r="A15" s="1" t="s">
-        <v>366</v>
+        <v>508</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="15.6">
       <c r="A16" s="1" t="s">
-        <v>367</v>
+        <v>509</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="15.6">
       <c r="A17" s="1" t="s">
-        <v>368</v>
+        <v>510</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15.6">
       <c r="A18" s="1" t="s">
-        <v>369</v>
+        <v>511</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="15.6">
       <c r="A19" s="1" t="s">
-        <v>370</v>
+        <v>512</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15.6">
       <c r="A20" s="1" t="s">
-        <v>371</v>
+        <v>513</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="15.6">
       <c r="A21" s="1" t="s">
-        <v>372</v>
+        <v>514</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="15.6">
       <c r="A22" s="1" t="s">
-        <v>373</v>
+        <v>515</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="15.6">
       <c r="A23" s="1" t="s">
-        <v>374</v>
+        <v>516</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="15.6">
       <c r="A24" s="1" t="s">
-        <v>375</v>
+        <v>517</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="15.6">
       <c r="A25" s="1" t="s">
-        <v>376</v>
+        <v>518</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="15.6">
       <c r="A26" s="1" t="s">
-        <v>377</v>
+        <v>519</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="15.6">
       <c r="A27" s="1" t="s">
-        <v>378</v>
+        <v>520</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="15.6">
       <c r="A28" s="1" t="s">
-        <v>379</v>
+        <v>521</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="15.6">
       <c r="A29" s="1" t="s">
-        <v>380</v>
+        <v>522</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="15.6">
       <c r="A30" s="1" t="s">
-        <v>381</v>
+        <v>523</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="15.6">
       <c r="A31" s="1" t="s">
-        <v>382</v>
+        <v>524</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="15.6">
       <c r="A32" s="1" t="s">
-        <v>383</v>
+        <v>525</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="15.6">
       <c r="A33" s="1" t="s">
-        <v>384</v>
+        <v>526</v>
       </c>
     </row>
   </sheetData>
@@ -5618,7 +7561,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>385</v>
+        <v>527</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -5687,7 +7630,7 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>386</v>
+        <v>528</v>
       </c>
     </row>
   </sheetData>
@@ -5773,7 +7716,7 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>387</v>
+        <v>435</v>
       </c>
     </row>
     <row r="4" spans="1:1">

--- a/data/Matriz_Normativa_IA_Educacion_LATAM.xlsx
+++ b/data/Matriz_Normativa_IA_Educacion_LATAM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tecmx-my.sharepoint.com/personal/a00834778_tec_mx/Documents/Desktop/Carlos Auquilla/Proyectos/GENIAL/GENIAL_dev/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="428" documentId="8_{DEF93B8B-1B75-490B-94A3-E0F7B496BF87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{350EF929-F841-4D67-802D-87771D8B7F4B}"/>
+  <xr:revisionPtr revIDLastSave="447" documentId="8_{DEF93B8B-1B75-490B-94A3-E0F7B496BF87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD8CB0F8-A2D3-4EA1-B504-03306B3930F1}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1595" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1721" uniqueCount="636">
   <si>
     <t>Investigador</t>
   </si>
@@ -1535,6 +1535,327 @@
   </si>
   <si>
     <t>Prohíbe el uso de 'Inteligencia Artificial generativa' en la elaboración de anteproyectos. Establece lineamientos para la admisión a la maestría en asuntos políticos y políticas públicas, incluyendo la detección de plagio.</t>
+  </si>
+  <si>
+    <t>Establece pautas para el uso de herramientas de IA en actividades académicas, incluyendo condiciones sobre 'propiedad intelectual' y 'plagio'. Promueve la 'alfabetización en IA' como parte de las competencias educativas en CETYS Universidad.</t>
+  </si>
+  <si>
+    <t>Instituto de Estudios Jurídicos - IDEJ</t>
+  </si>
+  <si>
+    <t>https://idej.edu.mx/egresados/</t>
+  </si>
+  <si>
+    <t>Establece principios sobre la 'responsabilidad ética' en el uso de la inteligencia artificial en la educación superior. Aunque no es una norma formal, su contenido es relevante para la gobernanza de IA en el ámbito educativo.</t>
+  </si>
+  <si>
+    <t>Fiscalía General de Justicia de la Ciudad de México</t>
+  </si>
+  <si>
+    <t>https://www.fgjcdmx.gob.mx/storage/app/media/Banner/FGJCDMX%20Plan%20de%20Poliitica%20Criminal%20y%20Programa%20de%20Persecucion%20Penal%202026/fgjcdmx-plan-de-politica-criminal-y-programa-de-persecucion-penal-2026.pdf</t>
+  </si>
+  <si>
+    <t>Establece lineamientos para la 'Política de Cero' que incluye el uso de 'inteligencia artificial' para garantizar la presencia efectiva del personal mediante geolocalización. Aunque menciona IA, su enfoque principal es la política criminal y no se centra en la educación superior.</t>
+  </si>
+  <si>
+    <t>https://www.bib.ibero.mx/ahco/files/original/041f64dcc0a60c38f3b95fb52b74a5dd.pdf</t>
+  </si>
+  <si>
+    <t>Establece directrices para el uso de la 'Inteligencia Artificial' en procesos educativos, indicando que su uso debe ser autorizado por los docentes y regulado en las 'Guías de estudio del Profesor'. Prohíbe el uso no reportado de IA en la elaboración de productos académicos, considerándolo una falta académica.</t>
+  </si>
+  <si>
+    <t>Tecnológico Nacional de México</t>
+  </si>
+  <si>
+    <t>https://www.apizaco.tecnm.mx/wp-content/uploads/2025/04/IAD-2416-Inteligencia-artificial-explicable.pdf</t>
+  </si>
+  <si>
+    <t>Establece la asignatura 'Inteligencia Artificial Explicable' en el plan de estudios de la carrera de 'Ingeniería en Inteligencia Artificial'. Promueve la 'transparencia', 'ética' y 'comprensibilidad' en sistemas de IA, preparando a los estudiantes para su diseño y evaluación responsable.</t>
+  </si>
+  <si>
+    <t>Instituto Nacional de Salud Pública</t>
+  </si>
+  <si>
+    <t>https://insp.mx/resources/images/stories/INSP/Docs/cultura_institucional/ComiteEtica_2026/260217_codigo_etica_integridad_BGAPF.pdf</t>
+  </si>
+  <si>
+    <t>Establece lineamientos sobre el uso de 'inteligencia artificial' en contravención a las disposiciones éticas. Proporciona un marco para la integridad en el uso de tecnologías digitales en el ámbito institucional.</t>
+  </si>
+  <si>
+    <t>https://repositorio.cetys.mx/handle/60000/1856</t>
+  </si>
+  <si>
+    <t>Universidad del Valle de Atemajac</t>
+  </si>
+  <si>
+    <t>https://www.univa.mx/zamora/wp-content/uploads/sites/3/2024/01/Codigo-de-Honor-e-Integridad-Academica-SU_2024_Zamora.pdf</t>
+  </si>
+  <si>
+    <t>Establece principios de 'honestidad' e 'integridad académica' y regula el uso de herramientas de inteligencia artificial, enfatizando que el trabajo final debe ser resultado del 'propio entendimiento y esfuerzo' del estudiante.</t>
+  </si>
+  <si>
+    <t>Secretaría de Economía</t>
+  </si>
+  <si>
+    <t>https://www.economia.gob.mx/files/gobmx/dgpe/informe_avance_resultados_2023_2024_proseco.pdf</t>
+  </si>
+  <si>
+    <t>Establece lineamientos para la implementación de políticas públicas en el marco del 'Plan Nacional de Desarrollo 2019-2024'. Incluye aspectos relacionados con la economía digital y la inversión en tecnología, aunque no se centra exclusivamente en IA.</t>
+  </si>
+  <si>
+    <t>Universidad Nacional Rosario Castellanos</t>
+  </si>
+  <si>
+    <t>https://www.rcastellanos.cdmx.gob.mx/storage/app/media/lineamientos-para-el-uso-etico-de-la-inteligencia-artificial-en-trabajos-academicos-de-estudiantes-de-posgrado.pdf</t>
+  </si>
+  <si>
+    <t>Establece directrices para el uso ético de la inteligencia artificial en trabajos académicos. Promueve la integridad académica y el uso responsable de herramientas de IA en la educación superior.</t>
+  </si>
+  <si>
+    <t>Secretaría Anticorrupción y Buen Gobierno - INR</t>
+  </si>
+  <si>
+    <t>https://www.inr.gob.mx/Descargas/acercade/CODIGO_ETICA_GOB_FED.pdf</t>
+  </si>
+  <si>
+    <t>Establece lineamientos éticos en el uso de 'inteligencia artificial', abordando aspectos no deseados ni solicitados por la persona receptora. Aunque menciona IA, su enfoque principal es ético y no normativo en el ámbito educativo.</t>
+  </si>
+  <si>
+    <t>Universidad Autónoma de Tamaulipas</t>
+  </si>
+  <si>
+    <t>https://gaceta.uat.edu.mx/images/GacetaUAT-14-Extraordinaria-ENE2026.pdf</t>
+  </si>
+  <si>
+    <t>Establece lineamientos claros para el uso de la 'inteligencia artificial' como herramienta en el proceso educativo y la investigación. Busca beneficiar a la comunidad universitaria y a la sociedad en general.</t>
+  </si>
+  <si>
+    <t>Poder Judicial del estado de Querétaro</t>
+  </si>
+  <si>
+    <t>https://www.poderjudicialqro.gob.mx/biblio/leeDoc.php?cual=158007&amp;reglamentos=1</t>
+  </si>
+  <si>
+    <t>Establece el uso 'responsable, ético y seguro' de herramientas de IA en la administración de justicia. Define conceptos clave como 'decisiones automatizadas' e 'inteligencia artificial', y es de observancia obligatoria para el personal del Poder Judicial.</t>
+  </si>
+  <si>
+    <t>https://www.escom.ipn.mx/docs/oferta/uaIIA2020/aprendizajeMaquina_IIA2020.pdf</t>
+  </si>
+  <si>
+    <t>Establece el 'Programa Académico de Ingeniería en Inteligencia Artificial', definiendo contenidos y métodos de enseñanza relacionados con 'aprendizaje de máquina'. Incluye estrategias de evaluación y bibliografía específica para la formación en IA.</t>
+  </si>
+  <si>
+    <t>UNESCO IESALC</t>
+  </si>
+  <si>
+    <t>https://www.uacj.mx/planeacion/documentos/evaluacion_inst/2024/ChatGPT_e_Inteligencia_Artificial_en_la_educación_superior_guía_de_inicio_rápido.pdf</t>
+  </si>
+  <si>
+    <t>Proporciona un marco para la implementación de 'ChatGPT' en la educación superior, abordando retos e implicaciones éticas de la IA. Ofrece medidas prácticas que las instituciones pueden adoptar para integrar la IA en sus procesos educativos.</t>
+  </si>
+  <si>
+    <t>https://www.fgjcdmx.gob.mx/storage/app/media/Marco%20Normativo/Entidades%20Federativas/Michoacan/doc_690d132a74030_ReglamentoVersinFiscala.pdf</t>
+  </si>
+  <si>
+    <t>Promueve el uso de 'tecnología, inteligencia artificial, minería de datos y análisis predictivo' en la investigación criminal. Establece lineamientos para la implementación de herramientas tecnológicas en procesos administrativos y periciales.</t>
+  </si>
+  <si>
+    <t>INSTITUTO POLITÉCNICO NACIONAL</t>
+  </si>
+  <si>
+    <t>https://www.escom.ipn.mx/docs/oferta/uaISC2020/inteligenciaArtificial_ISC2020.pdf</t>
+  </si>
+  <si>
+    <t>Establece el 'propósito de la unidad de aprendizaje' en inteligencia artificial, incluyendo el desarrollo de 'sistemas inteligentes' y el uso de 'algoritmos de aprendizaje'. Define métodos de enseñanza y evaluación, contribuyendo a la formación profesional en el área de sistemas computacionales.</t>
+  </si>
+  <si>
+    <t>Instituto Tecnológico de Jiquilpan</t>
+  </si>
+  <si>
+    <t>http://www.jiquilpan.tecnm.mx/documentos/Carreras/Ing_SistemasComputacionales/Especialidades/Desarrollo_Apps_Intel_Web-Movil.pdf</t>
+  </si>
+  <si>
+    <t>Establece un marco formativo en áreas de 'Inteligencia Artificial', incluyendo 'visión por computadora' y 'aprendizaje automático'. Define competencias específicas para el egreso en el contexto de aplicaciones inteligentes, lo que es relevante para la educación en IA.</t>
+  </si>
+  <si>
+    <t>Instituto Nacional de Transparencia, Acceso a la Información y Protección de Datos Personales</t>
+  </si>
+  <si>
+    <t>https://www.ujed.mx/doc/banners/Carta_DDigitales.pdf</t>
+  </si>
+  <si>
+    <t>Establece derechos relacionados con el uso de 'inteligencia artificial centrada en la persona' y la 'privacidad y protección de datos personales'. Incluye principios de 'transparencia' y 'seguridad' en el uso de IA, lo que es relevante para la gobernanza de la IA en el ámbito educativo.</t>
+  </si>
+  <si>
+    <t>https://www.itsna.edu.mx/descargas/vinculacion/innovatecnm/ReglamentoTecnicoInnoBotica2025.pdf</t>
+  </si>
+  <si>
+    <t>Establece las 'consideraciones específicas' y 'especificaciones técnicas' para el evento InnoBótica, promoviendo el desarrollo de propuestas en robótica. Fomenta la creatividad y habilidades tecnológicas en la comunidad estudiantil, vinculando la educación con la innovación tecnológica.</t>
+  </si>
+  <si>
+    <t>Instituto Tecnológico de Ciudad Victoria</t>
+  </si>
+  <si>
+    <t>https://www.itvictoria.edu.mx/oferta//maestria_sistemas/Archivos/4.%20Plan%20Estudios%20MSC.pdf</t>
+  </si>
+  <si>
+    <t>Establece las 'líneas de trabajo' en la Maestría en Sistemas Computacionales, incluyendo 'Inteligencia Artificial' y su aplicación en 'biometría' y 'toma de decisiones inteligentes'. Contribuye a la formación de profesionales capacitados en áreas tecnológicas relevantes para la región.</t>
+  </si>
+  <si>
+    <t>https://www.fgjcdmx.gob.mx/storage/app/uploads/public/69a/f0f/c16/69af0fc167b8f670078603.pdf</t>
+  </si>
+  <si>
+    <t>Establece disposiciones sobre 'información tecnológica y de inteligencia artificial' en el contexto de la desaparición forzada. Aunque menciona IA, su enfoque principal no es la regulación educativa específica.</t>
+  </si>
+  <si>
+    <t>UCEMICH</t>
+  </si>
+  <si>
+    <t>https://ucemich.edu.mx/wp-content/uploads/2026/02/convocatoria26/PORRA.pdf</t>
+  </si>
+  <si>
+    <t>Prohíbe el uso de herramientas de 'Inteligencia Artificial' para la generación de propuestas, garantizando la 'autenticidad y creatividad' de los participantes. Establece que las propuestas deben ser originales y de autoría personal, descalificando aquellas que utilicen IA.</t>
+  </si>
+  <si>
+    <t>https://www.cic.ipn.mx/doc/MCyTIAyCD/2-Oblig-Fundamentos-IAyCD%202023%2006%2028.pdf</t>
+  </si>
+  <si>
+    <t>Establece los 'Fundamentos de Inteligencia Artificial y Ciencia de Datos' como unidad de aprendizaje obligatoria en la Maestría en Ciencia y Tecnología de IA. Define competencias y metodologías relacionadas con la IA aplicadas en contextos académicos y profesionales.</t>
+  </si>
+  <si>
+    <t>https://comunicacionsocial.senado.gob.mx/informacion/comunicados/13874-presentan-lineamientos-para-el-uso-responsable-de-la-inteligencia-artificial-en-la-abogacia</t>
+  </si>
+  <si>
+    <t>Establece lineamientos para el 'uso responsable de la Inteligencia Artificial' en la abogacía, promoviendo principios éticos y buenas prácticas. Es un documento relevante para la regulación de la IA en el ámbito legal en México.</t>
+  </si>
+  <si>
+    <t>https://www.iee.edu.mx/iee-ciudad-de-mexico/licenciatura-ejecutiva-en-derecho/</t>
+  </si>
+  <si>
+    <t>Introduce la 'inteligencia artificial aplicada al derecho' como parte de los lineamientos académicos. Establece un enfoque en la ética y la toma de decisiones en el contexto del derecho.</t>
+  </si>
+  <si>
+    <t>https://exlegibus.pjedomex.gob.mx/index.php/exlegibus/article/download/486/692/1070</t>
+  </si>
+  <si>
+    <t>Desarrolla directrices para abordar la 'inteligencia artificial' en la educación. Proporciona pautas para los operadores de IA, aunque aún se encuentra en fase de proyecto.</t>
+  </si>
+  <si>
+    <t>Universidad del Norte</t>
+  </si>
+  <si>
+    <t>https://www.un.edu.mx/wp-content/uploads/2026/01/Reglamento_general_UN_2026.2.pdf</t>
+  </si>
+  <si>
+    <t>Establece disposiciones sobre el 'buen uso y manejo de la Tecnología', que puede incluir aspectos relacionados con la IA en el contexto educativo. Regula derechos y obligaciones del personal docente y alumnos, lo que puede influir en la implementación de tecnologías educativas.</t>
+  </si>
+  <si>
+    <t>Universidad Autónoma de Nayarit</t>
+  </si>
+  <si>
+    <t>https://www.uan.edu.mx/es/maestria-en-ciencias-e-ingenieria</t>
+  </si>
+  <si>
+    <t>Establece el perfil de egreso del Maestro(a) en Ciencias e Ingeniería, incluyendo 'fundamentos avanzados de Inteligencia Artificial y Robótica' y la 'capacidad para diseñar, implementar y evaluar sistemas de inteligencia artificial'. Define competencias específicas relacionadas con la aplicación de IA en contextos industriales y sociales.</t>
+  </si>
+  <si>
+    <t>https://www.ucol.mx/documentos-normateca/descarga/lineamientos/propuesta_IA_generativa_v9/</t>
+  </si>
+  <si>
+    <t>Establece lineamientos para el uso de 'Inteligencia Artificial Generativa' en la Universidad de Colima. Busca transformar la educación mediante la integración de tecnologías de información.</t>
+  </si>
+  <si>
+    <t>Instituto Tecnológico de Hermosillo</t>
+  </si>
+  <si>
+    <t>https://ith.mx/posgrado/MIA/Lineamientos.html</t>
+  </si>
+  <si>
+    <t>Establece lineamientos para la operación de la 'Maestría en Inteligencia Artificial', regulando aspectos pedagógicos y administrativos del programa. Es un documento clave para la implementación de la educación en IA en el ámbito del Tecnológico Nacional de México.</t>
+  </si>
+  <si>
+    <t>ISU Universidad</t>
+  </si>
+  <si>
+    <t>https://isu.edu.mx/doctorados-en-linea/doctorado-en-ciencias-penales-y-politica-criminal/</t>
+  </si>
+  <si>
+    <t>Establece la línea de investigación sobre 'Inteligencia artificial y ciencia de datos en la prevención y persecución del delito', promoviendo el uso de 'big data' y 'machine learning' en la seguridad pública. Se enfoca en la adaptación de modelos internacionales de IA a la investigación criminal en México.</t>
+  </si>
+  <si>
+    <t>Universidad Autónoma de la Ciudad de México</t>
+  </si>
+  <si>
+    <t>https://uacm.edu.mx/Portals/0/OfertaAcademica/CCyT/Programas/CS/Software/Optativas/IA/Inteligencia_artificial.pdf</t>
+  </si>
+  <si>
+    <t>Establece el 'Programa de Estudios' para la materia de Inteligencia Artificial, definiendo objetivos, contenidos y metodologías de enseñanza. Promueve el desarrollo de habilidades en el análisis y resolución de problemas prácticos en el ámbito de la IA.</t>
+  </si>
+  <si>
+    <t>https://www.zaragoza.unam.mx/presentan-recursos-digitales-para-fortalecer-la-ensenanza/</t>
+  </si>
+  <si>
+    <t>Establece el 'proceso de registro y control' para las licencias Creative Commons asignadas a recursos educativos digitales. Regula la titularidad de derechos morales y patrimoniales sobre dichos recursos, vinculando la creación de contenidos con la normativa de derechos de autor.</t>
+  </si>
+  <si>
+    <t>ifpes</t>
+  </si>
+  <si>
+    <t>https://ifpes.fgjcdmx.gob.mx/storage/app/uploads/public/692/dcd/a59/692dcda594b52522575729.pdf</t>
+  </si>
+  <si>
+    <t>Prohíbe el 'uso indebido de inteligencia artificial' que derive en suplantación, plagio o falsificación de información. Establece principios éticos para el uso de IA en el ámbito educativo.</t>
+  </si>
+  <si>
+    <t>Universidad de Celay</t>
+  </si>
+  <si>
+    <t>https://paginas.udec.edu.mx/uploads/documentos/Decalogo+de+Integridad+del+Docente+UdeC.pdf</t>
+  </si>
+  <si>
+    <t>Promueve el 'uso ético de la tecnología' y la 'Inteligencia Artificial con Integridad Académica'. Establece principios como el respeto a la privacidad y la promoción de un ambiente digital sano.</t>
+  </si>
+  <si>
+    <t>https://www.fermatta.edu.mx/planes-educativos-mae/maestr%C3%ADa-en-audio-y-la-industria-del-entretenimiento-digital-con-certificaci%C3%B3n-en-dise%C3%B1o-de-audio-y-postproducci%C3%B3n-para-cine-y-televisi%C3%B3n</t>
+  </si>
+  <si>
+    <t>Establece un programa académico que incluye 'Herramientas de Inteligencia Artificial para la Creación de Música' en varios semestres. Proporciona formación integral en diseño de audio y postproducción, integrando tecnología avanzada y enfoques estratégicos en el entretenimiento digital.</t>
+  </si>
+  <si>
+    <t>Coordinación de la Estrategia Digital Nacional</t>
+  </si>
+  <si>
+    <t>https://www.gob.mx/cms/uploads/attachment/file/415644/Consolidado_Comentarios_Consulta_IA__1_.pdf</t>
+  </si>
+  <si>
+    <t>Establece 'Principios Generales' y una 'Guía de Análisis de Impacto' para el uso responsable de IA en la administración pública. Promueve la ética y la protección de datos personales en el desarrollo de sistemas de IA.</t>
+  </si>
+  <si>
+    <t>https://www.cic.ipn.mx/doc/MCyTIAyCD/4-Opt-Introducci%C3%B3n-inteligencia-artificial-simb%C3%B3lica.pdf</t>
+  </si>
+  <si>
+    <t>Establece los lineamientos para la creación de la unidad de aprendizaje 'Introducción a la Inteligencia Artificial Simbólica'. Define objetivos de aprendizaje, contenidos y metodologías relacionadas con la inteligencia artificial en el contexto académico.</t>
+  </si>
+  <si>
+    <t>Universidad Autónoma de Carmen</t>
+  </si>
+  <si>
+    <t>http://www.cgtic.unacar.mx/normatividad/Reglamento_TIC_UNACAR.pdf</t>
+  </si>
+  <si>
+    <t>Establece la 'metodología de Desarrollo de Sistemas de Información (DSI)' y propone procedimientos y políticas apegados a 'mejores prácticas' en desarrollo. Aunque no menciona IA explícitamente, su enfoque en sistemas de información puede implicar su uso en el contexto educativo.</t>
+  </si>
+  <si>
+    <t>https://www.ucol.mx/normateca/lineamientos.htm</t>
+  </si>
+  <si>
+    <t>Regula las etapas, pautas, requisitos y criterios para la educación continua. Aunque no menciona IA explícitamente, establece un marco que podría incluir su uso en procesos educativos.</t>
+  </si>
+  <si>
+    <t>https://www.ensenada.tecnm.mx/wp-content/uploads/2024/05/ReglamentoTecOficial_2024.pdf</t>
+  </si>
+  <si>
+    <t>Establece lineamientos para la participación en la 'InnoBótica', promoviendo el desarrollo de propuestas en robótica. Define especificaciones técnicas y procesos de registro para equipos multidisciplinarios, fomentando la innovación y la colaboración en el ámbito educativo.</t>
   </si>
   <si>
     <t>Brasil</t>
@@ -2096,9 +2417,36 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{FEFD5123-BFF8-434C-8C7F-5058A3E0BD3F}">
+  <we:reference id="WA200009404" version="1.0.0.8" store="en-us" storeType="omex"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="en-us" storeType="omex"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;ad233bae-3073-48b2-9894-5a598d531588&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+  <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
+      <we:containsCustomFunctions/>
+    </a:ext>
+  </we:extLst>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M135"/>
+  <dimension ref="A1:M196"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="16.140625" customWidth="1"/>
@@ -7065,8 +7413,8 @@
       <c r="I121" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="J121" s="6" t="s">
-        <v>287</v>
+      <c r="J121" s="3" t="s">
+        <v>435</v>
       </c>
       <c r="K121" s="13" t="s">
         <v>493</v>
@@ -7078,215 +7426,1382 @@
         <v>43</v>
       </c>
     </row>
-    <row r="122" spans="1:13">
+    <row r="122" spans="1:13" ht="152.25">
       <c r="A122" s="3"/>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
       <c r="E122" s="3"/>
-      <c r="F122" s="3"/>
+      <c r="F122" s="3" t="s">
+        <v>186</v>
+      </c>
       <c r="G122" s="3"/>
       <c r="H122" s="3"/>
       <c r="I122" s="3"/>
       <c r="J122" s="6"/>
-      <c r="K122" s="3"/>
-      <c r="L122" s="3"/>
+      <c r="K122" s="13" t="s">
+        <v>407</v>
+      </c>
+      <c r="L122" s="12" t="s">
+        <v>495</v>
+      </c>
       <c r="M122" s="3"/>
     </row>
-    <row r="123" spans="1:13">
+    <row r="123" spans="1:13" ht="121.5">
       <c r="A123" s="3"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
       <c r="E123" s="3"/>
-      <c r="F123" s="3"/>
+      <c r="F123" s="3" t="s">
+        <v>496</v>
+      </c>
       <c r="G123" s="3"/>
       <c r="H123" s="3"/>
       <c r="I123" s="3"/>
       <c r="J123" s="6"/>
-      <c r="K123" s="3"/>
-      <c r="L123" s="3"/>
+      <c r="K123" s="13" t="s">
+        <v>497</v>
+      </c>
+      <c r="L123" s="12" t="s">
+        <v>498</v>
+      </c>
       <c r="M123" s="3"/>
     </row>
-    <row r="124" spans="1:13">
+    <row r="124" spans="1:13" ht="167.25">
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
-      <c r="F124" s="3"/>
+      <c r="F124" s="3" t="s">
+        <v>499</v>
+      </c>
       <c r="G124" s="3"/>
       <c r="H124" s="3"/>
       <c r="I124" s="3"/>
       <c r="J124" s="6"/>
-      <c r="K124" s="3"/>
-      <c r="L124" s="3"/>
+      <c r="K124" s="13" t="s">
+        <v>500</v>
+      </c>
+      <c r="L124" s="12" t="s">
+        <v>501</v>
+      </c>
       <c r="M124" s="3"/>
     </row>
-    <row r="125" spans="1:13">
+    <row r="125" spans="1:13" ht="183">
       <c r="A125" s="3"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
       <c r="D125" s="3"/>
       <c r="E125" s="3"/>
-      <c r="F125" s="3"/>
+      <c r="F125" s="3" t="s">
+        <v>139</v>
+      </c>
       <c r="G125" s="3"/>
       <c r="H125" s="3"/>
       <c r="I125" s="3"/>
       <c r="J125" s="6"/>
-      <c r="K125" s="3"/>
-      <c r="L125" s="3"/>
+      <c r="K125" s="13" t="s">
+        <v>502</v>
+      </c>
+      <c r="L125" s="12" t="s">
+        <v>503</v>
+      </c>
       <c r="M125" s="3"/>
     </row>
-    <row r="126" spans="1:13">
+    <row r="126" spans="1:13" ht="183">
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
       <c r="E126" s="3"/>
-      <c r="F126" s="3"/>
+      <c r="F126" s="3" t="s">
+        <v>504</v>
+      </c>
       <c r="G126" s="3"/>
       <c r="H126" s="3"/>
       <c r="I126" s="3"/>
       <c r="J126" s="6"/>
-      <c r="K126" s="3"/>
-      <c r="L126" s="3"/>
+      <c r="K126" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="L126" s="12" t="s">
+        <v>506</v>
+      </c>
       <c r="M126" s="3"/>
     </row>
-    <row r="127" spans="1:13">
+    <row r="127" spans="1:13" ht="121.5">
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
       <c r="D127" s="3"/>
       <c r="E127" s="3"/>
-      <c r="F127" s="3"/>
+      <c r="F127" s="3" t="s">
+        <v>507</v>
+      </c>
       <c r="G127" s="3"/>
       <c r="H127" s="3"/>
       <c r="I127" s="3"/>
       <c r="J127" s="6"/>
-      <c r="K127" s="3"/>
-      <c r="L127" s="3"/>
+      <c r="K127" s="13" t="s">
+        <v>508</v>
+      </c>
+      <c r="L127" s="12" t="s">
+        <v>509</v>
+      </c>
       <c r="M127" s="3"/>
     </row>
-    <row r="128" spans="1:13">
+    <row r="128" spans="1:13" ht="167.25">
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
       <c r="D128" s="3"/>
       <c r="E128" s="3"/>
-      <c r="F128" s="3"/>
+      <c r="F128" s="3" t="s">
+        <v>186</v>
+      </c>
       <c r="G128" s="3"/>
       <c r="H128" s="3"/>
       <c r="I128" s="3"/>
       <c r="J128" s="6"/>
-      <c r="K128" s="3"/>
-      <c r="L128" s="3"/>
+      <c r="K128" s="13" t="s">
+        <v>510</v>
+      </c>
+      <c r="L128" s="12" t="s">
+        <v>410</v>
+      </c>
       <c r="M128" s="3"/>
     </row>
-    <row r="129" spans="1:13">
+    <row r="129" spans="1:13" ht="137.25">
       <c r="A129" s="3"/>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
       <c r="D129" s="3"/>
       <c r="E129" s="3"/>
-      <c r="F129" s="3"/>
+      <c r="F129" s="3" t="s">
+        <v>511</v>
+      </c>
       <c r="G129" s="3"/>
       <c r="H129" s="3"/>
       <c r="I129" s="3"/>
       <c r="J129" s="6"/>
-      <c r="K129" s="3"/>
-      <c r="L129" s="3"/>
+      <c r="K129" s="13" t="s">
+        <v>512</v>
+      </c>
+      <c r="L129" s="12" t="s">
+        <v>513</v>
+      </c>
       <c r="M129" s="3"/>
     </row>
-    <row r="130" spans="1:13">
+    <row r="130" spans="1:13" ht="167.25">
       <c r="A130" s="3"/>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
       <c r="E130" s="3"/>
-      <c r="F130" s="3"/>
+      <c r="F130" s="3" t="s">
+        <v>514</v>
+      </c>
       <c r="G130" s="3"/>
       <c r="H130" s="3"/>
       <c r="I130" s="3"/>
       <c r="J130" s="6"/>
-      <c r="K130" s="3"/>
-      <c r="L130" s="3"/>
+      <c r="K130" s="13" t="s">
+        <v>515</v>
+      </c>
+      <c r="L130" s="12" t="s">
+        <v>516</v>
+      </c>
       <c r="M130" s="3"/>
     </row>
-    <row r="131" spans="1:13">
+    <row r="131" spans="1:13" ht="121.5">
       <c r="A131" s="3"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
       <c r="D131" s="3"/>
       <c r="E131" s="3"/>
-      <c r="F131" s="3"/>
+      <c r="F131" s="3" t="s">
+        <v>517</v>
+      </c>
       <c r="G131" s="3"/>
       <c r="H131" s="3"/>
       <c r="I131" s="3"/>
       <c r="J131" s="6"/>
-      <c r="K131" s="3"/>
-      <c r="L131" s="3"/>
+      <c r="K131" s="13" t="s">
+        <v>518</v>
+      </c>
+      <c r="L131" s="12" t="s">
+        <v>519</v>
+      </c>
       <c r="M131" s="3"/>
     </row>
-    <row r="132" spans="1:13">
+    <row r="132" spans="1:13" ht="137.25">
       <c r="A132" s="3"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
-      <c r="F132" s="3"/>
+      <c r="F132" s="3" t="s">
+        <v>520</v>
+      </c>
       <c r="G132" s="3"/>
       <c r="H132" s="3"/>
       <c r="I132" s="3"/>
       <c r="J132" s="6"/>
-      <c r="K132" s="3"/>
-      <c r="L132" s="3"/>
+      <c r="K132" s="13" t="s">
+        <v>521</v>
+      </c>
+      <c r="L132" s="12" t="s">
+        <v>522</v>
+      </c>
       <c r="M132" s="3"/>
     </row>
-    <row r="133" spans="1:13">
+    <row r="133" spans="1:13" ht="121.5">
       <c r="A133" s="3"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
       <c r="E133" s="3"/>
-      <c r="F133" s="3"/>
+      <c r="F133" s="3" t="s">
+        <v>523</v>
+      </c>
       <c r="G133" s="3"/>
       <c r="H133" s="3"/>
       <c r="I133" s="3"/>
       <c r="J133" s="6"/>
-      <c r="K133" s="3"/>
-      <c r="L133" s="3"/>
+      <c r="K133" s="13" t="s">
+        <v>524</v>
+      </c>
+      <c r="L133" s="12" t="s">
+        <v>525</v>
+      </c>
       <c r="M133" s="3"/>
     </row>
-    <row r="134" spans="1:13">
+    <row r="134" spans="1:13" ht="137.25">
       <c r="A134" s="3"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
       <c r="E134" s="3"/>
-      <c r="F134" s="3"/>
+      <c r="F134" s="3" t="s">
+        <v>526</v>
+      </c>
       <c r="G134" s="3"/>
       <c r="H134" s="3"/>
       <c r="I134" s="3"/>
       <c r="J134" s="6"/>
-      <c r="K134" s="3"/>
-      <c r="L134" s="3"/>
+      <c r="K134" s="13" t="s">
+        <v>527</v>
+      </c>
+      <c r="L134" s="12" t="s">
+        <v>528</v>
+      </c>
       <c r="M134" s="3"/>
     </row>
-    <row r="135" spans="1:13">
+    <row r="135" spans="1:13" ht="167.25">
       <c r="A135" s="3"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
       <c r="E135" s="3"/>
-      <c r="F135" s="3"/>
+      <c r="F135" s="3" t="s">
+        <v>300</v>
+      </c>
       <c r="G135" s="3"/>
       <c r="H135" s="3"/>
       <c r="I135" s="3"/>
       <c r="J135" s="6"/>
-      <c r="K135" s="3"/>
-      <c r="L135" s="3"/>
+      <c r="K135" s="13" t="s">
+        <v>529</v>
+      </c>
+      <c r="L135" s="12" t="s">
+        <v>530</v>
+      </c>
       <c r="M135" s="3"/>
+    </row>
+    <row r="136" spans="1:13" ht="137.25">
+      <c r="A136" s="3"/>
+      <c r="B136" s="3"/>
+      <c r="C136" s="3"/>
+      <c r="D136" s="3"/>
+      <c r="E136" s="3"/>
+      <c r="F136" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="G136" s="3"/>
+      <c r="H136" s="3"/>
+      <c r="I136" s="3"/>
+      <c r="J136" s="6"/>
+      <c r="K136" s="13" t="s">
+        <v>532</v>
+      </c>
+      <c r="L136" s="12" t="s">
+        <v>533</v>
+      </c>
+      <c r="M136" s="3"/>
+    </row>
+    <row r="137" spans="1:13" ht="152.25">
+      <c r="A137" s="3"/>
+      <c r="B137" s="3"/>
+      <c r="C137" s="3"/>
+      <c r="D137" s="3"/>
+      <c r="E137" s="3"/>
+      <c r="F137" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="G137" s="3"/>
+      <c r="H137" s="3"/>
+      <c r="I137" s="3"/>
+      <c r="J137" s="6"/>
+      <c r="K137" s="13" t="s">
+        <v>534</v>
+      </c>
+      <c r="L137" s="12" t="s">
+        <v>535</v>
+      </c>
+      <c r="M137" s="3"/>
+    </row>
+    <row r="138" spans="1:13" ht="167.25">
+      <c r="A138" s="3"/>
+      <c r="B138" s="3"/>
+      <c r="C138" s="3"/>
+      <c r="D138" s="3"/>
+      <c r="E138" s="3"/>
+      <c r="F138" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="G138" s="3"/>
+      <c r="H138" s="3"/>
+      <c r="I138" s="3"/>
+      <c r="J138" s="6"/>
+      <c r="K138" s="13" t="s">
+        <v>537</v>
+      </c>
+      <c r="L138" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="M138" s="3"/>
+    </row>
+    <row r="139" spans="1:13" ht="167.25">
+      <c r="A139" s="3"/>
+      <c r="B139" s="3"/>
+      <c r="C139" s="3"/>
+      <c r="D139" s="3"/>
+      <c r="E139" s="3"/>
+      <c r="F139" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="G139" s="3"/>
+      <c r="H139" s="3"/>
+      <c r="I139" s="3"/>
+      <c r="J139" s="6"/>
+      <c r="K139" s="13" t="s">
+        <v>540</v>
+      </c>
+      <c r="L139" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="M139" s="3"/>
+    </row>
+    <row r="140" spans="1:13" ht="167.25">
+      <c r="A140" s="3"/>
+      <c r="B140" s="3"/>
+      <c r="C140" s="3"/>
+      <c r="D140" s="3"/>
+      <c r="E140" s="3"/>
+      <c r="F140" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="G140" s="3"/>
+      <c r="H140" s="3"/>
+      <c r="I140" s="3"/>
+      <c r="J140" s="6"/>
+      <c r="K140" s="13" t="s">
+        <v>543</v>
+      </c>
+      <c r="L140" s="12" t="s">
+        <v>544</v>
+      </c>
+      <c r="M140" s="3"/>
+    </row>
+    <row r="141" spans="1:13" ht="167.25">
+      <c r="A141" s="3"/>
+      <c r="B141" s="3"/>
+      <c r="C141" s="3"/>
+      <c r="D141" s="3"/>
+      <c r="E141" s="3"/>
+      <c r="F141" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="G141" s="3"/>
+      <c r="H141" s="3"/>
+      <c r="I141" s="3"/>
+      <c r="J141" s="6"/>
+      <c r="K141" s="13" t="s">
+        <v>545</v>
+      </c>
+      <c r="L141" s="12" t="s">
+        <v>546</v>
+      </c>
+      <c r="M141" s="3"/>
+    </row>
+    <row r="142" spans="1:13" ht="167.25">
+      <c r="A142" s="3"/>
+      <c r="B142" s="3"/>
+      <c r="C142" s="3"/>
+      <c r="D142" s="3"/>
+      <c r="E142" s="3"/>
+      <c r="F142" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="G142" s="3"/>
+      <c r="H142" s="3"/>
+      <c r="I142" s="3"/>
+      <c r="J142" s="6"/>
+      <c r="K142" s="13" t="s">
+        <v>548</v>
+      </c>
+      <c r="L142" s="12" t="s">
+        <v>549</v>
+      </c>
+      <c r="M142" s="3"/>
+    </row>
+    <row r="143" spans="1:13" ht="121.5">
+      <c r="A143" s="3"/>
+      <c r="B143" s="3"/>
+      <c r="C143" s="3"/>
+      <c r="D143" s="3"/>
+      <c r="E143" s="3"/>
+      <c r="F143" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="G143" s="3"/>
+      <c r="H143" s="3"/>
+      <c r="I143" s="3"/>
+      <c r="J143" s="6"/>
+      <c r="K143" s="13" t="s">
+        <v>550</v>
+      </c>
+      <c r="L143" s="12" t="s">
+        <v>551</v>
+      </c>
+      <c r="M143" s="3"/>
+    </row>
+    <row r="144" spans="1:13" ht="167.25">
+      <c r="A144" s="3"/>
+      <c r="B144" s="3"/>
+      <c r="C144" s="3"/>
+      <c r="D144" s="3"/>
+      <c r="E144" s="3"/>
+      <c r="F144" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="G144" s="3"/>
+      <c r="H144" s="3"/>
+      <c r="I144" s="3"/>
+      <c r="J144" s="6"/>
+      <c r="K144" s="13" t="s">
+        <v>553</v>
+      </c>
+      <c r="L144" s="12" t="s">
+        <v>554</v>
+      </c>
+      <c r="M144" s="3"/>
+    </row>
+    <row r="145" spans="1:13" ht="167.25">
+      <c r="A145" s="3"/>
+      <c r="B145" s="3"/>
+      <c r="C145" s="3"/>
+      <c r="D145" s="3"/>
+      <c r="E145" s="3"/>
+      <c r="F145" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="G145" s="3"/>
+      <c r="H145" s="3"/>
+      <c r="I145" s="3"/>
+      <c r="J145" s="6"/>
+      <c r="K145" s="13" t="s">
+        <v>555</v>
+      </c>
+      <c r="L145" s="12" t="s">
+        <v>556</v>
+      </c>
+      <c r="M145" s="3"/>
+    </row>
+    <row r="146" spans="1:13" ht="137.25">
+      <c r="A146" s="3"/>
+      <c r="B146" s="3"/>
+      <c r="C146" s="3"/>
+      <c r="D146" s="3"/>
+      <c r="E146" s="3"/>
+      <c r="F146" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G146" s="3"/>
+      <c r="H146" s="3"/>
+      <c r="I146" s="3"/>
+      <c r="J146" s="6"/>
+      <c r="K146" s="13" t="s">
+        <v>557</v>
+      </c>
+      <c r="L146" s="12" t="s">
+        <v>558</v>
+      </c>
+      <c r="M146" s="3"/>
+    </row>
+    <row r="147" spans="1:13" ht="106.5">
+      <c r="A147" s="3"/>
+      <c r="B147" s="3"/>
+      <c r="C147" s="3"/>
+      <c r="D147" s="3"/>
+      <c r="E147" s="3"/>
+      <c r="F147" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="G147" s="3"/>
+      <c r="H147" s="3"/>
+      <c r="I147" s="3"/>
+      <c r="J147" s="6"/>
+      <c r="K147" s="13" t="s">
+        <v>559</v>
+      </c>
+      <c r="L147" s="12" t="s">
+        <v>560</v>
+      </c>
+      <c r="M147" s="3"/>
+    </row>
+    <row r="148" spans="1:13" ht="106.5">
+      <c r="A148" s="3"/>
+      <c r="B148" s="3"/>
+      <c r="C148" s="3"/>
+      <c r="D148" s="3"/>
+      <c r="E148" s="3"/>
+      <c r="F148" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="G148" s="3"/>
+      <c r="H148" s="3"/>
+      <c r="I148" s="3"/>
+      <c r="J148" s="6"/>
+      <c r="K148" s="13" t="s">
+        <v>561</v>
+      </c>
+      <c r="L148" s="12" t="s">
+        <v>562</v>
+      </c>
+      <c r="M148" s="3"/>
+    </row>
+    <row r="149" spans="1:13" ht="167.25">
+      <c r="A149" s="3"/>
+      <c r="B149" s="3"/>
+      <c r="C149" s="3"/>
+      <c r="D149" s="3"/>
+      <c r="E149" s="3"/>
+      <c r="F149" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="G149" s="3"/>
+      <c r="H149" s="3"/>
+      <c r="I149" s="3"/>
+      <c r="J149" s="6"/>
+      <c r="K149" s="13" t="s">
+        <v>564</v>
+      </c>
+      <c r="L149" s="12" t="s">
+        <v>565</v>
+      </c>
+      <c r="M149" s="3"/>
+    </row>
+    <row r="150" spans="1:13" ht="198">
+      <c r="A150" s="3"/>
+      <c r="B150" s="3"/>
+      <c r="C150" s="3"/>
+      <c r="D150" s="3"/>
+      <c r="E150" s="3"/>
+      <c r="F150" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="G150" s="3"/>
+      <c r="H150" s="3"/>
+      <c r="I150" s="3"/>
+      <c r="J150" s="6"/>
+      <c r="K150" s="13" t="s">
+        <v>567</v>
+      </c>
+      <c r="L150" s="12" t="s">
+        <v>568</v>
+      </c>
+      <c r="M150" s="3"/>
+    </row>
+    <row r="151" spans="1:13" ht="106.5">
+      <c r="A151" s="3"/>
+      <c r="B151" s="3"/>
+      <c r="C151" s="3"/>
+      <c r="D151" s="3"/>
+      <c r="E151" s="3"/>
+      <c r="F151" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="G151" s="3"/>
+      <c r="H151" s="3"/>
+      <c r="I151" s="3"/>
+      <c r="J151" s="6"/>
+      <c r="K151" s="13" t="s">
+        <v>569</v>
+      </c>
+      <c r="L151" s="12" t="s">
+        <v>570</v>
+      </c>
+      <c r="M151" s="3"/>
+    </row>
+    <row r="152" spans="1:13" ht="167.25">
+      <c r="A152" s="3"/>
+      <c r="B152" s="3"/>
+      <c r="C152" s="3"/>
+      <c r="D152" s="3"/>
+      <c r="E152" s="3"/>
+      <c r="F152" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="G152" s="3"/>
+      <c r="H152" s="3"/>
+      <c r="I152" s="3"/>
+      <c r="J152" s="6"/>
+      <c r="K152" s="13" t="s">
+        <v>572</v>
+      </c>
+      <c r="L152" s="12" t="s">
+        <v>573</v>
+      </c>
+      <c r="M152" s="3"/>
+    </row>
+    <row r="153" spans="1:13" ht="198">
+      <c r="A153" s="3"/>
+      <c r="B153" s="3"/>
+      <c r="C153" s="3"/>
+      <c r="D153" s="3"/>
+      <c r="E153" s="3"/>
+      <c r="F153" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="G153" s="3"/>
+      <c r="H153" s="3"/>
+      <c r="I153" s="3"/>
+      <c r="J153" s="6"/>
+      <c r="K153" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="L153" s="12" t="s">
+        <v>576</v>
+      </c>
+      <c r="M153" s="3"/>
+    </row>
+    <row r="154" spans="1:13" ht="152.25">
+      <c r="A154" s="3"/>
+      <c r="B154" s="3"/>
+      <c r="C154" s="3"/>
+      <c r="D154" s="3"/>
+      <c r="E154" s="3"/>
+      <c r="F154" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="G154" s="3"/>
+      <c r="H154" s="3"/>
+      <c r="I154" s="3"/>
+      <c r="J154" s="6"/>
+      <c r="K154" s="13" t="s">
+        <v>578</v>
+      </c>
+      <c r="L154" s="12" t="s">
+        <v>579</v>
+      </c>
+      <c r="M154" s="3"/>
+    </row>
+    <row r="155" spans="1:13" ht="167.25">
+      <c r="A155" s="3"/>
+      <c r="B155" s="3"/>
+      <c r="C155" s="3"/>
+      <c r="D155" s="3"/>
+      <c r="E155" s="3"/>
+      <c r="F155" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G155" s="3"/>
+      <c r="H155" s="3"/>
+      <c r="I155" s="3"/>
+      <c r="J155" s="6"/>
+      <c r="K155" s="13" t="s">
+        <v>580</v>
+      </c>
+      <c r="L155" s="12" t="s">
+        <v>581</v>
+      </c>
+      <c r="M155" s="3"/>
+    </row>
+    <row r="156" spans="1:13" ht="106.5">
+      <c r="A156" s="3"/>
+      <c r="B156" s="3"/>
+      <c r="C156" s="3"/>
+      <c r="D156" s="3"/>
+      <c r="E156" s="3"/>
+      <c r="F156" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="G156" s="3"/>
+      <c r="H156" s="3"/>
+      <c r="I156" s="3"/>
+      <c r="J156" s="6"/>
+      <c r="K156" s="13" t="s">
+        <v>583</v>
+      </c>
+      <c r="L156" s="12" t="s">
+        <v>584</v>
+      </c>
+      <c r="M156" s="3"/>
+    </row>
+    <row r="157" spans="1:13" ht="106.5">
+      <c r="A157" s="3"/>
+      <c r="B157" s="3"/>
+      <c r="C157" s="3"/>
+      <c r="D157" s="3"/>
+      <c r="E157" s="3"/>
+      <c r="F157" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="G157" s="3"/>
+      <c r="H157" s="3"/>
+      <c r="I157" s="3"/>
+      <c r="J157" s="6"/>
+      <c r="K157" s="13" t="s">
+        <v>586</v>
+      </c>
+      <c r="L157" s="12" t="s">
+        <v>587</v>
+      </c>
+      <c r="M157" s="3"/>
+    </row>
+    <row r="158" spans="1:13" ht="167.25">
+      <c r="A158" s="3"/>
+      <c r="B158" s="3"/>
+      <c r="C158" s="3"/>
+      <c r="D158" s="3"/>
+      <c r="E158" s="3"/>
+      <c r="F158" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="G158" s="3"/>
+      <c r="H158" s="3"/>
+      <c r="I158" s="3"/>
+      <c r="J158" s="6"/>
+      <c r="K158" s="13" t="s">
+        <v>588</v>
+      </c>
+      <c r="L158" s="12" t="s">
+        <v>589</v>
+      </c>
+      <c r="M158" s="3"/>
+    </row>
+    <row r="159" spans="1:13" ht="137.25">
+      <c r="A159" s="3"/>
+      <c r="B159" s="3"/>
+      <c r="C159" s="3"/>
+      <c r="D159" s="3"/>
+      <c r="E159" s="3"/>
+      <c r="F159" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="G159" s="3"/>
+      <c r="H159" s="3"/>
+      <c r="I159" s="3"/>
+      <c r="J159" s="6"/>
+      <c r="K159" s="13" t="s">
+        <v>591</v>
+      </c>
+      <c r="L159" s="12" t="s">
+        <v>592</v>
+      </c>
+      <c r="M159" s="3"/>
+    </row>
+    <row r="160" spans="1:13" ht="137.25">
+      <c r="A160" s="3"/>
+      <c r="B160" s="3"/>
+      <c r="C160" s="3"/>
+      <c r="D160" s="3"/>
+      <c r="E160" s="3"/>
+      <c r="F160" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="G160" s="3"/>
+      <c r="H160" s="3"/>
+      <c r="I160" s="3"/>
+      <c r="J160" s="6"/>
+      <c r="K160" s="13" t="s">
+        <v>593</v>
+      </c>
+      <c r="L160" s="12" t="s">
+        <v>594</v>
+      </c>
+      <c r="M160" s="3"/>
+    </row>
+    <row r="161" spans="1:13" ht="167.25">
+      <c r="A161" s="3"/>
+      <c r="B161" s="3"/>
+      <c r="C161" s="3"/>
+      <c r="D161" s="3"/>
+      <c r="E161" s="3"/>
+      <c r="F161" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="G161" s="3"/>
+      <c r="H161" s="3"/>
+      <c r="I161" s="3"/>
+      <c r="J161" s="6"/>
+      <c r="K161" s="13" t="s">
+        <v>596</v>
+      </c>
+      <c r="L161" s="12" t="s">
+        <v>597</v>
+      </c>
+      <c r="M161" s="3"/>
+    </row>
+    <row r="162" spans="1:13" ht="106.5">
+      <c r="A162" s="3"/>
+      <c r="B162" s="3"/>
+      <c r="C162" s="3"/>
+      <c r="D162" s="3"/>
+      <c r="E162" s="3"/>
+      <c r="F162" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="G162" s="3"/>
+      <c r="H162" s="3"/>
+      <c r="I162" s="3"/>
+      <c r="J162" s="6"/>
+      <c r="K162" s="13" t="s">
+        <v>598</v>
+      </c>
+      <c r="L162" s="12" t="s">
+        <v>599</v>
+      </c>
+      <c r="M162" s="3"/>
+    </row>
+    <row r="163" spans="1:13" ht="167.25">
+      <c r="A163" s="3"/>
+      <c r="B163" s="3"/>
+      <c r="C163" s="3"/>
+      <c r="D163" s="3"/>
+      <c r="E163" s="3"/>
+      <c r="F163" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="G163" s="3"/>
+      <c r="H163" s="3"/>
+      <c r="I163" s="3"/>
+      <c r="J163" s="6"/>
+      <c r="K163" s="13" t="s">
+        <v>600</v>
+      </c>
+      <c r="L163" s="12" t="s">
+        <v>601</v>
+      </c>
+      <c r="M163" s="3"/>
+    </row>
+    <row r="164" spans="1:13">
+      <c r="A164" s="3"/>
+      <c r="B164" s="3"/>
+      <c r="C164" s="3"/>
+      <c r="D164" s="3"/>
+      <c r="E164" s="3"/>
+      <c r="F164" s="3"/>
+      <c r="G164" s="3"/>
+      <c r="H164" s="3"/>
+      <c r="I164" s="3"/>
+      <c r="J164" s="6"/>
+      <c r="K164" s="3"/>
+      <c r="L164" s="3"/>
+      <c r="M164" s="3"/>
+    </row>
+    <row r="165" spans="1:13">
+      <c r="A165" s="3"/>
+      <c r="B165" s="3"/>
+      <c r="C165" s="3"/>
+      <c r="D165" s="3"/>
+      <c r="E165" s="3"/>
+      <c r="F165" s="3"/>
+      <c r="G165" s="3"/>
+      <c r="H165" s="3"/>
+      <c r="I165" s="3"/>
+      <c r="J165" s="6"/>
+      <c r="K165" s="3"/>
+      <c r="L165" s="3"/>
+      <c r="M165" s="3"/>
+    </row>
+    <row r="166" spans="1:13">
+      <c r="A166" s="3"/>
+      <c r="B166" s="3"/>
+      <c r="C166" s="3"/>
+      <c r="D166" s="3"/>
+      <c r="E166" s="3"/>
+      <c r="F166" s="3"/>
+      <c r="G166" s="3"/>
+      <c r="H166" s="3"/>
+      <c r="I166" s="3"/>
+      <c r="J166" s="6"/>
+      <c r="K166" s="3"/>
+      <c r="L166" s="3"/>
+      <c r="M166" s="3"/>
+    </row>
+    <row r="167" spans="1:13">
+      <c r="A167" s="3"/>
+      <c r="B167" s="3"/>
+      <c r="C167" s="3"/>
+      <c r="D167" s="3"/>
+      <c r="E167" s="3"/>
+      <c r="F167" s="3"/>
+      <c r="G167" s="3"/>
+      <c r="H167" s="3"/>
+      <c r="I167" s="3"/>
+      <c r="J167" s="6"/>
+      <c r="K167" s="3"/>
+      <c r="L167" s="3"/>
+      <c r="M167" s="3"/>
+    </row>
+    <row r="168" spans="1:13">
+      <c r="A168" s="3"/>
+      <c r="B168" s="3"/>
+      <c r="C168" s="3"/>
+      <c r="D168" s="3"/>
+      <c r="E168" s="3"/>
+      <c r="F168" s="3"/>
+      <c r="G168" s="3"/>
+      <c r="H168" s="3"/>
+      <c r="I168" s="3"/>
+      <c r="J168" s="6"/>
+      <c r="K168" s="3"/>
+      <c r="L168" s="3"/>
+      <c r="M168" s="3"/>
+    </row>
+    <row r="169" spans="1:13">
+      <c r="A169" s="3"/>
+      <c r="B169" s="3"/>
+      <c r="C169" s="3"/>
+      <c r="D169" s="3"/>
+      <c r="E169" s="3"/>
+      <c r="F169" s="3"/>
+      <c r="G169" s="3"/>
+      <c r="H169" s="3"/>
+      <c r="I169" s="3"/>
+      <c r="J169" s="6"/>
+      <c r="K169" s="3"/>
+      <c r="L169" s="3"/>
+      <c r="M169" s="3"/>
+    </row>
+    <row r="170" spans="1:13">
+      <c r="A170" s="3"/>
+      <c r="B170" s="3"/>
+      <c r="C170" s="3"/>
+      <c r="D170" s="3"/>
+      <c r="E170" s="3"/>
+      <c r="F170" s="3"/>
+      <c r="G170" s="3"/>
+      <c r="H170" s="3"/>
+      <c r="I170" s="3"/>
+      <c r="J170" s="6"/>
+      <c r="K170" s="3"/>
+      <c r="L170" s="3"/>
+      <c r="M170" s="3"/>
+    </row>
+    <row r="171" spans="1:13">
+      <c r="A171" s="3"/>
+      <c r="B171" s="3"/>
+      <c r="C171" s="3"/>
+      <c r="D171" s="3"/>
+      <c r="E171" s="3"/>
+      <c r="F171" s="3"/>
+      <c r="G171" s="3"/>
+      <c r="H171" s="3"/>
+      <c r="I171" s="3"/>
+      <c r="J171" s="6"/>
+      <c r="K171" s="3"/>
+      <c r="L171" s="3"/>
+      <c r="M171" s="3"/>
+    </row>
+    <row r="172" spans="1:13">
+      <c r="A172" s="3"/>
+      <c r="B172" s="3"/>
+      <c r="C172" s="3"/>
+      <c r="D172" s="3"/>
+      <c r="E172" s="3"/>
+      <c r="F172" s="3"/>
+      <c r="G172" s="3"/>
+      <c r="H172" s="3"/>
+      <c r="I172" s="3"/>
+      <c r="J172" s="6"/>
+      <c r="K172" s="3"/>
+      <c r="L172" s="3"/>
+      <c r="M172" s="3"/>
+    </row>
+    <row r="173" spans="1:13">
+      <c r="A173" s="3"/>
+      <c r="B173" s="3"/>
+      <c r="C173" s="3"/>
+      <c r="D173" s="3"/>
+      <c r="E173" s="3"/>
+      <c r="F173" s="3"/>
+      <c r="G173" s="3"/>
+      <c r="H173" s="3"/>
+      <c r="I173" s="3"/>
+      <c r="J173" s="6"/>
+      <c r="K173" s="3"/>
+      <c r="L173" s="3"/>
+      <c r="M173" s="3"/>
+    </row>
+    <row r="174" spans="1:13">
+      <c r="A174" s="3"/>
+      <c r="B174" s="3"/>
+      <c r="C174" s="3"/>
+      <c r="D174" s="3"/>
+      <c r="E174" s="3"/>
+      <c r="F174" s="3"/>
+      <c r="G174" s="3"/>
+      <c r="H174" s="3"/>
+      <c r="I174" s="3"/>
+      <c r="J174" s="6"/>
+      <c r="K174" s="3"/>
+      <c r="L174" s="3"/>
+      <c r="M174" s="3"/>
+    </row>
+    <row r="175" spans="1:13">
+      <c r="A175" s="3"/>
+      <c r="B175" s="3"/>
+      <c r="C175" s="3"/>
+      <c r="D175" s="3"/>
+      <c r="E175" s="3"/>
+      <c r="F175" s="3"/>
+      <c r="G175" s="3"/>
+      <c r="H175" s="3"/>
+      <c r="I175" s="3"/>
+      <c r="J175" s="6"/>
+      <c r="K175" s="3"/>
+      <c r="L175" s="3"/>
+      <c r="M175" s="3"/>
+    </row>
+    <row r="176" spans="1:13">
+      <c r="A176" s="3"/>
+      <c r="B176" s="3"/>
+      <c r="C176" s="3"/>
+      <c r="D176" s="3"/>
+      <c r="E176" s="3"/>
+      <c r="F176" s="3"/>
+      <c r="G176" s="3"/>
+      <c r="H176" s="3"/>
+      <c r="I176" s="3"/>
+      <c r="J176" s="6"/>
+      <c r="K176" s="3"/>
+      <c r="L176" s="3"/>
+      <c r="M176" s="3"/>
+    </row>
+    <row r="177" spans="1:13">
+      <c r="A177" s="3"/>
+      <c r="B177" s="3"/>
+      <c r="C177" s="3"/>
+      <c r="D177" s="3"/>
+      <c r="E177" s="3"/>
+      <c r="F177" s="3"/>
+      <c r="G177" s="3"/>
+      <c r="H177" s="3"/>
+      <c r="I177" s="3"/>
+      <c r="J177" s="6"/>
+      <c r="K177" s="3"/>
+      <c r="L177" s="3"/>
+      <c r="M177" s="3"/>
+    </row>
+    <row r="178" spans="1:13">
+      <c r="A178" s="3"/>
+      <c r="B178" s="3"/>
+      <c r="C178" s="3"/>
+      <c r="D178" s="3"/>
+      <c r="E178" s="3"/>
+      <c r="F178" s="3"/>
+      <c r="G178" s="3"/>
+      <c r="H178" s="3"/>
+      <c r="I178" s="3"/>
+      <c r="J178" s="6"/>
+      <c r="K178" s="3"/>
+      <c r="L178" s="3"/>
+      <c r="M178" s="3"/>
+    </row>
+    <row r="179" spans="1:13">
+      <c r="A179" s="3"/>
+      <c r="B179" s="3"/>
+      <c r="C179" s="3"/>
+      <c r="D179" s="3"/>
+      <c r="E179" s="3"/>
+      <c r="F179" s="3"/>
+      <c r="G179" s="3"/>
+      <c r="H179" s="3"/>
+      <c r="I179" s="3"/>
+      <c r="J179" s="6"/>
+      <c r="K179" s="3"/>
+      <c r="L179" s="3"/>
+      <c r="M179" s="3"/>
+    </row>
+    <row r="180" spans="1:13">
+      <c r="A180" s="3"/>
+      <c r="B180" s="3"/>
+      <c r="C180" s="3"/>
+      <c r="D180" s="3"/>
+      <c r="E180" s="3"/>
+      <c r="F180" s="3"/>
+      <c r="G180" s="3"/>
+      <c r="H180" s="3"/>
+      <c r="I180" s="3"/>
+      <c r="J180" s="6"/>
+      <c r="K180" s="3"/>
+      <c r="L180" s="3"/>
+      <c r="M180" s="3"/>
+    </row>
+    <row r="181" spans="1:13">
+      <c r="A181" s="3"/>
+      <c r="B181" s="3"/>
+      <c r="C181" s="3"/>
+      <c r="D181" s="3"/>
+      <c r="E181" s="3"/>
+      <c r="F181" s="3"/>
+      <c r="G181" s="3"/>
+      <c r="H181" s="3"/>
+      <c r="I181" s="3"/>
+      <c r="J181" s="6"/>
+      <c r="K181" s="3"/>
+      <c r="L181" s="3"/>
+      <c r="M181" s="3"/>
+    </row>
+    <row r="182" spans="1:13">
+      <c r="A182" s="3"/>
+      <c r="B182" s="3"/>
+      <c r="C182" s="3"/>
+      <c r="D182" s="3"/>
+      <c r="E182" s="3"/>
+      <c r="F182" s="3"/>
+      <c r="G182" s="3"/>
+      <c r="H182" s="3"/>
+      <c r="I182" s="3"/>
+      <c r="J182" s="6"/>
+      <c r="K182" s="3"/>
+      <c r="L182" s="3"/>
+      <c r="M182" s="3"/>
+    </row>
+    <row r="183" spans="1:13">
+      <c r="A183" s="3"/>
+      <c r="B183" s="3"/>
+      <c r="C183" s="3"/>
+      <c r="D183" s="3"/>
+      <c r="E183" s="3"/>
+      <c r="F183" s="3"/>
+      <c r="G183" s="3"/>
+      <c r="H183" s="3"/>
+      <c r="I183" s="3"/>
+      <c r="J183" s="6"/>
+      <c r="K183" s="3"/>
+      <c r="L183" s="3"/>
+      <c r="M183" s="3"/>
+    </row>
+    <row r="184" spans="1:13">
+      <c r="A184" s="3"/>
+      <c r="B184" s="3"/>
+      <c r="C184" s="3"/>
+      <c r="D184" s="3"/>
+      <c r="E184" s="3"/>
+      <c r="F184" s="3"/>
+      <c r="G184" s="3"/>
+      <c r="H184" s="3"/>
+      <c r="I184" s="3"/>
+      <c r="J184" s="6"/>
+      <c r="K184" s="3"/>
+      <c r="L184" s="3"/>
+      <c r="M184" s="3"/>
+    </row>
+    <row r="185" spans="1:13">
+      <c r="A185" s="3"/>
+      <c r="B185" s="3"/>
+      <c r="C185" s="3"/>
+      <c r="D185" s="3"/>
+      <c r="E185" s="3"/>
+      <c r="F185" s="3"/>
+      <c r="G185" s="3"/>
+      <c r="H185" s="3"/>
+      <c r="I185" s="3"/>
+      <c r="J185" s="6"/>
+      <c r="K185" s="3"/>
+      <c r="L185" s="3"/>
+      <c r="M185" s="3"/>
+    </row>
+    <row r="186" spans="1:13">
+      <c r="A186" s="3"/>
+      <c r="B186" s="3"/>
+      <c r="C186" s="3"/>
+      <c r="D186" s="3"/>
+      <c r="E186" s="3"/>
+      <c r="F186" s="3"/>
+      <c r="G186" s="3"/>
+      <c r="H186" s="3"/>
+      <c r="I186" s="3"/>
+      <c r="J186" s="6"/>
+      <c r="K186" s="3"/>
+      <c r="L186" s="3"/>
+      <c r="M186" s="3"/>
+    </row>
+    <row r="187" spans="1:13">
+      <c r="A187" s="3"/>
+      <c r="B187" s="3"/>
+      <c r="C187" s="3"/>
+      <c r="D187" s="3"/>
+      <c r="E187" s="3"/>
+      <c r="F187" s="3"/>
+      <c r="G187" s="3"/>
+      <c r="H187" s="3"/>
+      <c r="I187" s="3"/>
+      <c r="J187" s="6"/>
+      <c r="K187" s="3"/>
+      <c r="L187" s="3"/>
+      <c r="M187" s="3"/>
+    </row>
+    <row r="188" spans="1:13">
+      <c r="A188" s="3"/>
+      <c r="B188" s="3"/>
+      <c r="C188" s="3"/>
+      <c r="D188" s="3"/>
+      <c r="E188" s="3"/>
+      <c r="F188" s="3"/>
+      <c r="G188" s="3"/>
+      <c r="H188" s="3"/>
+      <c r="I188" s="3"/>
+      <c r="J188" s="6"/>
+      <c r="K188" s="3"/>
+      <c r="L188" s="3"/>
+      <c r="M188" s="3"/>
+    </row>
+    <row r="189" spans="1:13">
+      <c r="A189" s="3"/>
+      <c r="B189" s="3"/>
+      <c r="C189" s="3"/>
+      <c r="D189" s="3"/>
+      <c r="E189" s="3"/>
+      <c r="F189" s="3"/>
+      <c r="G189" s="3"/>
+      <c r="H189" s="3"/>
+      <c r="I189" s="3"/>
+      <c r="J189" s="6"/>
+      <c r="K189" s="3"/>
+      <c r="L189" s="3"/>
+      <c r="M189" s="3"/>
+    </row>
+    <row r="190" spans="1:13">
+      <c r="A190" s="3"/>
+      <c r="B190" s="3"/>
+      <c r="C190" s="3"/>
+      <c r="D190" s="3"/>
+      <c r="E190" s="3"/>
+      <c r="F190" s="3"/>
+      <c r="G190" s="3"/>
+      <c r="H190" s="3"/>
+      <c r="I190" s="3"/>
+      <c r="J190" s="6"/>
+      <c r="K190" s="3"/>
+      <c r="L190" s="3"/>
+      <c r="M190" s="3"/>
+    </row>
+    <row r="191" spans="1:13">
+      <c r="A191" s="3"/>
+      <c r="B191" s="3"/>
+      <c r="C191" s="3"/>
+      <c r="D191" s="3"/>
+      <c r="E191" s="3"/>
+      <c r="F191" s="3"/>
+      <c r="G191" s="3"/>
+      <c r="H191" s="3"/>
+      <c r="I191" s="3"/>
+      <c r="J191" s="6"/>
+      <c r="K191" s="3"/>
+      <c r="L191" s="3"/>
+      <c r="M191" s="3"/>
+    </row>
+    <row r="192" spans="1:13">
+      <c r="A192" s="3"/>
+      <c r="B192" s="3"/>
+      <c r="C192" s="3"/>
+      <c r="D192" s="3"/>
+      <c r="E192" s="3"/>
+      <c r="F192" s="3"/>
+      <c r="G192" s="3"/>
+      <c r="H192" s="3"/>
+      <c r="I192" s="3"/>
+      <c r="J192" s="6"/>
+      <c r="K192" s="3"/>
+      <c r="L192" s="3"/>
+      <c r="M192" s="3"/>
+    </row>
+    <row r="193" spans="1:13">
+      <c r="A193" s="3"/>
+      <c r="B193" s="3"/>
+      <c r="C193" s="3"/>
+      <c r="D193" s="3"/>
+      <c r="E193" s="3"/>
+      <c r="F193" s="3"/>
+      <c r="G193" s="3"/>
+      <c r="H193" s="3"/>
+      <c r="I193" s="3"/>
+      <c r="J193" s="6"/>
+      <c r="K193" s="3"/>
+      <c r="L193" s="3"/>
+      <c r="M193" s="3"/>
+    </row>
+    <row r="194" spans="1:13">
+      <c r="A194" s="3"/>
+      <c r="B194" s="3"/>
+      <c r="C194" s="3"/>
+      <c r="D194" s="3"/>
+      <c r="E194" s="3"/>
+      <c r="F194" s="3"/>
+      <c r="G194" s="3"/>
+      <c r="H194" s="3"/>
+      <c r="I194" s="3"/>
+      <c r="J194" s="6"/>
+      <c r="K194" s="3"/>
+      <c r="L194" s="3"/>
+      <c r="M194" s="3"/>
+    </row>
+    <row r="195" spans="1:13">
+      <c r="A195" s="3"/>
+      <c r="B195" s="3"/>
+      <c r="C195" s="3"/>
+      <c r="D195" s="3"/>
+      <c r="E195" s="3"/>
+      <c r="F195" s="3"/>
+      <c r="G195" s="3"/>
+      <c r="H195" s="3"/>
+      <c r="I195" s="3"/>
+      <c r="J195" s="6"/>
+      <c r="K195" s="3"/>
+      <c r="L195" s="3"/>
+      <c r="M195" s="3"/>
+    </row>
+    <row r="196" spans="1:13">
+      <c r="A196" s="3"/>
+      <c r="B196" s="3"/>
+      <c r="C196" s="3"/>
+      <c r="D196" s="3"/>
+      <c r="E196" s="3"/>
+      <c r="F196" s="3"/>
+      <c r="G196" s="3"/>
+      <c r="H196" s="3"/>
+      <c r="I196" s="3"/>
+      <c r="J196" s="6"/>
+      <c r="K196" s="3"/>
+      <c r="L196" s="3"/>
+      <c r="M196" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -7332,13 +8847,13 @@
           <x14:formula1>
             <xm:f>'Tipo de norma'!$A$1:$A$10</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D109 D111:D1048576</xm:sqref>
+          <xm:sqref>D2:D109 D111:D1048576 E140</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{EF828923-8993-5646-A9D3-B4E6E4049B2E}">
           <x14:formula1>
             <xm:f>Estado!$A$1:$A$3</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E1048576</xm:sqref>
+          <xm:sqref>E2:E139 E141:E1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{010CCE2F-A20E-E249-89B6-2FD5F86ADDCB}">
           <x14:formula1>
@@ -7350,7 +8865,7 @@
           <x14:formula1>
             <xm:f>'Dedicacion del texto'!$A$1:$A$4</xm:f>
           </x14:formula1>
-          <xm:sqref>I2:I1048576</xm:sqref>
+          <xm:sqref>I2:I1048576 J121</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{78262786-E61E-8940-BCEE-286BD25672E3}">
           <x14:formula1>
@@ -7380,7 +8895,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="15.6">
       <c r="A1" s="1" t="s">
-        <v>495</v>
+        <v>602</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="15.6">
@@ -7390,157 +8905,157 @@
     </row>
     <row r="3" spans="1:1" ht="15.6">
       <c r="A3" s="1" t="s">
-        <v>496</v>
+        <v>603</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="15.6">
       <c r="A4" s="1" t="s">
-        <v>497</v>
+        <v>604</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="15.6">
       <c r="A5" s="1" t="s">
-        <v>498</v>
+        <v>605</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="15.6">
       <c r="A6" s="1" t="s">
-        <v>499</v>
+        <v>606</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="15.6">
       <c r="A7" s="1" t="s">
-        <v>500</v>
+        <v>607</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="15.6">
       <c r="A8" s="1" t="s">
-        <v>501</v>
+        <v>608</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="15.6">
       <c r="A9" s="1" t="s">
-        <v>502</v>
+        <v>609</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="15.6">
       <c r="A10" s="1" t="s">
-        <v>503</v>
+        <v>610</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="15.6">
       <c r="A11" s="1" t="s">
-        <v>504</v>
+        <v>611</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="15.6">
       <c r="A12" s="1" t="s">
-        <v>505</v>
+        <v>612</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="15.6">
       <c r="A13" s="1" t="s">
-        <v>506</v>
+        <v>613</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="15.6">
       <c r="A14" s="1" t="s">
-        <v>507</v>
+        <v>614</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="15.6">
       <c r="A15" s="1" t="s">
-        <v>508</v>
+        <v>615</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="15.6">
       <c r="A16" s="1" t="s">
-        <v>509</v>
+        <v>616</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="15.6">
       <c r="A17" s="1" t="s">
-        <v>510</v>
+        <v>617</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15.6">
       <c r="A18" s="1" t="s">
-        <v>511</v>
+        <v>618</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="15.6">
       <c r="A19" s="1" t="s">
-        <v>512</v>
+        <v>619</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15.6">
       <c r="A20" s="1" t="s">
-        <v>513</v>
+        <v>620</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="15.6">
       <c r="A21" s="1" t="s">
-        <v>514</v>
+        <v>621</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="15.6">
       <c r="A22" s="1" t="s">
-        <v>515</v>
+        <v>622</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="15.6">
       <c r="A23" s="1" t="s">
-        <v>516</v>
+        <v>623</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="15.6">
       <c r="A24" s="1" t="s">
-        <v>517</v>
+        <v>624</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="15.6">
       <c r="A25" s="1" t="s">
-        <v>518</v>
+        <v>625</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="15.6">
       <c r="A26" s="1" t="s">
-        <v>519</v>
+        <v>626</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="15.6">
       <c r="A27" s="1" t="s">
-        <v>520</v>
+        <v>627</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="15.6">
       <c r="A28" s="1" t="s">
-        <v>521</v>
+        <v>628</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="15.6">
       <c r="A29" s="1" t="s">
-        <v>522</v>
+        <v>629</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="15.6">
       <c r="A30" s="1" t="s">
-        <v>523</v>
+        <v>630</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="15.6">
       <c r="A31" s="1" t="s">
-        <v>524</v>
+        <v>631</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="15.6">
       <c r="A32" s="1" t="s">
-        <v>525</v>
+        <v>632</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="15.6">
       <c r="A33" s="1" t="s">
-        <v>526</v>
+        <v>633</v>
       </c>
     </row>
   </sheetData>
@@ -7561,7 +9076,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>527</v>
+        <v>634</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -7630,7 +9145,7 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>528</v>
+        <v>635</v>
       </c>
     </row>
   </sheetData>

--- a/data/Matriz_Normativa_IA_Educacion_LATAM.xlsx
+++ b/data/Matriz_Normativa_IA_Educacion_LATAM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tecmx-my.sharepoint.com/personal/a00834778_tec_mx/Documents/Desktop/Carlos Auquilla/Proyectos/GENIAL/GENIAL_dev/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="516" documentId="8_{DEF93B8B-1B75-490B-94A3-E0F7B496BF87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01A1E41A-7E50-4619-9288-697E84FF4B8E}"/>
+  <xr:revisionPtr revIDLastSave="519" documentId="8_{DEF93B8B-1B75-490B-94A3-E0F7B496BF87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27FC3849-7F1D-48D7-8A84-10F6EC45A0B6}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2141" uniqueCount="686">
   <si>
-    <t>Gaceta</t>
+    <t>Investigador</t>
   </si>
   <si>
     <t>País</t>
@@ -2599,7 +2599,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:M196"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
   <cols>
@@ -2659,7 +2658,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15" hidden="1">
+    <row r="2" spans="1:13" ht="15">
       <c r="A2" s="3" t="s">
         <v>13</v>
       </c>
@@ -2701,7 +2700,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="15" hidden="1">
+    <row r="3" spans="1:13" ht="15">
       <c r="A3" s="3" t="s">
         <v>25</v>
       </c>
@@ -2742,7 +2741,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="15" hidden="1">
+    <row r="4" spans="1:13" ht="15">
       <c r="A4" s="3" t="s">
         <v>34</v>
       </c>
@@ -2783,7 +2782,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="15" hidden="1">
+    <row r="5" spans="1:13" ht="15">
       <c r="A5" s="3" t="s">
         <v>41</v>
       </c>
@@ -2824,7 +2823,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="15" hidden="1">
+    <row r="6" spans="1:13" ht="15">
       <c r="A6" s="3" t="s">
         <v>41</v>
       </c>
@@ -2865,7 +2864,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="15" hidden="1">
+    <row r="7" spans="1:13" ht="15">
       <c r="A7" s="3" t="s">
         <v>41</v>
       </c>
@@ -2906,7 +2905,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="15" hidden="1">
+    <row r="8" spans="1:13" ht="15">
       <c r="A8" s="3" t="s">
         <v>41</v>
       </c>
@@ -2947,7 +2946,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="15" hidden="1">
+    <row r="9" spans="1:13" ht="15">
       <c r="A9" s="3" t="s">
         <v>41</v>
       </c>
@@ -2988,7 +2987,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15" hidden="1">
+    <row r="10" spans="1:13" ht="15">
       <c r="A10" s="3" t="s">
         <v>41</v>
       </c>
@@ -3029,7 +3028,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15" hidden="1">
+    <row r="11" spans="1:13" ht="15">
       <c r="A11" s="3" t="s">
         <v>41</v>
       </c>
@@ -3070,7 +3069,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="15" hidden="1">
+    <row r="12" spans="1:13" ht="15">
       <c r="A12" s="3" t="s">
         <v>41</v>
       </c>
@@ -3111,7 +3110,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="15" hidden="1">
+    <row r="13" spans="1:13" ht="15">
       <c r="A13" s="3" t="s">
         <v>41</v>
       </c>
@@ -3152,7 +3151,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="15" hidden="1">
+    <row r="14" spans="1:13" ht="15">
       <c r="A14" s="3" t="s">
         <v>41</v>
       </c>
@@ -3193,7 +3192,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="15" hidden="1">
+    <row r="15" spans="1:13" ht="15">
       <c r="A15" s="3" t="s">
         <v>41</v>
       </c>
@@ -3234,7 +3233,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="15" hidden="1">
+    <row r="16" spans="1:13" ht="15">
       <c r="A16" s="3" t="s">
         <v>41</v>
       </c>
@@ -3275,7 +3274,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="60.75" hidden="1">
+    <row r="17" spans="1:13" ht="60.75">
       <c r="A17" s="3" t="s">
         <v>41</v>
       </c>
@@ -3316,7 +3315,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="60.75" hidden="1">
+    <row r="18" spans="1:13" ht="60.75">
       <c r="A18" s="3" t="s">
         <v>41</v>
       </c>
@@ -3357,7 +3356,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="60.75" hidden="1">
+    <row r="19" spans="1:13" ht="60.75">
       <c r="A19" s="3" t="s">
         <v>41</v>
       </c>
@@ -3398,7 +3397,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="15" hidden="1">
+    <row r="20" spans="1:13" ht="15">
       <c r="A20" s="3" t="s">
         <v>41</v>
       </c>
@@ -3439,7 +3438,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="15" hidden="1">
+    <row r="21" spans="1:13" ht="15">
       <c r="A21" s="3" t="s">
         <v>41</v>
       </c>
@@ -3480,7 +3479,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="15" hidden="1">
+    <row r="22" spans="1:13" ht="15">
       <c r="A22" s="3" t="s">
         <v>41</v>
       </c>
@@ -3521,7 +3520,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="13.5" hidden="1" customHeight="1">
+    <row r="23" spans="1:13" ht="13.5" customHeight="1">
       <c r="A23" s="3" t="s">
         <v>41</v>
       </c>
@@ -3562,7 +3561,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="15" hidden="1">
+    <row r="24" spans="1:13" ht="15">
       <c r="A24" s="3" t="s">
         <v>41</v>
       </c>
@@ -3603,7 +3602,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="15" hidden="1">
+    <row r="25" spans="1:13" ht="15">
       <c r="A25" s="3" t="s">
         <v>41</v>
       </c>
@@ -3644,7 +3643,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="15" hidden="1">
+    <row r="26" spans="1:13" ht="15">
       <c r="A26" s="3" t="s">
         <v>41</v>
       </c>
@@ -3685,7 +3684,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="15" hidden="1">
+    <row r="27" spans="1:13" ht="15">
       <c r="A27" s="10" t="s">
         <v>41</v>
       </c>
@@ -3726,7 +3725,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="15" hidden="1">
+    <row r="28" spans="1:13" ht="15">
       <c r="A28" s="3" t="s">
         <v>41</v>
       </c>
@@ -3767,7 +3766,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="15" hidden="1">
+    <row r="29" spans="1:13" ht="15">
       <c r="A29" s="3" t="s">
         <v>41</v>
       </c>
@@ -3808,7 +3807,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="15" hidden="1">
+    <row r="30" spans="1:13" ht="15">
       <c r="A30" s="3" t="s">
         <v>41</v>
       </c>
@@ -3849,7 +3848,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="15" hidden="1">
+    <row r="31" spans="1:13" ht="15">
       <c r="A31" s="3" t="s">
         <v>41</v>
       </c>
@@ -3890,7 +3889,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="15" hidden="1">
+    <row r="32" spans="1:13" ht="15">
       <c r="A32" s="3" t="s">
         <v>41</v>
       </c>
@@ -3931,7 +3930,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="15" hidden="1">
+    <row r="33" spans="1:13" ht="15">
       <c r="A33" s="3" t="s">
         <v>41</v>
       </c>
@@ -3972,7 +3971,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="15" hidden="1">
+    <row r="34" spans="1:13" ht="15">
       <c r="A34" s="3" t="s">
         <v>41</v>
       </c>
@@ -4013,7 +4012,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="15" hidden="1">
+    <row r="35" spans="1:13" ht="15">
       <c r="A35" s="3" t="s">
         <v>41</v>
       </c>
@@ -4054,7 +4053,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="15" hidden="1">
+    <row r="36" spans="1:13" ht="15">
       <c r="A36" s="3" t="s">
         <v>41</v>
       </c>
@@ -4095,7 +4094,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="15" hidden="1">
+    <row r="37" spans="1:13" ht="15">
       <c r="A37" s="3" t="s">
         <v>41</v>
       </c>
@@ -4136,7 +4135,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="15" hidden="1">
+    <row r="38" spans="1:13" ht="15">
       <c r="A38" s="3" t="s">
         <v>41</v>
       </c>
@@ -4177,7 +4176,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="15" hidden="1">
+    <row r="39" spans="1:13" ht="15">
       <c r="A39" s="3" t="s">
         <v>41</v>
       </c>
@@ -4218,7 +4217,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="15" hidden="1">
+    <row r="40" spans="1:13" ht="15">
       <c r="A40" s="3" t="s">
         <v>41</v>
       </c>
@@ -4259,7 +4258,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="15" hidden="1">
+    <row r="41" spans="1:13" ht="15">
       <c r="A41" s="3" t="s">
         <v>41</v>
       </c>
@@ -4300,7 +4299,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="15" hidden="1">
+    <row r="42" spans="1:13" ht="15">
       <c r="A42" s="3" t="s">
         <v>41</v>
       </c>
@@ -4341,7 +4340,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="15" hidden="1">
+    <row r="43" spans="1:13" ht="15">
       <c r="A43" s="3" t="s">
         <v>41</v>
       </c>
@@ -4382,7 +4381,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="15" hidden="1">
+    <row r="44" spans="1:13" ht="15">
       <c r="A44" s="3" t="s">
         <v>41</v>
       </c>
@@ -4423,7 +4422,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="15" hidden="1">
+    <row r="45" spans="1:13" ht="15">
       <c r="A45" s="3" t="s">
         <v>41</v>
       </c>
@@ -4464,7 +4463,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="15" hidden="1">
+    <row r="46" spans="1:13" ht="15">
       <c r="A46" s="3" t="s">
         <v>41</v>
       </c>
@@ -4505,7 +4504,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="15" hidden="1">
+    <row r="47" spans="1:13" ht="15">
       <c r="A47" s="3" t="s">
         <v>41</v>
       </c>
@@ -4546,7 +4545,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="15" hidden="1">
+    <row r="48" spans="1:13" ht="15">
       <c r="A48" s="3" t="s">
         <v>41</v>
       </c>
@@ -4587,7 +4586,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="49" spans="1:13" ht="15" hidden="1">
+    <row r="49" spans="1:13" ht="15">
       <c r="A49" s="3" t="s">
         <v>41</v>
       </c>
@@ -4628,7 +4627,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="15" hidden="1">
+    <row r="50" spans="1:13" ht="15">
       <c r="A50" s="3" t="s">
         <v>41</v>
       </c>
@@ -4669,7 +4668,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="15" hidden="1">
+    <row r="51" spans="1:13" ht="15">
       <c r="A51" s="3" t="s">
         <v>41</v>
       </c>
@@ -4710,7 +4709,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="52" spans="1:13" ht="15" hidden="1">
+    <row r="52" spans="1:13" ht="15">
       <c r="A52" s="3" t="s">
         <v>41</v>
       </c>
@@ -4751,7 +4750,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="15" hidden="1">
+    <row r="53" spans="1:13" ht="15">
       <c r="A53" s="3" t="s">
         <v>41</v>
       </c>
@@ -4792,7 +4791,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="15" hidden="1">
+    <row r="54" spans="1:13" ht="15">
       <c r="A54" s="3" t="s">
         <v>41</v>
       </c>
@@ -4833,7 +4832,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="55" spans="1:13" ht="15" hidden="1">
+    <row r="55" spans="1:13" ht="15">
       <c r="A55" s="3" t="s">
         <v>41</v>
       </c>
@@ -4874,7 +4873,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="56" spans="1:13" ht="15" hidden="1">
+    <row r="56" spans="1:13" ht="15">
       <c r="A56" s="3" t="s">
         <v>41</v>
       </c>
@@ -4915,7 +4914,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="57" spans="1:13" ht="15" hidden="1">
+    <row r="57" spans="1:13" ht="15">
       <c r="A57" s="3" t="s">
         <v>41</v>
       </c>
@@ -4956,7 +4955,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="58" spans="1:13" ht="15" hidden="1">
+    <row r="58" spans="1:13" ht="15">
       <c r="A58" s="3" t="s">
         <v>41</v>
       </c>
@@ -4997,7 +4996,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="60.75" hidden="1">
+    <row r="59" spans="1:13" ht="60.75">
       <c r="A59" s="3" t="s">
         <v>41</v>
       </c>
@@ -5038,7 +5037,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="60" spans="1:13" ht="15" hidden="1">
+    <row r="60" spans="1:13" ht="15">
       <c r="A60" s="3" t="s">
         <v>41</v>
       </c>
@@ -5079,7 +5078,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="61" spans="1:13" ht="15" hidden="1">
+    <row r="61" spans="1:13" ht="15">
       <c r="A61" s="3" t="s">
         <v>41</v>
       </c>
@@ -5120,7 +5119,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="15" hidden="1">
+    <row r="62" spans="1:13" ht="15">
       <c r="A62" s="3" t="s">
         <v>41</v>
       </c>
@@ -5161,7 +5160,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="63" spans="1:13" ht="15" hidden="1">
+    <row r="63" spans="1:13" ht="15">
       <c r="A63" s="3" t="s">
         <v>41</v>
       </c>
@@ -5202,7 +5201,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="64" spans="1:13" ht="30.75" hidden="1">
+    <row r="64" spans="1:13" ht="30.75">
       <c r="A64" s="3" t="s">
         <v>41</v>
       </c>
@@ -5243,7 +5242,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="65" spans="1:13" ht="15" hidden="1">
+    <row r="65" spans="1:13" ht="15">
       <c r="A65" s="3" t="s">
         <v>41</v>
       </c>
@@ -5284,7 +5283,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="66" spans="1:13" ht="15" hidden="1">
+    <row r="66" spans="1:13" ht="15">
       <c r="A66" s="3" t="s">
         <v>41</v>
       </c>
@@ -5325,7 +5324,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="67" spans="1:13" ht="15" hidden="1">
+    <row r="67" spans="1:13" ht="15">
       <c r="A67" s="3" t="s">
         <v>41</v>
       </c>
@@ -5366,7 +5365,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="68" spans="1:13" ht="15" hidden="1">
+    <row r="68" spans="1:13" ht="15">
       <c r="A68" s="3" t="s">
         <v>41</v>
       </c>
@@ -5407,7 +5406,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="15" hidden="1">
+    <row r="69" spans="1:13" ht="15">
       <c r="A69" s="3" t="s">
         <v>41</v>
       </c>
@@ -5448,7 +5447,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="30.75" hidden="1">
+    <row r="70" spans="1:13" ht="30.75">
       <c r="A70" s="3" t="s">
         <v>41</v>
       </c>
@@ -5489,7 +5488,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="71" spans="1:13" ht="24.75" hidden="1" customHeight="1">
+    <row r="71" spans="1:13" ht="24.75" customHeight="1">
       <c r="A71" s="3" t="s">
         <v>41</v>
       </c>
@@ -5530,7 +5529,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="30.75" hidden="1">
+    <row r="72" spans="1:13" ht="30.75">
       <c r="A72" s="3" t="s">
         <v>41</v>
       </c>
@@ -5571,7 +5570,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="30.75" hidden="1">
+    <row r="73" spans="1:13" ht="30.75">
       <c r="A73" s="3" t="s">
         <v>41</v>
       </c>
@@ -5612,7 +5611,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="74" spans="1:13" ht="15" hidden="1">
+    <row r="74" spans="1:13" ht="15">
       <c r="A74" s="3" t="s">
         <v>41</v>
       </c>
@@ -5653,7 +5652,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="75" spans="1:13" ht="30.75" hidden="1">
+    <row r="75" spans="1:13" ht="30.75">
       <c r="A75" s="3" t="s">
         <v>41</v>
       </c>
@@ -5694,7 +5693,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="76" spans="1:13" ht="30.75" hidden="1">
+    <row r="76" spans="1:13" ht="30.75">
       <c r="A76" s="3" t="s">
         <v>41</v>
       </c>
@@ -5735,7 +5734,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="77" spans="1:13" ht="30.75" hidden="1">
+    <row r="77" spans="1:13" ht="30.75">
       <c r="A77" s="3" t="s">
         <v>41</v>
       </c>
@@ -5776,7 +5775,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="78" spans="1:13" ht="30.75" hidden="1">
+    <row r="78" spans="1:13" ht="30.75">
       <c r="A78" s="3" t="s">
         <v>41</v>
       </c>
@@ -5817,7 +5816,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="79" spans="1:13" ht="15" hidden="1">
+    <row r="79" spans="1:13" ht="15">
       <c r="A79" s="3" t="s">
         <v>41</v>
       </c>
@@ -5858,7 +5857,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="80" spans="1:13" ht="30.75" hidden="1">
+    <row r="80" spans="1:13" ht="30.75">
       <c r="A80" s="3" t="s">
         <v>41</v>
       </c>
@@ -5899,7 +5898,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="81" spans="1:13" ht="30.75" hidden="1">
+    <row r="81" spans="1:13" ht="30.75">
       <c r="A81" s="3" t="s">
         <v>41</v>
       </c>
@@ -5940,7 +5939,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="82" spans="1:13" ht="15" hidden="1">
+    <row r="82" spans="1:13" ht="15">
       <c r="A82" s="3" t="s">
         <v>41</v>
       </c>
@@ -5981,7 +5980,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="83" spans="1:13" ht="167.25" hidden="1">
+    <row r="83" spans="1:13" ht="167.25">
       <c r="A83" s="3" t="s">
         <v>41</v>
       </c>
@@ -6022,7 +6021,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="84" spans="1:13" ht="213" hidden="1">
+    <row r="84" spans="1:13" ht="213">
       <c r="A84" s="3" t="s">
         <v>41</v>
       </c>
@@ -6063,7 +6062,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="85" spans="1:13" ht="167.25" hidden="1">
+    <row r="85" spans="1:13" ht="167.25">
       <c r="A85" s="3" t="s">
         <v>41</v>
       </c>
@@ -6104,7 +6103,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="86" spans="1:13" ht="183" hidden="1">
+    <row r="86" spans="1:13" ht="183">
       <c r="A86" s="3" t="s">
         <v>41</v>
       </c>
@@ -6145,7 +6144,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="87" spans="1:13" ht="137.25" hidden="1">
+    <row r="87" spans="1:13" ht="137.25">
       <c r="A87" s="3" t="s">
         <v>41</v>
       </c>
@@ -6186,7 +6185,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="88" spans="1:13" ht="198" hidden="1">
+    <row r="88" spans="1:13" ht="198">
       <c r="A88" s="3" t="s">
         <v>41</v>
       </c>
@@ -6227,7 +6226,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="89" spans="1:13" ht="152.25" hidden="1">
+    <row r="89" spans="1:13" ht="152.25">
       <c r="A89" s="3" t="s">
         <v>41</v>
       </c>
@@ -6268,7 +6267,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="90" spans="1:13" ht="183" hidden="1">
+    <row r="90" spans="1:13" ht="183">
       <c r="A90" s="3" t="s">
         <v>41</v>
       </c>
@@ -6309,7 +6308,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="91" spans="1:13" ht="213" hidden="1">
+    <row r="91" spans="1:13" ht="213">
       <c r="A91" s="3" t="s">
         <v>41</v>
       </c>
@@ -6350,7 +6349,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="92" spans="1:13" ht="121.5" hidden="1">
+    <row r="92" spans="1:13" ht="121.5">
       <c r="A92" s="3" t="s">
         <v>41</v>
       </c>
@@ -6391,7 +6390,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="93" spans="1:13" ht="91.5" hidden="1">
+    <row r="93" spans="1:13" ht="91.5">
       <c r="A93" s="3" t="s">
         <v>41</v>
       </c>
@@ -6432,7 +6431,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="94" spans="1:13" ht="198" hidden="1">
+    <row r="94" spans="1:13" ht="198">
       <c r="A94" s="3" t="s">
         <v>41</v>
       </c>
@@ -6473,7 +6472,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="95" spans="1:13" ht="137.25" hidden="1">
+    <row r="95" spans="1:13" ht="137.25">
       <c r="A95" s="3" t="s">
         <v>41</v>
       </c>
@@ -6514,7 +6513,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="96" spans="1:13" ht="76.5" hidden="1">
+    <row r="96" spans="1:13" ht="76.5">
       <c r="A96" s="3" t="s">
         <v>41</v>
       </c>
@@ -6555,7 +6554,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="97" spans="1:13" ht="121.5" hidden="1">
+    <row r="97" spans="1:13" ht="121.5">
       <c r="A97" s="3" t="s">
         <v>41</v>
       </c>
@@ -6596,7 +6595,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="98" spans="1:13" ht="183" hidden="1">
+    <row r="98" spans="1:13" ht="183">
       <c r="A98" s="3" t="s">
         <v>41</v>
       </c>
@@ -6637,7 +6636,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="99" spans="1:13" ht="183" hidden="1">
+    <row r="99" spans="1:13" ht="183">
       <c r="A99" s="3" t="s">
         <v>41</v>
       </c>
@@ -6678,7 +6677,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="100" spans="1:13" ht="152.25" hidden="1">
+    <row r="100" spans="1:13" ht="152.25">
       <c r="A100" s="3" t="s">
         <v>41</v>
       </c>
@@ -6719,7 +6718,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="101" spans="1:13" ht="121.5" hidden="1">
+    <row r="101" spans="1:13" ht="121.5">
       <c r="A101" s="3" t="s">
         <v>41</v>
       </c>
@@ -6760,7 +6759,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="102" spans="1:13" ht="30.75" hidden="1">
+    <row r="102" spans="1:13" ht="30.75">
       <c r="A102" s="3" t="s">
         <v>41</v>
       </c>
@@ -6801,7 +6800,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="103" spans="1:13" ht="15" hidden="1">
+    <row r="103" spans="1:13" ht="15">
       <c r="A103" s="3" t="s">
         <v>41</v>
       </c>
@@ -6842,7 +6841,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="104" spans="1:13" ht="30.75" hidden="1">
+    <row r="104" spans="1:13" ht="30.75">
       <c r="A104" s="3" t="s">
         <v>41</v>
       </c>
@@ -6883,7 +6882,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="105" spans="1:13" ht="15" hidden="1">
+    <row r="105" spans="1:13" ht="15">
       <c r="A105" s="3" t="s">
         <v>41</v>
       </c>
@@ -6924,7 +6923,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="106" spans="1:13" ht="15" hidden="1">
+    <row r="106" spans="1:13" ht="15">
       <c r="A106" s="3" t="s">
         <v>41</v>
       </c>
@@ -6965,7 +6964,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="107" spans="1:13" ht="15" hidden="1">
+    <row r="107" spans="1:13" ht="15">
       <c r="A107" s="3" t="s">
         <v>41</v>
       </c>
@@ -7006,7 +7005,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="108" spans="1:13" ht="30.75" hidden="1">
+    <row r="108" spans="1:13" ht="30.75">
       <c r="A108" s="3" t="s">
         <v>41</v>
       </c>
@@ -7047,7 +7046,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="109" spans="1:13" ht="30.75" hidden="1">
+    <row r="109" spans="1:13" ht="30.75">
       <c r="A109" s="3" t="s">
         <v>41</v>
       </c>
@@ -7088,7 +7087,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="110" spans="1:13" ht="30.75" hidden="1">
+    <row r="110" spans="1:13" ht="30.75">
       <c r="A110" s="3" t="s">
         <v>41</v>
       </c>
@@ -7129,7 +7128,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="111" spans="1:13" ht="15" hidden="1">
+    <row r="111" spans="1:13" ht="15">
       <c r="A111" s="3" t="s">
         <v>41</v>
       </c>
@@ -7170,7 +7169,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="112" spans="1:13" ht="30.75" hidden="1">
+    <row r="112" spans="1:13" ht="30.75">
       <c r="A112" s="3" t="s">
         <v>41</v>
       </c>
@@ -7211,7 +7210,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="113" spans="1:13" ht="30.75" hidden="1">
+    <row r="113" spans="1:13" ht="30.75">
       <c r="A113" s="3" t="s">
         <v>41</v>
       </c>
@@ -7252,7 +7251,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="114" spans="1:13" ht="30.75" hidden="1">
+    <row r="114" spans="1:13" ht="30.75">
       <c r="A114" s="3" t="s">
         <v>41</v>
       </c>
@@ -7293,7 +7292,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="115" spans="1:13" ht="15" hidden="1">
+    <row r="115" spans="1:13" ht="15">
       <c r="A115" s="3" t="s">
         <v>41</v>
       </c>
@@ -7334,7 +7333,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="116" spans="1:13" ht="15" hidden="1">
+    <row r="116" spans="1:13" ht="15">
       <c r="A116" s="3" t="s">
         <v>41</v>
       </c>
@@ -7375,7 +7374,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="117" spans="1:13" ht="30.75" hidden="1">
+    <row r="117" spans="1:13" ht="30.75">
       <c r="A117" s="3" t="s">
         <v>41</v>
       </c>
@@ -7416,7 +7415,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="118" spans="1:13" ht="30.75" hidden="1">
+    <row r="118" spans="1:13" ht="30.75">
       <c r="A118" s="3" t="s">
         <v>41</v>
       </c>
@@ -7457,7 +7456,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="119" spans="1:13" ht="30.75" hidden="1">
+    <row r="119" spans="1:13" ht="30.75">
       <c r="A119" s="3" t="s">
         <v>41</v>
       </c>
@@ -7498,7 +7497,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="120" spans="1:13" ht="30.75" hidden="1">
+    <row r="120" spans="1:13" ht="30.75">
       <c r="A120" s="3" t="s">
         <v>41</v>
       </c>
@@ -7539,7 +7538,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="121" spans="1:13" ht="15" hidden="1">
+    <row r="121" spans="1:13" ht="15">
       <c r="A121" s="3" t="s">
         <v>41</v>
       </c>
@@ -7580,7 +7579,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="122" spans="1:13" ht="152.25" hidden="1">
+    <row r="122" spans="1:13" ht="152.25">
       <c r="A122" s="3" t="s">
         <v>41</v>
       </c>
@@ -7621,7 +7620,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="123" spans="1:13" ht="121.5" hidden="1">
+    <row r="123" spans="1:13" ht="121.5">
       <c r="A123" s="3" t="s">
         <v>41</v>
       </c>
@@ -7662,7 +7661,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="124" spans="1:13" ht="167.25" hidden="1">
+    <row r="124" spans="1:13" ht="167.25">
       <c r="A124" s="3" t="s">
         <v>41</v>
       </c>
@@ -7703,7 +7702,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="125" spans="1:13" ht="183" hidden="1">
+    <row r="125" spans="1:13" ht="183">
       <c r="A125" s="3" t="s">
         <v>41</v>
       </c>
@@ -7744,7 +7743,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="126" spans="1:13" ht="183" hidden="1">
+    <row r="126" spans="1:13" ht="183">
       <c r="A126" s="3" t="s">
         <v>41</v>
       </c>
@@ -7785,7 +7784,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="127" spans="1:13" ht="121.5" hidden="1">
+    <row r="127" spans="1:13" ht="121.5">
       <c r="A127" s="3" t="s">
         <v>41</v>
       </c>
@@ -7826,7 +7825,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="128" spans="1:13" ht="167.25" hidden="1">
+    <row r="128" spans="1:13" ht="167.25">
       <c r="A128" s="3" t="s">
         <v>41</v>
       </c>
@@ -7867,7 +7866,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="129" spans="1:13" ht="137.25" hidden="1">
+    <row r="129" spans="1:13" ht="137.25">
       <c r="A129" s="3" t="s">
         <v>41</v>
       </c>
@@ -7908,7 +7907,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="130" spans="1:13" ht="167.25" hidden="1">
+    <row r="130" spans="1:13" ht="167.25">
       <c r="A130" s="3" t="s">
         <v>41</v>
       </c>
@@ -7949,7 +7948,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="131" spans="1:13" ht="121.5" hidden="1">
+    <row r="131" spans="1:13" ht="121.5">
       <c r="A131" s="3" t="s">
         <v>41</v>
       </c>
@@ -7990,7 +7989,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="132" spans="1:13" ht="137.25" hidden="1">
+    <row r="132" spans="1:13" ht="137.25">
       <c r="A132" s="3" t="s">
         <v>41</v>
       </c>
@@ -8031,7 +8030,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="133" spans="1:13" ht="121.5" hidden="1">
+    <row r="133" spans="1:13" ht="121.5">
       <c r="A133" s="3" t="s">
         <v>41</v>
       </c>
@@ -8072,7 +8071,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="134" spans="1:13" ht="137.25" hidden="1">
+    <row r="134" spans="1:13" ht="137.25">
       <c r="A134" s="3" t="s">
         <v>41</v>
       </c>
@@ -8113,7 +8112,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="135" spans="1:13" ht="167.25" hidden="1">
+    <row r="135" spans="1:13" ht="167.25">
       <c r="A135" s="3" t="s">
         <v>41</v>
       </c>
@@ -8195,7 +8194,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="137" spans="1:13" ht="152.25" hidden="1">
+    <row r="137" spans="1:13" ht="152.25">
       <c r="A137" s="3" t="s">
         <v>41</v>
       </c>
@@ -8236,7 +8235,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="138" spans="1:13" ht="167.25" hidden="1">
+    <row r="138" spans="1:13" ht="167.25">
       <c r="A138" s="3" t="s">
         <v>41</v>
       </c>
@@ -8277,7 +8276,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="139" spans="1:13" ht="167.25" hidden="1">
+    <row r="139" spans="1:13" ht="167.25">
       <c r="A139" s="3" t="s">
         <v>41</v>
       </c>
@@ -8318,7 +8317,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="140" spans="1:13" ht="167.25" hidden="1">
+    <row r="140" spans="1:13" ht="167.25">
       <c r="A140" s="3" t="s">
         <v>41</v>
       </c>
@@ -8359,7 +8358,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="141" spans="1:13" ht="167.25" hidden="1">
+    <row r="141" spans="1:13" ht="167.25">
       <c r="A141" s="3" t="s">
         <v>41</v>
       </c>
@@ -8400,7 +8399,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="142" spans="1:13" ht="167.25" hidden="1">
+    <row r="142" spans="1:13" ht="167.25">
       <c r="A142" s="3" t="s">
         <v>41</v>
       </c>
@@ -8441,7 +8440,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="143" spans="1:13" ht="121.5" hidden="1">
+    <row r="143" spans="1:13" ht="121.5">
       <c r="A143" s="3" t="s">
         <v>41</v>
       </c>
@@ -8482,7 +8481,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="144" spans="1:13" ht="167.25" hidden="1">
+    <row r="144" spans="1:13" ht="167.25">
       <c r="A144" s="3" t="s">
         <v>41</v>
       </c>
@@ -8523,7 +8522,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="145" spans="1:13" ht="167.25" hidden="1">
+    <row r="145" spans="1:13" ht="167.25">
       <c r="A145" s="3" t="s">
         <v>41</v>
       </c>
@@ -8564,7 +8563,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="146" spans="1:13" ht="137.25" hidden="1">
+    <row r="146" spans="1:13" ht="137.25">
       <c r="A146" s="3" t="s">
         <v>41</v>
       </c>
@@ -8605,7 +8604,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="147" spans="1:13" ht="106.5" hidden="1">
+    <row r="147" spans="1:13" ht="106.5">
       <c r="A147" s="3" t="s">
         <v>41</v>
       </c>
@@ -8646,7 +8645,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="148" spans="1:13" ht="106.5" hidden="1">
+    <row r="148" spans="1:13" ht="106.5">
       <c r="A148" s="3" t="s">
         <v>41</v>
       </c>
@@ -8687,7 +8686,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="149" spans="1:13" ht="167.25" hidden="1">
+    <row r="149" spans="1:13" ht="167.25">
       <c r="A149" s="3" t="s">
         <v>41</v>
       </c>
@@ -8728,7 +8727,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="150" spans="1:13" ht="198" hidden="1">
+    <row r="150" spans="1:13" ht="198">
       <c r="A150" s="3" t="s">
         <v>41</v>
       </c>
@@ -8769,7 +8768,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="151" spans="1:13" ht="106.5" hidden="1">
+    <row r="151" spans="1:13" ht="106.5">
       <c r="A151" s="3" t="s">
         <v>41</v>
       </c>
@@ -8810,7 +8809,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="152" spans="1:13" ht="167.25" hidden="1">
+    <row r="152" spans="1:13" ht="167.25">
       <c r="A152" s="3" t="s">
         <v>41</v>
       </c>
@@ -8851,7 +8850,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="153" spans="1:13" ht="198" hidden="1">
+    <row r="153" spans="1:13" ht="198">
       <c r="A153" s="3" t="s">
         <v>41</v>
       </c>
@@ -8892,7 +8891,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="154" spans="1:13" ht="152.25" hidden="1">
+    <row r="154" spans="1:13" ht="152.25">
       <c r="A154" s="3" t="s">
         <v>41</v>
       </c>
@@ -8933,7 +8932,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="155" spans="1:13" ht="167.25" hidden="1">
+    <row r="155" spans="1:13" ht="167.25">
       <c r="A155" s="3" t="s">
         <v>41</v>
       </c>
@@ -8974,7 +8973,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="156" spans="1:13" ht="106.5" hidden="1">
+    <row r="156" spans="1:13" ht="106.5">
       <c r="A156" s="3" t="s">
         <v>41</v>
       </c>
@@ -9015,7 +9014,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="157" spans="1:13" ht="106.5" hidden="1">
+    <row r="157" spans="1:13" ht="106.5">
       <c r="A157" s="3" t="s">
         <v>41</v>
       </c>
@@ -9056,7 +9055,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="158" spans="1:13" ht="167.25" hidden="1">
+    <row r="158" spans="1:13" ht="167.25">
       <c r="A158" s="3" t="s">
         <v>41</v>
       </c>
@@ -9097,7 +9096,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="159" spans="1:13" ht="137.25" hidden="1">
+    <row r="159" spans="1:13" ht="137.25">
       <c r="A159" s="3" t="s">
         <v>41</v>
       </c>
@@ -9138,7 +9137,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="160" spans="1:13" ht="137.25" hidden="1">
+    <row r="160" spans="1:13" ht="137.25">
       <c r="A160" s="3" t="s">
         <v>41</v>
       </c>
@@ -9179,7 +9178,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="161" spans="1:13" ht="167.25" hidden="1">
+    <row r="161" spans="1:13" ht="167.25">
       <c r="A161" s="3" t="s">
         <v>41</v>
       </c>
@@ -9220,7 +9219,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="162" spans="1:13" ht="106.5" hidden="1">
+    <row r="162" spans="1:13" ht="106.5">
       <c r="A162" s="3" t="s">
         <v>41</v>
       </c>
@@ -9261,7 +9260,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="163" spans="1:13" ht="167.25" hidden="1">
+    <row r="163" spans="1:13" ht="167.25">
       <c r="A163" s="3" t="s">
         <v>41</v>
       </c>
@@ -9798,13 +9797,6 @@
       <c r="M196" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M163" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="12">
-      <filters>
-        <filter val="No especificado"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <dataValidations count="1">
     <dataValidation allowBlank="1" sqref="G1:H1" xr:uid="{368EE41E-2705-1B43-9A52-5A9881088DDE}"/>
   </dataValidations>
